--- a/src/results_template/CEC2014/30Dim.xlsx
+++ b/src/results_template/CEC2014/30Dim.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GtiHub\Repositories\Base-Optimization-Framework\src\results\results_template\CEC2014\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GtiHub\Repositories\Base-Optimization-Framework\src\results_template\CEC2014\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFBEAB7-EA47-4191-9696-995CBC43CD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E0BEC6-40BE-48F0-99DC-7544D0C0DABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conclusions" sheetId="2" r:id="rId1"/>
@@ -34,8 +34,33 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1209,7 +1234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1262,6 +1287,15 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1293,7 +1327,256 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="38">
+  <dxfs count="68">
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1563,12 +1846,6 @@
       </font>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <border outline="0">
         <top style="thin">
           <color indexed="64"/>
@@ -1577,9 +1854,6 @@
           <color indexed="64"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1595,11 +1869,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="S2:T92" totalsRowShown="0" headerRowDxfId="37" tableBorderDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="S2:T92" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="67">
   <autoFilter ref="S2:T92" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1937,26 +2211,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
     </row>
     <row r="2" spans="1:36" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -2009,10 +2283,10 @@
       <c r="R2" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="S2" s="9" t="s">
+      <c r="S2" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="T2" s="9" t="s">
+      <c r="T2" s="20" t="s">
         <v>39</v>
       </c>
       <c r="V2" s="12" t="str">
@@ -2077,13 +2351,13 @@
       </c>
     </row>
     <row r="3" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="22" t="s">
         <v>95</v>
       </c>
       <c r="D3" s="3"/>
@@ -2104,76 +2378,76 @@
       <c r="S3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T3" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="7" t="e">
-        <f t="shared" ref="V3:AJ3" si="1">_xlfn.RANK.EQ(D3,$D3:$R3,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W3" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X3" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y3" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z3" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA3" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB3" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC3" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD3" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE3" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF3" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG3" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH3" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI3" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ3" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
+      <c r="V3" s="7" t="e" cm="1">
+        <f t="array" ref="V3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(D3,2-INT(LOG10(ABS(D3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W3" s="7" t="e" cm="1">
+        <f t="array" ref="W3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(E3,2-INT(LOG10(ABS(E3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X3" s="7" t="e" cm="1">
+        <f t="array" ref="X3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(F3,2-INT(LOG10(ABS(F3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y3" s="7" t="e" cm="1">
+        <f t="array" ref="Y3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(G3,2-INT(LOG10(ABS(G3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z3" s="7" t="e" cm="1">
+        <f t="array" ref="Z3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(H3,2-INT(LOG10(ABS(H3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA3" s="7" t="e" cm="1">
+        <f t="array" ref="AA3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(I3,2-INT(LOG10(ABS(I3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB3" s="7" t="e" cm="1">
+        <f t="array" ref="AB3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(J3,2-INT(LOG10(ABS(J3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC3" s="7" t="e" cm="1">
+        <f t="array" ref="AC3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(K3,2-INT(LOG10(ABS(K3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD3" s="7" t="e" cm="1">
+        <f t="array" ref="AD3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(L3,2-INT(LOG10(ABS(L3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE3" s="7" t="e" cm="1">
+        <f t="array" ref="AE3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(M3,2-INT(LOG10(ABS(M3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF3" s="7" t="e" cm="1">
+        <f t="array" ref="AF3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(N3,2-INT(LOG10(ABS(N3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG3" s="7" t="e" cm="1">
+        <f t="array" ref="AG3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(O3,2-INT(LOG10(ABS(O3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH3" s="7" t="e" cm="1">
+        <f t="array" ref="AH3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(P3,2-INT(LOG10(ABS(P3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI3" s="7" t="e" cm="1">
+        <f t="array" ref="AI3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(Q3,2-INT(LOG10(ABS(Q3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ3" s="7" t="e" cm="1">
+        <f t="array" ref="AJ3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(R3,2-INT(LOG10(ABS(R3))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A4" s="21"/>
-      <c r="B4" s="9" t="s">
+      <c r="A4" s="24"/>
+      <c r="B4" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="20" t="s">
         <v>96</v>
       </c>
       <c r="D4" s="8"/>
@@ -2192,7 +2466,7 @@
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
       <c r="S4" s="14"/>
-      <c r="T4" s="9" t="s">
+      <c r="T4" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V4" s="7"/>
@@ -2208,11 +2482,11 @@
       <c r="AF4" s="7"/>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="24"/>
+      <c r="B5" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="21" t="s">
         <v>97</v>
       </c>
       <c r="D5" s="6"/>
@@ -2231,7 +2505,7 @@
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="5" t="s">
+      <c r="T5" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V5" s="7"/>
@@ -2247,11 +2521,11 @@
       <c r="AF5" s="7"/>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A6" s="21"/>
-      <c r="B6" s="2" t="s">
+      <c r="A6" s="24"/>
+      <c r="B6" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="22" t="s">
         <v>98</v>
       </c>
       <c r="D6" s="3"/>
@@ -2272,76 +2546,76 @@
       <c r="S6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="T6" s="2" t="s">
+      <c r="T6" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V6" s="7" t="e">
-        <f t="shared" ref="V6:AJ6" si="2">_xlfn.RANK.EQ(D6,$D6:$R6,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W6" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X6" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y6" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z6" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA6" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB6" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC6" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD6" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE6" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF6" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG6" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH6" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI6" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ6" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#N/A</v>
+      <c r="V6" s="7" t="e" cm="1">
+        <f t="array" ref="V6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(D6,2-INT(LOG10(ABS(D6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W6" s="7" t="e" cm="1">
+        <f t="array" ref="W6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(E6,2-INT(LOG10(ABS(E6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X6" s="7" t="e" cm="1">
+        <f t="array" ref="X6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(F6,2-INT(LOG10(ABS(F6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y6" s="7" t="e" cm="1">
+        <f t="array" ref="Y6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(G6,2-INT(LOG10(ABS(G6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z6" s="7" t="e" cm="1">
+        <f t="array" ref="Z6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(H6,2-INT(LOG10(ABS(H6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA6" s="7" t="e" cm="1">
+        <f t="array" ref="AA6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(I6,2-INT(LOG10(ABS(I6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB6" s="7" t="e" cm="1">
+        <f t="array" ref="AB6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(J6,2-INT(LOG10(ABS(J6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC6" s="7" t="e" cm="1">
+        <f t="array" ref="AC6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(K6,2-INT(LOG10(ABS(K6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD6" s="7" t="e" cm="1">
+        <f t="array" ref="AD6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(L6,2-INT(LOG10(ABS(L6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE6" s="7" t="e" cm="1">
+        <f t="array" ref="AE6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(M6,2-INT(LOG10(ABS(M6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF6" s="7" t="e" cm="1">
+        <f t="array" ref="AF6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(N6,2-INT(LOG10(ABS(N6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG6" s="7" t="e" cm="1">
+        <f t="array" ref="AG6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(O6,2-INT(LOG10(ABS(O6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH6" s="7" t="e" cm="1">
+        <f t="array" ref="AH6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(P6,2-INT(LOG10(ABS(P6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI6" s="7" t="e" cm="1">
+        <f t="array" ref="AI6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(Q6,2-INT(LOG10(ABS(Q6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ6" s="7" t="e" cm="1">
+        <f t="array" ref="AJ6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(R6,2-INT(LOG10(ABS(R6))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A7" s="21"/>
-      <c r="B7" s="9" t="s">
+      <c r="A7" s="24"/>
+      <c r="B7" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="20" t="s">
         <v>99</v>
       </c>
       <c r="D7" s="8"/>
@@ -2360,7 +2634,7 @@
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
       <c r="S7" s="14"/>
-      <c r="T7" s="9" t="s">
+      <c r="T7" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V7" s="7"/>
@@ -2376,11 +2650,11 @@
       <c r="AF7" s="7"/>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
-      <c r="B8" s="5" t="s">
+      <c r="A8" s="24"/>
+      <c r="B8" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="21" t="s">
         <v>100</v>
       </c>
       <c r="D8" s="6"/>
@@ -2399,7 +2673,7 @@
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
       <c r="S8" s="4"/>
-      <c r="T8" s="5" t="s">
+      <c r="T8" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V8" s="7"/>
@@ -2415,11 +2689,11 @@
       <c r="AF8" s="7"/>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A9" s="21"/>
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="24"/>
+      <c r="B9" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="22" t="s">
         <v>101</v>
       </c>
       <c r="D9" s="3"/>
@@ -2440,76 +2714,76 @@
       <c r="S9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="T9" s="2" t="s">
+      <c r="T9" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V9" s="7" t="e">
-        <f t="shared" ref="V9:AJ9" si="3">_xlfn.RANK.EQ(D9,$D9:$R9,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W9" s="7" t="e">
-        <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X9" s="7" t="e">
-        <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y9" s="7" t="e">
-        <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z9" s="7" t="e">
-        <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA9" s="7" t="e">
-        <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB9" s="7" t="e">
-        <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC9" s="7" t="e">
-        <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD9" s="7" t="e">
-        <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE9" s="7" t="e">
-        <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF9" s="7" t="e">
-        <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG9" s="7" t="e">
-        <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH9" s="7" t="e">
-        <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI9" s="7" t="e">
-        <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ9" s="7" t="e">
-        <f t="shared" si="3"/>
-        <v>#N/A</v>
+      <c r="V9" s="7" t="e" cm="1">
+        <f t="array" ref="V9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(D9,2-INT(LOG10(ABS(D9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W9" s="7" t="e" cm="1">
+        <f t="array" ref="W9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(E9,2-INT(LOG10(ABS(E9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X9" s="7" t="e" cm="1">
+        <f t="array" ref="X9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(F9,2-INT(LOG10(ABS(F9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y9" s="7" t="e" cm="1">
+        <f t="array" ref="Y9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(G9,2-INT(LOG10(ABS(G9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z9" s="7" t="e" cm="1">
+        <f t="array" ref="Z9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(H9,2-INT(LOG10(ABS(H9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA9" s="7" t="e" cm="1">
+        <f t="array" ref="AA9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(I9,2-INT(LOG10(ABS(I9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB9" s="7" t="e" cm="1">
+        <f t="array" ref="AB9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(J9,2-INT(LOG10(ABS(J9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC9" s="7" t="e" cm="1">
+        <f t="array" ref="AC9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(K9,2-INT(LOG10(ABS(K9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD9" s="7" t="e" cm="1">
+        <f t="array" ref="AD9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(L9,2-INT(LOG10(ABS(L9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE9" s="7" t="e" cm="1">
+        <f t="array" ref="AE9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(M9,2-INT(LOG10(ABS(M9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF9" s="7" t="e" cm="1">
+        <f t="array" ref="AF9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(N9,2-INT(LOG10(ABS(N9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG9" s="7" t="e" cm="1">
+        <f t="array" ref="AG9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(O9,2-INT(LOG10(ABS(O9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH9" s="7" t="e" cm="1">
+        <f t="array" ref="AH9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(P9,2-INT(LOG10(ABS(P9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI9" s="7" t="e" cm="1">
+        <f t="array" ref="AI9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(Q9,2-INT(LOG10(ABS(Q9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ9" s="7" t="e" cm="1">
+        <f t="array" ref="AJ9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(R9,2-INT(LOG10(ABS(R9))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A10" s="21"/>
-      <c r="B10" s="9" t="s">
+      <c r="A10" s="24"/>
+      <c r="B10" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="20" t="s">
         <v>102</v>
       </c>
       <c r="D10" s="8"/>
@@ -2528,7 +2802,7 @@
       <c r="Q10" s="8"/>
       <c r="R10" s="8"/>
       <c r="S10" s="14"/>
-      <c r="T10" s="9" t="s">
+      <c r="T10" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V10" s="7"/>
@@ -2544,11 +2818,11 @@
       <c r="AF10" s="7"/>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A11" s="24"/>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="27"/>
+      <c r="B11" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="21" t="s">
         <v>103</v>
       </c>
       <c r="D11" s="6"/>
@@ -2567,7 +2841,7 @@
       <c r="Q11" s="6"/>
       <c r="R11" s="6"/>
       <c r="S11" s="4"/>
-      <c r="T11" s="5" t="s">
+      <c r="T11" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V11" s="7"/>
@@ -2583,13 +2857,13 @@
       <c r="AF11" s="7"/>
     </row>
     <row r="12" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="22" t="s">
         <v>104</v>
       </c>
       <c r="D12" s="3"/>
@@ -2610,76 +2884,76 @@
       <c r="S12" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="T12" s="2" t="s">
+      <c r="T12" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V12" s="7" t="e">
-        <f t="shared" ref="V12:AJ12" si="4">_xlfn.RANK.EQ(D12,$D12:$R12,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W12" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X12" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y12" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z12" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA12" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB12" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC12" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD12" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE12" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF12" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG12" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH12" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI12" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ12" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#N/A</v>
+      <c r="V12" s="7" t="e" cm="1">
+        <f t="array" ref="V12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(D12,2-INT(LOG10(ABS(D12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W12" s="7" t="e" cm="1">
+        <f t="array" ref="W12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(E12,2-INT(LOG10(ABS(E12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X12" s="7" t="e" cm="1">
+        <f t="array" ref="X12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(F12,2-INT(LOG10(ABS(F12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y12" s="7" t="e" cm="1">
+        <f t="array" ref="Y12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(G12,2-INT(LOG10(ABS(G12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z12" s="7" t="e" cm="1">
+        <f t="array" ref="Z12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(H12,2-INT(LOG10(ABS(H12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA12" s="7" t="e" cm="1">
+        <f t="array" ref="AA12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(I12,2-INT(LOG10(ABS(I12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB12" s="7" t="e" cm="1">
+        <f t="array" ref="AB12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(J12,2-INT(LOG10(ABS(J12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC12" s="7" t="e" cm="1">
+        <f t="array" ref="AC12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(K12,2-INT(LOG10(ABS(K12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD12" s="7" t="e" cm="1">
+        <f t="array" ref="AD12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(L12,2-INT(LOG10(ABS(L12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE12" s="7" t="e" cm="1">
+        <f t="array" ref="AE12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(M12,2-INT(LOG10(ABS(M12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF12" s="7" t="e" cm="1">
+        <f t="array" ref="AF12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(N12,2-INT(LOG10(ABS(N12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG12" s="7" t="e" cm="1">
+        <f t="array" ref="AG12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(O12,2-INT(LOG10(ABS(O12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH12" s="7" t="e" cm="1">
+        <f t="array" ref="AH12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(P12,2-INT(LOG10(ABS(P12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI12" s="7" t="e" cm="1">
+        <f t="array" ref="AI12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(Q12,2-INT(LOG10(ABS(Q12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ12" s="7" t="e" cm="1">
+        <f t="array" ref="AJ12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(R12,2-INT(LOG10(ABS(R12))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A13" s="21"/>
-      <c r="B13" s="9" t="s">
+      <c r="A13" s="24"/>
+      <c r="B13" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="20" t="s">
         <v>105</v>
       </c>
       <c r="D13" s="8"/>
@@ -2698,7 +2972,7 @@
       <c r="Q13" s="8"/>
       <c r="R13" s="8"/>
       <c r="S13" s="14"/>
-      <c r="T13" s="9" t="s">
+      <c r="T13" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V13" s="7"/>
@@ -2714,11 +2988,11 @@
       <c r="AF13" s="7"/>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
-      <c r="B14" s="5" t="s">
+      <c r="A14" s="24"/>
+      <c r="B14" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="21" t="s">
         <v>106</v>
       </c>
       <c r="D14" s="6"/>
@@ -2737,7 +3011,7 @@
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
       <c r="S14" s="4"/>
-      <c r="T14" s="5" t="s">
+      <c r="T14" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V14" s="7"/>
@@ -2753,11 +3027,11 @@
       <c r="AF14" s="7"/>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A15" s="21"/>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="24"/>
+      <c r="B15" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="22" t="s">
         <v>107</v>
       </c>
       <c r="D15" s="3"/>
@@ -2778,76 +3052,76 @@
       <c r="S15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="T15" s="2" t="s">
+      <c r="T15" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V15" s="7" t="e">
-        <f t="shared" ref="V15:AJ15" si="5">_xlfn.RANK.EQ(D15,$D15:$R15,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W15" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X15" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y15" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z15" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA15" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB15" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC15" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD15" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE15" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF15" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG15" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH15" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI15" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ15" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#N/A</v>
+      <c r="V15" s="7" t="e" cm="1">
+        <f t="array" ref="V15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(D15,2-INT(LOG10(ABS(D15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W15" s="7" t="e" cm="1">
+        <f t="array" ref="W15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(E15,2-INT(LOG10(ABS(E15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X15" s="7" t="e" cm="1">
+        <f t="array" ref="X15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(F15,2-INT(LOG10(ABS(F15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y15" s="7" t="e" cm="1">
+        <f t="array" ref="Y15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(G15,2-INT(LOG10(ABS(G15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z15" s="7" t="e" cm="1">
+        <f t="array" ref="Z15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(H15,2-INT(LOG10(ABS(H15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA15" s="7" t="e" cm="1">
+        <f t="array" ref="AA15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(I15,2-INT(LOG10(ABS(I15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB15" s="7" t="e" cm="1">
+        <f t="array" ref="AB15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(J15,2-INT(LOG10(ABS(J15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC15" s="7" t="e" cm="1">
+        <f t="array" ref="AC15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(K15,2-INT(LOG10(ABS(K15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD15" s="7" t="e" cm="1">
+        <f t="array" ref="AD15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(L15,2-INT(LOG10(ABS(L15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE15" s="7" t="e" cm="1">
+        <f t="array" ref="AE15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(M15,2-INT(LOG10(ABS(M15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF15" s="7" t="e" cm="1">
+        <f t="array" ref="AF15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(N15,2-INT(LOG10(ABS(N15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG15" s="7" t="e" cm="1">
+        <f t="array" ref="AG15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(O15,2-INT(LOG10(ABS(O15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH15" s="7" t="e" cm="1">
+        <f t="array" ref="AH15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(P15,2-INT(LOG10(ABS(P15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI15" s="7" t="e" cm="1">
+        <f t="array" ref="AI15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(Q15,2-INT(LOG10(ABS(Q15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ15" s="7" t="e" cm="1">
+        <f t="array" ref="AJ15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(R15,2-INT(LOG10(ABS(R15))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A16" s="21"/>
-      <c r="B16" s="9" t="s">
+      <c r="A16" s="24"/>
+      <c r="B16" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="20" t="s">
         <v>108</v>
       </c>
       <c r="D16" s="8"/>
@@ -2866,7 +3140,7 @@
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
       <c r="S16" s="14"/>
-      <c r="T16" s="9" t="s">
+      <c r="T16" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V16" s="7"/>
@@ -2882,11 +3156,11 @@
       <c r="AF16" s="7"/>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A17" s="21"/>
-      <c r="B17" s="5" t="s">
+      <c r="A17" s="24"/>
+      <c r="B17" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="21" t="s">
         <v>109</v>
       </c>
       <c r="D17" s="6"/>
@@ -2905,7 +3179,7 @@
       <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
       <c r="S17" s="4"/>
-      <c r="T17" s="5" t="s">
+      <c r="T17" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V17" s="7"/>
@@ -2921,11 +3195,11 @@
       <c r="AF17" s="7"/>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A18" s="21"/>
-      <c r="B18" s="2" t="s">
+      <c r="A18" s="24"/>
+      <c r="B18" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="22" t="s">
         <v>110</v>
       </c>
       <c r="D18" s="3"/>
@@ -2946,76 +3220,76 @@
       <c r="S18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="T18" s="2" t="s">
+      <c r="T18" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V18" s="7" t="e">
-        <f t="shared" ref="V18:AJ18" si="6">_xlfn.RANK.EQ(D18,$D18:$R18,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W18" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X18" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y18" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z18" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA18" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB18" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC18" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD18" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE18" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF18" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG18" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH18" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI18" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ18" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#N/A</v>
+      <c r="V18" s="7" t="e" cm="1">
+        <f t="array" ref="V18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(D18,2-INT(LOG10(ABS(D18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W18" s="7" t="e" cm="1">
+        <f t="array" ref="W18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(E18,2-INT(LOG10(ABS(E18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X18" s="7" t="e" cm="1">
+        <f t="array" ref="X18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(F18,2-INT(LOG10(ABS(F18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y18" s="7" t="e" cm="1">
+        <f t="array" ref="Y18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(G18,2-INT(LOG10(ABS(G18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z18" s="7" t="e" cm="1">
+        <f t="array" ref="Z18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(H18,2-INT(LOG10(ABS(H18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA18" s="7" t="e" cm="1">
+        <f t="array" ref="AA18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(I18,2-INT(LOG10(ABS(I18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB18" s="7" t="e" cm="1">
+        <f t="array" ref="AB18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(J18,2-INT(LOG10(ABS(J18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC18" s="7" t="e" cm="1">
+        <f t="array" ref="AC18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(K18,2-INT(LOG10(ABS(K18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD18" s="7" t="e" cm="1">
+        <f t="array" ref="AD18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(L18,2-INT(LOG10(ABS(L18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE18" s="7" t="e" cm="1">
+        <f t="array" ref="AE18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(M18,2-INT(LOG10(ABS(M18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF18" s="7" t="e" cm="1">
+        <f t="array" ref="AF18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(N18,2-INT(LOG10(ABS(N18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG18" s="7" t="e" cm="1">
+        <f t="array" ref="AG18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(O18,2-INT(LOG10(ABS(O18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH18" s="7" t="e" cm="1">
+        <f t="array" ref="AH18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(P18,2-INT(LOG10(ABS(P18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI18" s="7" t="e" cm="1">
+        <f t="array" ref="AI18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(Q18,2-INT(LOG10(ABS(Q18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ18" s="7" t="e" cm="1">
+        <f t="array" ref="AJ18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(R18,2-INT(LOG10(ABS(R18))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A19" s="21"/>
-      <c r="B19" s="9" t="s">
+      <c r="A19" s="24"/>
+      <c r="B19" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="20" t="s">
         <v>111</v>
       </c>
       <c r="D19" s="8"/>
@@ -3034,7 +3308,7 @@
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
       <c r="S19" s="14"/>
-      <c r="T19" s="9" t="s">
+      <c r="T19" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V19" s="7"/>
@@ -3050,11 +3324,11 @@
       <c r="AF19" s="7"/>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A20" s="21"/>
-      <c r="B20" s="5" t="s">
+      <c r="A20" s="24"/>
+      <c r="B20" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="21" t="s">
         <v>112</v>
       </c>
       <c r="D20" s="6"/>
@@ -3073,7 +3347,7 @@
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
       <c r="S20" s="4"/>
-      <c r="T20" s="5" t="s">
+      <c r="T20" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V20" s="7"/>
@@ -3089,11 +3363,11 @@
       <c r="AF20" s="7"/>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A21" s="21"/>
-      <c r="B21" s="2" t="s">
+      <c r="A21" s="24"/>
+      <c r="B21" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="22" t="s">
         <v>113</v>
       </c>
       <c r="D21" s="3"/>
@@ -3114,76 +3388,76 @@
       <c r="S21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="T21" s="2" t="s">
+      <c r="T21" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V21" s="7" t="e">
-        <f t="shared" ref="V21:AJ21" si="7">_xlfn.RANK.EQ(D21,$D21:$R21,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W21" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X21" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y21" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z21" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA21" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB21" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC21" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD21" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE21" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF21" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG21" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH21" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI21" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ21" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#N/A</v>
+      <c r="V21" s="7" t="e" cm="1">
+        <f t="array" ref="V21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(D21,2-INT(LOG10(ABS(D21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W21" s="7" t="e" cm="1">
+        <f t="array" ref="W21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(E21,2-INT(LOG10(ABS(E21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X21" s="7" t="e" cm="1">
+        <f t="array" ref="X21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(F21,2-INT(LOG10(ABS(F21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y21" s="7" t="e" cm="1">
+        <f t="array" ref="Y21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(G21,2-INT(LOG10(ABS(G21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z21" s="7" t="e" cm="1">
+        <f t="array" ref="Z21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(H21,2-INT(LOG10(ABS(H21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA21" s="7" t="e" cm="1">
+        <f t="array" ref="AA21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(I21,2-INT(LOG10(ABS(I21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB21" s="7" t="e" cm="1">
+        <f t="array" ref="AB21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(J21,2-INT(LOG10(ABS(J21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC21" s="7" t="e" cm="1">
+        <f t="array" ref="AC21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(K21,2-INT(LOG10(ABS(K21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD21" s="7" t="e" cm="1">
+        <f t="array" ref="AD21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(L21,2-INT(LOG10(ABS(L21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE21" s="7" t="e" cm="1">
+        <f t="array" ref="AE21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(M21,2-INT(LOG10(ABS(M21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF21" s="7" t="e" cm="1">
+        <f t="array" ref="AF21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(N21,2-INT(LOG10(ABS(N21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG21" s="7" t="e" cm="1">
+        <f t="array" ref="AG21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(O21,2-INT(LOG10(ABS(O21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH21" s="7" t="e" cm="1">
+        <f t="array" ref="AH21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(P21,2-INT(LOG10(ABS(P21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI21" s="7" t="e" cm="1">
+        <f t="array" ref="AI21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(Q21,2-INT(LOG10(ABS(Q21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ21" s="7" t="e" cm="1">
+        <f t="array" ref="AJ21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(R21,2-INT(LOG10(ABS(R21))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A22" s="21"/>
-      <c r="B22" s="9" t="s">
+      <c r="A22" s="24"/>
+      <c r="B22" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="20" t="s">
         <v>114</v>
       </c>
       <c r="D22" s="8"/>
@@ -3202,7 +3476,7 @@
       <c r="Q22" s="8"/>
       <c r="R22" s="8"/>
       <c r="S22" s="14"/>
-      <c r="T22" s="9" t="s">
+      <c r="T22" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V22" s="7"/>
@@ -3218,11 +3492,11 @@
       <c r="AF22" s="7"/>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A23" s="21"/>
-      <c r="B23" s="5" t="s">
+      <c r="A23" s="24"/>
+      <c r="B23" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="21" t="s">
         <v>115</v>
       </c>
       <c r="D23" s="6"/>
@@ -3241,7 +3515,7 @@
       <c r="Q23" s="6"/>
       <c r="R23" s="6"/>
       <c r="S23" s="4"/>
-      <c r="T23" s="5" t="s">
+      <c r="T23" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V23" s="7"/>
@@ -3257,11 +3531,11 @@
       <c r="AF23" s="7"/>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A24" s="21"/>
-      <c r="B24" s="2" t="s">
+      <c r="A24" s="24"/>
+      <c r="B24" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="22" t="s">
         <v>116</v>
       </c>
       <c r="D24" s="3"/>
@@ -3282,76 +3556,76 @@
       <c r="S24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="T24" s="2" t="s">
+      <c r="T24" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V24" s="7" t="e">
-        <f t="shared" ref="V24:AJ24" si="8">_xlfn.RANK.EQ(D24,$D24:$R24,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W24" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X24" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y24" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z24" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA24" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB24" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC24" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD24" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE24" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF24" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG24" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH24" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI24" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ24" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#N/A</v>
+      <c r="V24" s="7" t="e" cm="1">
+        <f t="array" ref="V24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(D24,2-INT(LOG10(ABS(D24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W24" s="7" t="e" cm="1">
+        <f t="array" ref="W24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(E24,2-INT(LOG10(ABS(E24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X24" s="7" t="e" cm="1">
+        <f t="array" ref="X24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(F24,2-INT(LOG10(ABS(F24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y24" s="7" t="e" cm="1">
+        <f t="array" ref="Y24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(G24,2-INT(LOG10(ABS(G24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z24" s="7" t="e" cm="1">
+        <f t="array" ref="Z24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(H24,2-INT(LOG10(ABS(H24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA24" s="7" t="e" cm="1">
+        <f t="array" ref="AA24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(I24,2-INT(LOG10(ABS(I24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB24" s="7" t="e" cm="1">
+        <f t="array" ref="AB24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(J24,2-INT(LOG10(ABS(J24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC24" s="7" t="e" cm="1">
+        <f t="array" ref="AC24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(K24,2-INT(LOG10(ABS(K24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD24" s="7" t="e" cm="1">
+        <f t="array" ref="AD24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(L24,2-INT(LOG10(ABS(L24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE24" s="7" t="e" cm="1">
+        <f t="array" ref="AE24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(M24,2-INT(LOG10(ABS(M24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF24" s="7" t="e" cm="1">
+        <f t="array" ref="AF24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(N24,2-INT(LOG10(ABS(N24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG24" s="7" t="e" cm="1">
+        <f t="array" ref="AG24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(O24,2-INT(LOG10(ABS(O24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH24" s="7" t="e" cm="1">
+        <f t="array" ref="AH24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(P24,2-INT(LOG10(ABS(P24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI24" s="7" t="e" cm="1">
+        <f t="array" ref="AI24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(Q24,2-INT(LOG10(ABS(Q24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ24" s="7" t="e" cm="1">
+        <f t="array" ref="AJ24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(R24,2-INT(LOG10(ABS(R24))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A25" s="21"/>
-      <c r="B25" s="9" t="s">
+      <c r="A25" s="24"/>
+      <c r="B25" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="20" t="s">
         <v>117</v>
       </c>
       <c r="D25" s="8"/>
@@ -3370,7 +3644,7 @@
       <c r="Q25" s="8"/>
       <c r="R25" s="8"/>
       <c r="S25" s="14"/>
-      <c r="T25" s="9" t="s">
+      <c r="T25" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V25" s="7"/>
@@ -3386,11 +3660,11 @@
       <c r="AF25" s="7"/>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A26" s="21"/>
-      <c r="B26" s="5" t="s">
+      <c r="A26" s="24"/>
+      <c r="B26" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="21" t="s">
         <v>118</v>
       </c>
       <c r="D26" s="6"/>
@@ -3409,7 +3683,7 @@
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="4"/>
-      <c r="T26" s="5" t="s">
+      <c r="T26" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V26" s="7"/>
@@ -3425,11 +3699,11 @@
       <c r="AF26" s="7"/>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A27" s="21"/>
-      <c r="B27" s="2" t="s">
+      <c r="A27" s="24"/>
+      <c r="B27" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="22" t="s">
         <v>119</v>
       </c>
       <c r="D27" s="3"/>
@@ -3450,76 +3724,76 @@
       <c r="S27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="T27" s="2" t="s">
+      <c r="T27" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V27" s="7" t="e">
-        <f t="shared" ref="V27:AJ27" si="9">_xlfn.RANK.EQ(D27,$D27:$R27,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W27" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X27" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y27" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z27" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA27" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB27" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC27" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD27" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE27" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF27" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG27" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH27" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI27" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ27" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#N/A</v>
+      <c r="V27" s="7" t="e" cm="1">
+        <f t="array" ref="V27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(D27,2-INT(LOG10(ABS(D27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W27" s="7" t="e" cm="1">
+        <f t="array" ref="W27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(E27,2-INT(LOG10(ABS(E27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X27" s="7" t="e" cm="1">
+        <f t="array" ref="X27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(F27,2-INT(LOG10(ABS(F27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y27" s="7" t="e" cm="1">
+        <f t="array" ref="Y27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(G27,2-INT(LOG10(ABS(G27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z27" s="7" t="e" cm="1">
+        <f t="array" ref="Z27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(H27,2-INT(LOG10(ABS(H27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA27" s="7" t="e" cm="1">
+        <f t="array" ref="AA27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(I27,2-INT(LOG10(ABS(I27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB27" s="7" t="e" cm="1">
+        <f t="array" ref="AB27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(J27,2-INT(LOG10(ABS(J27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC27" s="7" t="e" cm="1">
+        <f t="array" ref="AC27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(K27,2-INT(LOG10(ABS(K27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD27" s="7" t="e" cm="1">
+        <f t="array" ref="AD27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(L27,2-INT(LOG10(ABS(L27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE27" s="7" t="e" cm="1">
+        <f t="array" ref="AE27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(M27,2-INT(LOG10(ABS(M27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF27" s="7" t="e" cm="1">
+        <f t="array" ref="AF27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(N27,2-INT(LOG10(ABS(N27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG27" s="7" t="e" cm="1">
+        <f t="array" ref="AG27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(O27,2-INT(LOG10(ABS(O27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH27" s="7" t="e" cm="1">
+        <f t="array" ref="AH27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(P27,2-INT(LOG10(ABS(P27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI27" s="7" t="e" cm="1">
+        <f t="array" ref="AI27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(Q27,2-INT(LOG10(ABS(Q27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ27" s="7" t="e" cm="1">
+        <f t="array" ref="AJ27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(R27,2-INT(LOG10(ABS(R27))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A28" s="21"/>
-      <c r="B28" s="9" t="s">
+      <c r="A28" s="24"/>
+      <c r="B28" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="20" t="s">
         <v>120</v>
       </c>
       <c r="D28" s="8"/>
@@ -3538,7 +3812,7 @@
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
       <c r="S28" s="14"/>
-      <c r="T28" s="9" t="s">
+      <c r="T28" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V28" s="7"/>
@@ -3554,11 +3828,11 @@
       <c r="AF28" s="7"/>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A29" s="21"/>
-      <c r="B29" s="5" t="s">
+      <c r="A29" s="24"/>
+      <c r="B29" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="21" t="s">
         <v>121</v>
       </c>
       <c r="D29" s="6"/>
@@ -3577,7 +3851,7 @@
       <c r="Q29" s="6"/>
       <c r="R29" s="6"/>
       <c r="S29" s="4"/>
-      <c r="T29" s="5" t="s">
+      <c r="T29" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V29" s="7"/>
@@ -3593,11 +3867,11 @@
       <c r="AF29" s="7"/>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A30" s="21"/>
-      <c r="B30" s="2" t="s">
+      <c r="A30" s="24"/>
+      <c r="B30" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="22" t="s">
         <v>122</v>
       </c>
       <c r="D30" s="3"/>
@@ -3618,76 +3892,76 @@
       <c r="S30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="T30" s="2" t="s">
+      <c r="T30" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V30" s="7" t="e">
-        <f t="shared" ref="V30:AJ30" si="10">_xlfn.RANK.EQ(D30,$D30:$R30,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W30" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X30" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y30" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z30" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA30" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB30" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC30" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD30" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE30" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF30" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG30" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH30" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI30" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ30" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#N/A</v>
+      <c r="V30" s="7" t="e" cm="1">
+        <f t="array" ref="V30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(D30,2-INT(LOG10(ABS(D30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W30" s="7" t="e" cm="1">
+        <f t="array" ref="W30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(E30,2-INT(LOG10(ABS(E30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X30" s="7" t="e" cm="1">
+        <f t="array" ref="X30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(F30,2-INT(LOG10(ABS(F30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y30" s="7" t="e" cm="1">
+        <f t="array" ref="Y30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(G30,2-INT(LOG10(ABS(G30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z30" s="7" t="e" cm="1">
+        <f t="array" ref="Z30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(H30,2-INT(LOG10(ABS(H30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA30" s="7" t="e" cm="1">
+        <f t="array" ref="AA30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(I30,2-INT(LOG10(ABS(I30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB30" s="7" t="e" cm="1">
+        <f t="array" ref="AB30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(J30,2-INT(LOG10(ABS(J30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC30" s="7" t="e" cm="1">
+        <f t="array" ref="AC30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(K30,2-INT(LOG10(ABS(K30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD30" s="7" t="e" cm="1">
+        <f t="array" ref="AD30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(L30,2-INT(LOG10(ABS(L30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE30" s="7" t="e" cm="1">
+        <f t="array" ref="AE30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(M30,2-INT(LOG10(ABS(M30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF30" s="7" t="e" cm="1">
+        <f t="array" ref="AF30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(N30,2-INT(LOG10(ABS(N30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG30" s="7" t="e" cm="1">
+        <f t="array" ref="AG30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(O30,2-INT(LOG10(ABS(O30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH30" s="7" t="e" cm="1">
+        <f t="array" ref="AH30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(P30,2-INT(LOG10(ABS(P30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI30" s="7" t="e" cm="1">
+        <f t="array" ref="AI30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(Q30,2-INT(LOG10(ABS(Q30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ30" s="7" t="e" cm="1">
+        <f t="array" ref="AJ30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(R30,2-INT(LOG10(ABS(R30))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A31" s="21"/>
-      <c r="B31" s="9" t="s">
+      <c r="A31" s="24"/>
+      <c r="B31" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="20" t="s">
         <v>123</v>
       </c>
       <c r="D31" s="8"/>
@@ -3706,7 +3980,7 @@
       <c r="Q31" s="8"/>
       <c r="R31" s="8"/>
       <c r="S31" s="14"/>
-      <c r="T31" s="9" t="s">
+      <c r="T31" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V31" s="7"/>
@@ -3722,11 +3996,11 @@
       <c r="AF31" s="7"/>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A32" s="21"/>
-      <c r="B32" s="5" t="s">
+      <c r="A32" s="24"/>
+      <c r="B32" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="21" t="s">
         <v>124</v>
       </c>
       <c r="D32" s="6"/>
@@ -3745,7 +4019,7 @@
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="4"/>
-      <c r="T32" s="5" t="s">
+      <c r="T32" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V32" s="7"/>
@@ -3761,11 +4035,11 @@
       <c r="AF32" s="7"/>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A33" s="21"/>
-      <c r="B33" s="2" t="s">
+      <c r="A33" s="24"/>
+      <c r="B33" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="22" t="s">
         <v>125</v>
       </c>
       <c r="D33" s="3"/>
@@ -3786,76 +4060,76 @@
       <c r="S33" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="T33" s="2" t="s">
+      <c r="T33" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V33" s="7" t="e">
-        <f t="shared" ref="V33:AJ33" si="11">_xlfn.RANK.EQ(D33,$D33:$R33,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W33" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X33" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y33" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z33" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA33" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB33" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC33" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD33" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE33" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF33" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG33" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH33" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI33" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ33" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#N/A</v>
+      <c r="V33" s="7" t="e" cm="1">
+        <f t="array" ref="V33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(D33,2-INT(LOG10(ABS(D33))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W33" s="7" t="e" cm="1">
+        <f t="array" ref="W33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(E33,2-INT(LOG10(ABS(E33))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X33" s="7" t="e" cm="1">
+        <f t="array" ref="X33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(F33,2-INT(LOG10(ABS(F33))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y33" s="7" t="e" cm="1">
+        <f t="array" ref="Y33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(G33,2-INT(LOG10(ABS(G33))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z33" s="7" t="e" cm="1">
+        <f t="array" ref="Z33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(H33,2-INT(LOG10(ABS(H33))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA33" s="7" t="e" cm="1">
+        <f t="array" ref="AA33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(I33,2-INT(LOG10(ABS(I33))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB33" s="7" t="e" cm="1">
+        <f t="array" ref="AB33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(J33,2-INT(LOG10(ABS(J33))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC33" s="7" t="e" cm="1">
+        <f t="array" ref="AC33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(K33,2-INT(LOG10(ABS(K33))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD33" s="7" t="e" cm="1">
+        <f t="array" ref="AD33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(L33,2-INT(LOG10(ABS(L33))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE33" s="7" t="e" cm="1">
+        <f t="array" ref="AE33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(M33,2-INT(LOG10(ABS(M33))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF33" s="7" t="e" cm="1">
+        <f t="array" ref="AF33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(N33,2-INT(LOG10(ABS(N33))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG33" s="7" t="e" cm="1">
+        <f t="array" ref="AG33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(O33,2-INT(LOG10(ABS(O33))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH33" s="7" t="e" cm="1">
+        <f t="array" ref="AH33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(P33,2-INT(LOG10(ABS(P33))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI33" s="7" t="e" cm="1">
+        <f t="array" ref="AI33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(Q33,2-INT(LOG10(ABS(Q33))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ33" s="7" t="e" cm="1">
+        <f t="array" ref="AJ33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(R33,2-INT(LOG10(ABS(R33))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A34" s="21"/>
-      <c r="B34" s="9" t="s">
+      <c r="A34" s="24"/>
+      <c r="B34" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="20" t="s">
         <v>126</v>
       </c>
       <c r="D34" s="8"/>
@@ -3874,7 +4148,7 @@
       <c r="Q34" s="8"/>
       <c r="R34" s="8"/>
       <c r="S34" s="14"/>
-      <c r="T34" s="9" t="s">
+      <c r="T34" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V34" s="7"/>
@@ -3890,11 +4164,11 @@
       <c r="AF34" s="7"/>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A35" s="21"/>
-      <c r="B35" s="5" t="s">
+      <c r="A35" s="24"/>
+      <c r="B35" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="21" t="s">
         <v>127</v>
       </c>
       <c r="D35" s="6"/>
@@ -3913,7 +4187,7 @@
       <c r="Q35" s="6"/>
       <c r="R35" s="6"/>
       <c r="S35" s="4"/>
-      <c r="T35" s="5" t="s">
+      <c r="T35" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V35" s="7"/>
@@ -3929,11 +4203,11 @@
       <c r="AF35" s="7"/>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A36" s="21"/>
-      <c r="B36" s="2" t="s">
+      <c r="A36" s="24"/>
+      <c r="B36" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="22" t="s">
         <v>128</v>
       </c>
       <c r="D36" s="3"/>
@@ -3954,76 +4228,76 @@
       <c r="S36" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="T36" s="2" t="s">
+      <c r="T36" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V36" s="7" t="e">
-        <f t="shared" ref="V36:AJ36" si="12">_xlfn.RANK.EQ(D36,$D36:$R36,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W36" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X36" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y36" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z36" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA36" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB36" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC36" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD36" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE36" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF36" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG36" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH36" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI36" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ36" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#N/A</v>
+      <c r="V36" s="7" t="e" cm="1">
+        <f t="array" ref="V36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(D36,2-INT(LOG10(ABS(D36))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W36" s="7" t="e" cm="1">
+        <f t="array" ref="W36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(E36,2-INT(LOG10(ABS(E36))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X36" s="7" t="e" cm="1">
+        <f t="array" ref="X36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(F36,2-INT(LOG10(ABS(F36))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y36" s="7" t="e" cm="1">
+        <f t="array" ref="Y36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(G36,2-INT(LOG10(ABS(G36))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z36" s="7" t="e" cm="1">
+        <f t="array" ref="Z36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(H36,2-INT(LOG10(ABS(H36))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA36" s="7" t="e" cm="1">
+        <f t="array" ref="AA36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(I36,2-INT(LOG10(ABS(I36))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB36" s="7" t="e" cm="1">
+        <f t="array" ref="AB36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(J36,2-INT(LOG10(ABS(J36))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC36" s="7" t="e" cm="1">
+        <f t="array" ref="AC36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(K36,2-INT(LOG10(ABS(K36))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD36" s="7" t="e" cm="1">
+        <f t="array" ref="AD36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(L36,2-INT(LOG10(ABS(L36))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE36" s="7" t="e" cm="1">
+        <f t="array" ref="AE36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(M36,2-INT(LOG10(ABS(M36))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF36" s="7" t="e" cm="1">
+        <f t="array" ref="AF36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(N36,2-INT(LOG10(ABS(N36))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG36" s="7" t="e" cm="1">
+        <f t="array" ref="AG36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(O36,2-INT(LOG10(ABS(O36))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH36" s="7" t="e" cm="1">
+        <f t="array" ref="AH36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(P36,2-INT(LOG10(ABS(P36))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI36" s="7" t="e" cm="1">
+        <f t="array" ref="AI36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(Q36,2-INT(LOG10(ABS(Q36))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ36" s="7" t="e" cm="1">
+        <f t="array" ref="AJ36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(R36,2-INT(LOG10(ABS(R36))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A37" s="21"/>
-      <c r="B37" s="9" t="s">
+      <c r="A37" s="24"/>
+      <c r="B37" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="20" t="s">
         <v>129</v>
       </c>
       <c r="D37" s="8"/>
@@ -4042,7 +4316,7 @@
       <c r="Q37" s="8"/>
       <c r="R37" s="8"/>
       <c r="S37" s="14"/>
-      <c r="T37" s="9" t="s">
+      <c r="T37" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V37" s="7"/>
@@ -4058,11 +4332,11 @@
       <c r="AF37" s="7"/>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A38" s="21"/>
-      <c r="B38" s="5" t="s">
+      <c r="A38" s="24"/>
+      <c r="B38" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="21" t="s">
         <v>130</v>
       </c>
       <c r="D38" s="6"/>
@@ -4081,7 +4355,7 @@
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
       <c r="S38" s="4"/>
-      <c r="T38" s="5" t="s">
+      <c r="T38" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V38" s="7"/>
@@ -4097,11 +4371,11 @@
       <c r="AF38" s="7"/>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A39" s="21"/>
-      <c r="B39" s="2" t="s">
+      <c r="A39" s="24"/>
+      <c r="B39" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="22" t="s">
         <v>131</v>
       </c>
       <c r="D39" s="3"/>
@@ -4122,76 +4396,76 @@
       <c r="S39" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="T39" s="2" t="s">
+      <c r="T39" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V39" s="7" t="e">
-        <f t="shared" ref="V39:AJ39" si="13">_xlfn.RANK.EQ(D39,$D39:$R39,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W39" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X39" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y39" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z39" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA39" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB39" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC39" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD39" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE39" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF39" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG39" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH39" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI39" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ39" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#N/A</v>
+      <c r="V39" s="7" t="e" cm="1">
+        <f t="array" ref="V39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(D39,2-INT(LOG10(ABS(D39))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W39" s="7" t="e" cm="1">
+        <f t="array" ref="W39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(E39,2-INT(LOG10(ABS(E39))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X39" s="7" t="e" cm="1">
+        <f t="array" ref="X39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(F39,2-INT(LOG10(ABS(F39))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y39" s="7" t="e" cm="1">
+        <f t="array" ref="Y39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(G39,2-INT(LOG10(ABS(G39))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z39" s="7" t="e" cm="1">
+        <f t="array" ref="Z39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(H39,2-INT(LOG10(ABS(H39))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA39" s="7" t="e" cm="1">
+        <f t="array" ref="AA39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(I39,2-INT(LOG10(ABS(I39))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB39" s="7" t="e" cm="1">
+        <f t="array" ref="AB39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(J39,2-INT(LOG10(ABS(J39))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC39" s="7" t="e" cm="1">
+        <f t="array" ref="AC39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(K39,2-INT(LOG10(ABS(K39))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD39" s="7" t="e" cm="1">
+        <f t="array" ref="AD39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(L39,2-INT(LOG10(ABS(L39))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE39" s="7" t="e" cm="1">
+        <f t="array" ref="AE39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(M39,2-INT(LOG10(ABS(M39))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF39" s="7" t="e" cm="1">
+        <f t="array" ref="AF39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(N39,2-INT(LOG10(ABS(N39))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG39" s="7" t="e" cm="1">
+        <f t="array" ref="AG39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(O39,2-INT(LOG10(ABS(O39))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH39" s="7" t="e" cm="1">
+        <f t="array" ref="AH39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(P39,2-INT(LOG10(ABS(P39))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI39" s="7" t="e" cm="1">
+        <f t="array" ref="AI39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(Q39,2-INT(LOG10(ABS(Q39))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ39" s="7" t="e" cm="1">
+        <f t="array" ref="AJ39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(R39,2-INT(LOG10(ABS(R39))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A40" s="21"/>
-      <c r="B40" s="9" t="s">
+      <c r="A40" s="24"/>
+      <c r="B40" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="20" t="s">
         <v>132</v>
       </c>
       <c r="D40" s="8"/>
@@ -4210,7 +4484,7 @@
       <c r="Q40" s="8"/>
       <c r="R40" s="8"/>
       <c r="S40" s="14"/>
-      <c r="T40" s="9" t="s">
+      <c r="T40" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V40" s="7"/>
@@ -4226,11 +4500,11 @@
       <c r="AF40" s="7"/>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A41" s="21"/>
-      <c r="B41" s="5" t="s">
+      <c r="A41" s="24"/>
+      <c r="B41" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="21" t="s">
         <v>133</v>
       </c>
       <c r="D41" s="6"/>
@@ -4249,7 +4523,7 @@
       <c r="Q41" s="6"/>
       <c r="R41" s="6"/>
       <c r="S41" s="4"/>
-      <c r="T41" s="5" t="s">
+      <c r="T41" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V41" s="7"/>
@@ -4265,11 +4539,11 @@
       <c r="AF41" s="7"/>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A42" s="21"/>
-      <c r="B42" s="2" t="s">
+      <c r="A42" s="24"/>
+      <c r="B42" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="22" t="s">
         <v>134</v>
       </c>
       <c r="D42" s="3"/>
@@ -4290,76 +4564,76 @@
       <c r="S42" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T42" s="2" t="s">
+      <c r="T42" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V42" s="7" t="e">
-        <f t="shared" ref="V42:AJ42" si="14">_xlfn.RANK.EQ(D42,$D42:$R42,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W42" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X42" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y42" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z42" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA42" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB42" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC42" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD42" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE42" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF42" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG42" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH42" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI42" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ42" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#N/A</v>
+      <c r="V42" s="7" t="e" cm="1">
+        <f t="array" ref="V42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(D42,2-INT(LOG10(ABS(D42))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W42" s="7" t="e" cm="1">
+        <f t="array" ref="W42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(E42,2-INT(LOG10(ABS(E42))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X42" s="7" t="e" cm="1">
+        <f t="array" ref="X42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(F42,2-INT(LOG10(ABS(F42))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y42" s="7" t="e" cm="1">
+        <f t="array" ref="Y42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(G42,2-INT(LOG10(ABS(G42))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z42" s="7" t="e" cm="1">
+        <f t="array" ref="Z42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(H42,2-INT(LOG10(ABS(H42))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA42" s="7" t="e" cm="1">
+        <f t="array" ref="AA42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(I42,2-INT(LOG10(ABS(I42))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB42" s="7" t="e" cm="1">
+        <f t="array" ref="AB42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(J42,2-INT(LOG10(ABS(J42))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC42" s="7" t="e" cm="1">
+        <f t="array" ref="AC42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(K42,2-INT(LOG10(ABS(K42))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD42" s="7" t="e" cm="1">
+        <f t="array" ref="AD42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(L42,2-INT(LOG10(ABS(L42))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE42" s="7" t="e" cm="1">
+        <f t="array" ref="AE42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(M42,2-INT(LOG10(ABS(M42))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF42" s="7" t="e" cm="1">
+        <f t="array" ref="AF42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(N42,2-INT(LOG10(ABS(N42))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG42" s="7" t="e" cm="1">
+        <f t="array" ref="AG42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(O42,2-INT(LOG10(ABS(O42))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH42" s="7" t="e" cm="1">
+        <f t="array" ref="AH42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(P42,2-INT(LOG10(ABS(P42))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI42" s="7" t="e" cm="1">
+        <f t="array" ref="AI42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(Q42,2-INT(LOG10(ABS(Q42))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ42" s="7" t="e" cm="1">
+        <f t="array" ref="AJ42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(R42,2-INT(LOG10(ABS(R42))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A43" s="21"/>
-      <c r="B43" s="9" t="s">
+      <c r="A43" s="24"/>
+      <c r="B43" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="20" t="s">
         <v>135</v>
       </c>
       <c r="D43" s="8"/>
@@ -4378,7 +4652,7 @@
       <c r="Q43" s="8"/>
       <c r="R43" s="8"/>
       <c r="S43" s="14"/>
-      <c r="T43" s="9" t="s">
+      <c r="T43" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V43" s="7"/>
@@ -4394,11 +4668,11 @@
       <c r="AF43" s="7"/>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A44" s="21"/>
-      <c r="B44" s="5" t="s">
+      <c r="A44" s="24"/>
+      <c r="B44" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="21" t="s">
         <v>136</v>
       </c>
       <c r="D44" s="6"/>
@@ -4417,7 +4691,7 @@
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
       <c r="S44" s="4"/>
-      <c r="T44" s="5" t="s">
+      <c r="T44" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V44" s="7"/>
@@ -4433,11 +4707,11 @@
       <c r="AF44" s="7"/>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A45" s="21"/>
-      <c r="B45" s="2" t="s">
+      <c r="A45" s="24"/>
+      <c r="B45" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="22" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="3"/>
@@ -4458,76 +4732,76 @@
       <c r="S45" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="T45" s="2" t="s">
+      <c r="T45" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V45" s="7" t="e">
-        <f t="shared" ref="V45:AJ45" si="15">_xlfn.RANK.EQ(D45,$D45:$R45,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W45" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X45" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y45" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z45" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA45" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB45" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC45" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD45" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE45" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF45" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG45" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH45" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI45" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ45" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#N/A</v>
+      <c r="V45" s="7" t="e" cm="1">
+        <f t="array" ref="V45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(D45,2-INT(LOG10(ABS(D45))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W45" s="7" t="e" cm="1">
+        <f t="array" ref="W45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(E45,2-INT(LOG10(ABS(E45))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X45" s="7" t="e" cm="1">
+        <f t="array" ref="X45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(F45,2-INT(LOG10(ABS(F45))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y45" s="7" t="e" cm="1">
+        <f t="array" ref="Y45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(G45,2-INT(LOG10(ABS(G45))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z45" s="7" t="e" cm="1">
+        <f t="array" ref="Z45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(H45,2-INT(LOG10(ABS(H45))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA45" s="7" t="e" cm="1">
+        <f t="array" ref="AA45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(I45,2-INT(LOG10(ABS(I45))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB45" s="7" t="e" cm="1">
+        <f t="array" ref="AB45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(J45,2-INT(LOG10(ABS(J45))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC45" s="7" t="e" cm="1">
+        <f t="array" ref="AC45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(K45,2-INT(LOG10(ABS(K45))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD45" s="7" t="e" cm="1">
+        <f t="array" ref="AD45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(L45,2-INT(LOG10(ABS(L45))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE45" s="7" t="e" cm="1">
+        <f t="array" ref="AE45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(M45,2-INT(LOG10(ABS(M45))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF45" s="7" t="e" cm="1">
+        <f t="array" ref="AF45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(N45,2-INT(LOG10(ABS(N45))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG45" s="7" t="e" cm="1">
+        <f t="array" ref="AG45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(O45,2-INT(LOG10(ABS(O45))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH45" s="7" t="e" cm="1">
+        <f t="array" ref="AH45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(P45,2-INT(LOG10(ABS(P45))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI45" s="7" t="e" cm="1">
+        <f t="array" ref="AI45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(Q45,2-INT(LOG10(ABS(Q45))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ45" s="7" t="e" cm="1">
+        <f t="array" ref="AJ45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(R45,2-INT(LOG10(ABS(R45))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A46" s="21"/>
-      <c r="B46" s="9" t="s">
+      <c r="A46" s="24"/>
+      <c r="B46" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C46" s="20" t="s">
         <v>138</v>
       </c>
       <c r="D46" s="8"/>
@@ -4546,7 +4820,7 @@
       <c r="Q46" s="8"/>
       <c r="R46" s="8"/>
       <c r="S46" s="14"/>
-      <c r="T46" s="9" t="s">
+      <c r="T46" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V46" s="7"/>
@@ -4562,11 +4836,11 @@
       <c r="AF46" s="7"/>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A47" s="21"/>
-      <c r="B47" s="5" t="s">
+      <c r="A47" s="24"/>
+      <c r="B47" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="21" t="s">
         <v>139</v>
       </c>
       <c r="D47" s="6"/>
@@ -4585,7 +4859,7 @@
       <c r="Q47" s="6"/>
       <c r="R47" s="6"/>
       <c r="S47" s="4"/>
-      <c r="T47" s="5" t="s">
+      <c r="T47" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V47" s="7"/>
@@ -4601,11 +4875,11 @@
       <c r="AF47" s="7"/>
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A48" s="21"/>
-      <c r="B48" s="2" t="s">
+      <c r="A48" s="24"/>
+      <c r="B48" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="22" t="s">
         <v>140</v>
       </c>
       <c r="D48" s="3"/>
@@ -4626,76 +4900,76 @@
       <c r="S48" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="T48" s="2" t="s">
+      <c r="T48" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V48" s="7" t="e">
-        <f t="shared" ref="V48:AJ48" si="16">_xlfn.RANK.EQ(D48,$D48:$R48,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W48" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X48" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y48" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z48" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA48" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB48" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC48" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD48" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE48" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF48" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG48" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH48" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI48" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ48" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#N/A</v>
+      <c r="V48" s="7" t="e" cm="1">
+        <f t="array" ref="V48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(D48,2-INT(LOG10(ABS(D48))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W48" s="7" t="e" cm="1">
+        <f t="array" ref="W48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(E48,2-INT(LOG10(ABS(E48))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X48" s="7" t="e" cm="1">
+        <f t="array" ref="X48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(F48,2-INT(LOG10(ABS(F48))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y48" s="7" t="e" cm="1">
+        <f t="array" ref="Y48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(G48,2-INT(LOG10(ABS(G48))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z48" s="7" t="e" cm="1">
+        <f t="array" ref="Z48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(H48,2-INT(LOG10(ABS(H48))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA48" s="7" t="e" cm="1">
+        <f t="array" ref="AA48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(I48,2-INT(LOG10(ABS(I48))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB48" s="7" t="e" cm="1">
+        <f t="array" ref="AB48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(J48,2-INT(LOG10(ABS(J48))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC48" s="7" t="e" cm="1">
+        <f t="array" ref="AC48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(K48,2-INT(LOG10(ABS(K48))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD48" s="7" t="e" cm="1">
+        <f t="array" ref="AD48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(L48,2-INT(LOG10(ABS(L48))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE48" s="7" t="e" cm="1">
+        <f t="array" ref="AE48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(M48,2-INT(LOG10(ABS(M48))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF48" s="7" t="e" cm="1">
+        <f t="array" ref="AF48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(N48,2-INT(LOG10(ABS(N48))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG48" s="7" t="e" cm="1">
+        <f t="array" ref="AG48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(O48,2-INT(LOG10(ABS(O48))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH48" s="7" t="e" cm="1">
+        <f t="array" ref="AH48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(P48,2-INT(LOG10(ABS(P48))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI48" s="7" t="e" cm="1">
+        <f t="array" ref="AI48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(Q48,2-INT(LOG10(ABS(Q48))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ48" s="7" t="e" cm="1">
+        <f t="array" ref="AJ48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(R48,2-INT(LOG10(ABS(R48))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="49" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A49" s="21"/>
-      <c r="B49" s="9" t="s">
+      <c r="A49" s="24"/>
+      <c r="B49" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="20" t="s">
         <v>141</v>
       </c>
       <c r="D49" s="8"/>
@@ -4714,7 +4988,7 @@
       <c r="Q49" s="8"/>
       <c r="R49" s="8"/>
       <c r="S49" s="14"/>
-      <c r="T49" s="9" t="s">
+      <c r="T49" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V49" s="7"/>
@@ -4730,11 +5004,11 @@
       <c r="AF49" s="7"/>
     </row>
     <row r="50" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A50" s="24"/>
-      <c r="B50" s="5" t="s">
+      <c r="A50" s="27"/>
+      <c r="B50" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="21" t="s">
         <v>142</v>
       </c>
       <c r="D50" s="6"/>
@@ -4753,7 +5027,7 @@
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
       <c r="S50" s="4"/>
-      <c r="T50" s="5" t="s">
+      <c r="T50" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V50" s="7"/>
@@ -4769,13 +5043,13 @@
       <c r="AF50" s="7"/>
     </row>
     <row r="51" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="26" t="s">
+      <c r="A51" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="22" t="s">
         <v>143</v>
       </c>
       <c r="D51" s="3"/>
@@ -4796,76 +5070,76 @@
       <c r="S51" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T51" s="2" t="s">
+      <c r="T51" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V51" s="7" t="e">
-        <f t="shared" ref="V51:AJ51" si="17">_xlfn.RANK.EQ(D51,$D51:$R51,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W51" s="7" t="e">
-        <f t="shared" si="17"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X51" s="7" t="e">
-        <f t="shared" si="17"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y51" s="7" t="e">
-        <f t="shared" si="17"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z51" s="7" t="e">
-        <f t="shared" si="17"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA51" s="7" t="e">
-        <f t="shared" si="17"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB51" s="7" t="e">
-        <f t="shared" si="17"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC51" s="7" t="e">
-        <f t="shared" si="17"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD51" s="7" t="e">
-        <f t="shared" si="17"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE51" s="7" t="e">
-        <f t="shared" si="17"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF51" s="7" t="e">
-        <f t="shared" si="17"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG51" s="7" t="e">
-        <f t="shared" si="17"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH51" s="7" t="e">
-        <f t="shared" si="17"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI51" s="7" t="e">
-        <f t="shared" si="17"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ51" s="7" t="e">
-        <f t="shared" si="17"/>
-        <v>#N/A</v>
+      <c r="V51" s="7" t="e" cm="1">
+        <f t="array" ref="V51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(D51,2-INT(LOG10(ABS(D51))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W51" s="7" t="e" cm="1">
+        <f t="array" ref="W51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(E51,2-INT(LOG10(ABS(E51))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X51" s="7" t="e" cm="1">
+        <f t="array" ref="X51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(F51,2-INT(LOG10(ABS(F51))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y51" s="7" t="e" cm="1">
+        <f t="array" ref="Y51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(G51,2-INT(LOG10(ABS(G51))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z51" s="7" t="e" cm="1">
+        <f t="array" ref="Z51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(H51,2-INT(LOG10(ABS(H51))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA51" s="7" t="e" cm="1">
+        <f t="array" ref="AA51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(I51,2-INT(LOG10(ABS(I51))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB51" s="7" t="e" cm="1">
+        <f t="array" ref="AB51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(J51,2-INT(LOG10(ABS(J51))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC51" s="7" t="e" cm="1">
+        <f t="array" ref="AC51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(K51,2-INT(LOG10(ABS(K51))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD51" s="7" t="e" cm="1">
+        <f t="array" ref="AD51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(L51,2-INT(LOG10(ABS(L51))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE51" s="7" t="e" cm="1">
+        <f t="array" ref="AE51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(M51,2-INT(LOG10(ABS(M51))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF51" s="7" t="e" cm="1">
+        <f t="array" ref="AF51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(N51,2-INT(LOG10(ABS(N51))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG51" s="7" t="e" cm="1">
+        <f t="array" ref="AG51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(O51,2-INT(LOG10(ABS(O51))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH51" s="7" t="e" cm="1">
+        <f t="array" ref="AH51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(P51,2-INT(LOG10(ABS(P51))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI51" s="7" t="e" cm="1">
+        <f t="array" ref="AI51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(Q51,2-INT(LOG10(ABS(Q51))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ51" s="7" t="e" cm="1">
+        <f t="array" ref="AJ51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(R51,2-INT(LOG10(ABS(R51))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="52" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A52" s="21"/>
-      <c r="B52" s="9" t="s">
+      <c r="A52" s="24"/>
+      <c r="B52" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="20" t="s">
         <v>144</v>
       </c>
       <c r="D52" s="8"/>
@@ -4884,7 +5158,7 @@
       <c r="Q52" s="8"/>
       <c r="R52" s="8"/>
       <c r="S52" s="14"/>
-      <c r="T52" s="9" t="s">
+      <c r="T52" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V52" s="7"/>
@@ -4900,11 +5174,11 @@
       <c r="AF52" s="7"/>
     </row>
     <row r="53" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A53" s="21"/>
-      <c r="B53" s="5" t="s">
+      <c r="A53" s="24"/>
+      <c r="B53" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="21" t="s">
         <v>145</v>
       </c>
       <c r="D53" s="6"/>
@@ -4923,7 +5197,7 @@
       <c r="Q53" s="6"/>
       <c r="R53" s="6"/>
       <c r="S53" s="4"/>
-      <c r="T53" s="5" t="s">
+      <c r="T53" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V53" s="7"/>
@@ -4939,11 +5213,11 @@
       <c r="AF53" s="7"/>
     </row>
     <row r="54" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A54" s="21"/>
-      <c r="B54" s="2" t="s">
+      <c r="A54" s="24"/>
+      <c r="B54" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="22" t="s">
         <v>146</v>
       </c>
       <c r="D54" s="3"/>
@@ -4964,76 +5238,76 @@
       <c r="S54" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="T54" s="2" t="s">
+      <c r="T54" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V54" s="7" t="e">
-        <f t="shared" ref="V54:AJ54" si="18">_xlfn.RANK.EQ(D54,$D54:$R54,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W54" s="7" t="e">
-        <f t="shared" si="18"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X54" s="7" t="e">
-        <f t="shared" si="18"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y54" s="7" t="e">
-        <f t="shared" si="18"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z54" s="7" t="e">
-        <f t="shared" si="18"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA54" s="7" t="e">
-        <f t="shared" si="18"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB54" s="7" t="e">
-        <f t="shared" si="18"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC54" s="7" t="e">
-        <f t="shared" si="18"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD54" s="7" t="e">
-        <f t="shared" si="18"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE54" s="7" t="e">
-        <f t="shared" si="18"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF54" s="7" t="e">
-        <f t="shared" si="18"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG54" s="7" t="e">
-        <f t="shared" si="18"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH54" s="7" t="e">
-        <f t="shared" si="18"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI54" s="7" t="e">
-        <f t="shared" si="18"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ54" s="7" t="e">
-        <f t="shared" si="18"/>
-        <v>#N/A</v>
+      <c r="V54" s="7" t="e" cm="1">
+        <f t="array" ref="V54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(D54,2-INT(LOG10(ABS(D54))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W54" s="7" t="e" cm="1">
+        <f t="array" ref="W54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(E54,2-INT(LOG10(ABS(E54))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X54" s="7" t="e" cm="1">
+        <f t="array" ref="X54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(F54,2-INT(LOG10(ABS(F54))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y54" s="7" t="e" cm="1">
+        <f t="array" ref="Y54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(G54,2-INT(LOG10(ABS(G54))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z54" s="7" t="e" cm="1">
+        <f t="array" ref="Z54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(H54,2-INT(LOG10(ABS(H54))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA54" s="7" t="e" cm="1">
+        <f t="array" ref="AA54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(I54,2-INT(LOG10(ABS(I54))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB54" s="7" t="e" cm="1">
+        <f t="array" ref="AB54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(J54,2-INT(LOG10(ABS(J54))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC54" s="7" t="e" cm="1">
+        <f t="array" ref="AC54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(K54,2-INT(LOG10(ABS(K54))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD54" s="7" t="e" cm="1">
+        <f t="array" ref="AD54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(L54,2-INT(LOG10(ABS(L54))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE54" s="7" t="e" cm="1">
+        <f t="array" ref="AE54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(M54,2-INT(LOG10(ABS(M54))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF54" s="7" t="e" cm="1">
+        <f t="array" ref="AF54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(N54,2-INT(LOG10(ABS(N54))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG54" s="7" t="e" cm="1">
+        <f t="array" ref="AG54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(O54,2-INT(LOG10(ABS(O54))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH54" s="7" t="e" cm="1">
+        <f t="array" ref="AH54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(P54,2-INT(LOG10(ABS(P54))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI54" s="7" t="e" cm="1">
+        <f t="array" ref="AI54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(Q54,2-INT(LOG10(ABS(Q54))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ54" s="7" t="e" cm="1">
+        <f t="array" ref="AJ54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(R54,2-INT(LOG10(ABS(R54))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="55" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A55" s="21"/>
-      <c r="B55" s="9" t="s">
+      <c r="A55" s="24"/>
+      <c r="B55" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C55" s="20" t="s">
         <v>147</v>
       </c>
       <c r="D55" s="8"/>
@@ -5052,7 +5326,7 @@
       <c r="Q55" s="8"/>
       <c r="R55" s="8"/>
       <c r="S55" s="14"/>
-      <c r="T55" s="9" t="s">
+      <c r="T55" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V55" s="7"/>
@@ -5068,11 +5342,11 @@
       <c r="AF55" s="7"/>
     </row>
     <row r="56" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A56" s="21"/>
-      <c r="B56" s="5" t="s">
+      <c r="A56" s="24"/>
+      <c r="B56" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="21" t="s">
         <v>148</v>
       </c>
       <c r="D56" s="6"/>
@@ -5091,7 +5365,7 @@
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
       <c r="S56" s="4"/>
-      <c r="T56" s="5" t="s">
+      <c r="T56" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V56" s="7"/>
@@ -5107,11 +5381,11 @@
       <c r="AF56" s="7"/>
     </row>
     <row r="57" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A57" s="21"/>
-      <c r="B57" s="2" t="s">
+      <c r="A57" s="24"/>
+      <c r="B57" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="22" t="s">
         <v>149</v>
       </c>
       <c r="D57" s="3"/>
@@ -5132,76 +5406,76 @@
       <c r="S57" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T57" s="2" t="s">
+      <c r="T57" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V57" s="7" t="e">
-        <f t="shared" ref="V57:AJ57" si="19">_xlfn.RANK.EQ(D57,$D57:$R57,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W57" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X57" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y57" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z57" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA57" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB57" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC57" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD57" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE57" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF57" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG57" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH57" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI57" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ57" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#N/A</v>
+      <c r="V57" s="7" t="e" cm="1">
+        <f t="array" ref="V57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(D57,2-INT(LOG10(ABS(D57))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W57" s="7" t="e" cm="1">
+        <f t="array" ref="W57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(E57,2-INT(LOG10(ABS(E57))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X57" s="7" t="e" cm="1">
+        <f t="array" ref="X57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(F57,2-INT(LOG10(ABS(F57))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y57" s="7" t="e" cm="1">
+        <f t="array" ref="Y57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(G57,2-INT(LOG10(ABS(G57))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z57" s="7" t="e" cm="1">
+        <f t="array" ref="Z57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(H57,2-INT(LOG10(ABS(H57))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA57" s="7" t="e" cm="1">
+        <f t="array" ref="AA57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(I57,2-INT(LOG10(ABS(I57))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB57" s="7" t="e" cm="1">
+        <f t="array" ref="AB57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(J57,2-INT(LOG10(ABS(J57))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC57" s="7" t="e" cm="1">
+        <f t="array" ref="AC57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(K57,2-INT(LOG10(ABS(K57))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD57" s="7" t="e" cm="1">
+        <f t="array" ref="AD57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(L57,2-INT(LOG10(ABS(L57))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE57" s="7" t="e" cm="1">
+        <f t="array" ref="AE57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(M57,2-INT(LOG10(ABS(M57))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF57" s="7" t="e" cm="1">
+        <f t="array" ref="AF57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(N57,2-INT(LOG10(ABS(N57))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG57" s="7" t="e" cm="1">
+        <f t="array" ref="AG57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(O57,2-INT(LOG10(ABS(O57))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH57" s="7" t="e" cm="1">
+        <f t="array" ref="AH57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(P57,2-INT(LOG10(ABS(P57))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI57" s="7" t="e" cm="1">
+        <f t="array" ref="AI57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(Q57,2-INT(LOG10(ABS(Q57))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ57" s="7" t="e" cm="1">
+        <f t="array" ref="AJ57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(R57,2-INT(LOG10(ABS(R57))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="58" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A58" s="21"/>
-      <c r="B58" s="9" t="s">
+      <c r="A58" s="24"/>
+      <c r="B58" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C58" s="20" t="s">
         <v>150</v>
       </c>
       <c r="D58" s="8"/>
@@ -5220,7 +5494,7 @@
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
       <c r="S58" s="14"/>
-      <c r="T58" s="9" t="s">
+      <c r="T58" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V58" s="7"/>
@@ -5236,11 +5510,11 @@
       <c r="AF58" s="7"/>
     </row>
     <row r="59" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A59" s="21"/>
-      <c r="B59" s="5" t="s">
+      <c r="A59" s="24"/>
+      <c r="B59" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C59" s="21" t="s">
         <v>151</v>
       </c>
       <c r="D59" s="6"/>
@@ -5259,7 +5533,7 @@
       <c r="Q59" s="6"/>
       <c r="R59" s="6"/>
       <c r="S59" s="4"/>
-      <c r="T59" s="5" t="s">
+      <c r="T59" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V59" s="7"/>
@@ -5275,11 +5549,11 @@
       <c r="AF59" s="7"/>
     </row>
     <row r="60" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A60" s="21"/>
-      <c r="B60" s="2" t="s">
+      <c r="A60" s="24"/>
+      <c r="B60" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="22" t="s">
         <v>152</v>
       </c>
       <c r="D60" s="3"/>
@@ -5300,76 +5574,76 @@
       <c r="S60" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="T60" s="2" t="s">
+      <c r="T60" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V60" s="7" t="e">
-        <f t="shared" ref="V60:AJ60" si="20">_xlfn.RANK.EQ(D60,$D60:$R60,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W60" s="7" t="e">
-        <f t="shared" si="20"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X60" s="7" t="e">
-        <f t="shared" si="20"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y60" s="7" t="e">
-        <f t="shared" si="20"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z60" s="7" t="e">
-        <f t="shared" si="20"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA60" s="7" t="e">
-        <f t="shared" si="20"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB60" s="7" t="e">
-        <f t="shared" si="20"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC60" s="7" t="e">
-        <f t="shared" si="20"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD60" s="7" t="e">
-        <f t="shared" si="20"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE60" s="7" t="e">
-        <f t="shared" si="20"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF60" s="7" t="e">
-        <f t="shared" si="20"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG60" s="7" t="e">
-        <f t="shared" si="20"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH60" s="7" t="e">
-        <f t="shared" si="20"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI60" s="7" t="e">
-        <f t="shared" si="20"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ60" s="7" t="e">
-        <f t="shared" si="20"/>
-        <v>#N/A</v>
+      <c r="V60" s="7" t="e" cm="1">
+        <f t="array" ref="V60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(D60,2-INT(LOG10(ABS(D60))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W60" s="7" t="e" cm="1">
+        <f t="array" ref="W60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(E60,2-INT(LOG10(ABS(E60))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X60" s="7" t="e" cm="1">
+        <f t="array" ref="X60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(F60,2-INT(LOG10(ABS(F60))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y60" s="7" t="e" cm="1">
+        <f t="array" ref="Y60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(G60,2-INT(LOG10(ABS(G60))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z60" s="7" t="e" cm="1">
+        <f t="array" ref="Z60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(H60,2-INT(LOG10(ABS(H60))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA60" s="7" t="e" cm="1">
+        <f t="array" ref="AA60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(I60,2-INT(LOG10(ABS(I60))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB60" s="7" t="e" cm="1">
+        <f t="array" ref="AB60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(J60,2-INT(LOG10(ABS(J60))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC60" s="7" t="e" cm="1">
+        <f t="array" ref="AC60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(K60,2-INT(LOG10(ABS(K60))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD60" s="7" t="e" cm="1">
+        <f t="array" ref="AD60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(L60,2-INT(LOG10(ABS(L60))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE60" s="7" t="e" cm="1">
+        <f t="array" ref="AE60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(M60,2-INT(LOG10(ABS(M60))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF60" s="7" t="e" cm="1">
+        <f t="array" ref="AF60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(N60,2-INT(LOG10(ABS(N60))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG60" s="7" t="e" cm="1">
+        <f t="array" ref="AG60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(O60,2-INT(LOG10(ABS(O60))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH60" s="7" t="e" cm="1">
+        <f t="array" ref="AH60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(P60,2-INT(LOG10(ABS(P60))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI60" s="7" t="e" cm="1">
+        <f t="array" ref="AI60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(Q60,2-INT(LOG10(ABS(Q60))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ60" s="7" t="e" cm="1">
+        <f t="array" ref="AJ60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(R60,2-INT(LOG10(ABS(R60))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="61" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A61" s="21"/>
-      <c r="B61" s="9" t="s">
+      <c r="A61" s="24"/>
+      <c r="B61" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="C61" s="20" t="s">
         <v>153</v>
       </c>
       <c r="D61" s="8"/>
@@ -5388,7 +5662,7 @@
       <c r="Q61" s="8"/>
       <c r="R61" s="8"/>
       <c r="S61" s="14"/>
-      <c r="T61" s="9" t="s">
+      <c r="T61" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V61" s="7"/>
@@ -5404,11 +5678,11 @@
       <c r="AF61" s="7"/>
     </row>
     <row r="62" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A62" s="21"/>
-      <c r="B62" s="5" t="s">
+      <c r="A62" s="24"/>
+      <c r="B62" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="21" t="s">
         <v>154</v>
       </c>
       <c r="D62" s="6"/>
@@ -5427,7 +5701,7 @@
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
       <c r="S62" s="4"/>
-      <c r="T62" s="5" t="s">
+      <c r="T62" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V62" s="7"/>
@@ -5443,11 +5717,11 @@
       <c r="AF62" s="7"/>
     </row>
     <row r="63" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A63" s="21"/>
-      <c r="B63" s="2" t="s">
+      <c r="A63" s="24"/>
+      <c r="B63" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="22" t="s">
         <v>155</v>
       </c>
       <c r="D63" s="3"/>
@@ -5468,76 +5742,76 @@
       <c r="S63" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T63" s="2" t="s">
+      <c r="T63" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V63" s="7" t="e">
-        <f t="shared" ref="V63:AJ63" si="21">_xlfn.RANK.EQ(D63,$D63:$R63,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W63" s="7" t="e">
-        <f t="shared" si="21"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X63" s="7" t="e">
-        <f t="shared" si="21"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y63" s="7" t="e">
-        <f t="shared" si="21"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z63" s="7" t="e">
-        <f t="shared" si="21"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA63" s="7" t="e">
-        <f t="shared" si="21"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB63" s="7" t="e">
-        <f t="shared" si="21"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC63" s="7" t="e">
-        <f t="shared" si="21"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD63" s="7" t="e">
-        <f t="shared" si="21"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE63" s="7" t="e">
-        <f t="shared" si="21"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF63" s="7" t="e">
-        <f t="shared" si="21"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG63" s="7" t="e">
-        <f t="shared" si="21"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH63" s="7" t="e">
-        <f t="shared" si="21"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI63" s="7" t="e">
-        <f t="shared" si="21"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ63" s="7" t="e">
-        <f t="shared" si="21"/>
-        <v>#N/A</v>
+      <c r="V63" s="7" t="e" cm="1">
+        <f t="array" ref="V63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(D63,2-INT(LOG10(ABS(D63))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W63" s="7" t="e" cm="1">
+        <f t="array" ref="W63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(E63,2-INT(LOG10(ABS(E63))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X63" s="7" t="e" cm="1">
+        <f t="array" ref="X63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(F63,2-INT(LOG10(ABS(F63))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y63" s="7" t="e" cm="1">
+        <f t="array" ref="Y63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(G63,2-INT(LOG10(ABS(G63))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z63" s="7" t="e" cm="1">
+        <f t="array" ref="Z63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(H63,2-INT(LOG10(ABS(H63))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA63" s="7" t="e" cm="1">
+        <f t="array" ref="AA63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(I63,2-INT(LOG10(ABS(I63))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB63" s="7" t="e" cm="1">
+        <f t="array" ref="AB63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(J63,2-INT(LOG10(ABS(J63))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC63" s="7" t="e" cm="1">
+        <f t="array" ref="AC63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(K63,2-INT(LOG10(ABS(K63))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD63" s="7" t="e" cm="1">
+        <f t="array" ref="AD63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(L63,2-INT(LOG10(ABS(L63))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE63" s="7" t="e" cm="1">
+        <f t="array" ref="AE63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(M63,2-INT(LOG10(ABS(M63))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF63" s="7" t="e" cm="1">
+        <f t="array" ref="AF63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(N63,2-INT(LOG10(ABS(N63))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG63" s="7" t="e" cm="1">
+        <f t="array" ref="AG63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(O63,2-INT(LOG10(ABS(O63))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH63" s="7" t="e" cm="1">
+        <f t="array" ref="AH63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(P63,2-INT(LOG10(ABS(P63))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI63" s="7" t="e" cm="1">
+        <f t="array" ref="AI63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(Q63,2-INT(LOG10(ABS(Q63))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ63" s="7" t="e" cm="1">
+        <f t="array" ref="AJ63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(R63,2-INT(LOG10(ABS(R63))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="64" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A64" s="21"/>
-      <c r="B64" s="9" t="s">
+      <c r="A64" s="24"/>
+      <c r="B64" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="C64" s="9" t="s">
+      <c r="C64" s="20" t="s">
         <v>156</v>
       </c>
       <c r="D64" s="8"/>
@@ -5556,7 +5830,7 @@
       <c r="Q64" s="8"/>
       <c r="R64" s="8"/>
       <c r="S64" s="14"/>
-      <c r="T64" s="9" t="s">
+      <c r="T64" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V64" s="7"/>
@@ -5572,11 +5846,11 @@
       <c r="AF64" s="7"/>
     </row>
     <row r="65" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A65" s="21"/>
-      <c r="B65" s="5" t="s">
+      <c r="A65" s="24"/>
+      <c r="B65" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="C65" s="21" t="s">
         <v>157</v>
       </c>
       <c r="D65" s="6"/>
@@ -5595,7 +5869,7 @@
       <c r="Q65" s="6"/>
       <c r="R65" s="6"/>
       <c r="S65" s="4"/>
-      <c r="T65" s="5" t="s">
+      <c r="T65" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V65" s="7"/>
@@ -5611,11 +5885,11 @@
       <c r="AF65" s="7"/>
     </row>
     <row r="66" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A66" s="21"/>
-      <c r="B66" s="2" t="s">
+      <c r="A66" s="24"/>
+      <c r="B66" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="22" t="s">
         <v>158</v>
       </c>
       <c r="D66" s="3"/>
@@ -5636,76 +5910,76 @@
       <c r="S66" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="T66" s="2" t="s">
+      <c r="T66" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V66" s="7" t="e">
-        <f t="shared" ref="V66:AJ66" si="22">_xlfn.RANK.EQ(D66,$D66:$R66,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W66" s="7" t="e">
-        <f t="shared" si="22"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X66" s="7" t="e">
-        <f t="shared" si="22"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y66" s="7" t="e">
-        <f t="shared" si="22"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z66" s="7" t="e">
-        <f t="shared" si="22"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA66" s="7" t="e">
-        <f t="shared" si="22"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB66" s="7" t="e">
-        <f t="shared" si="22"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC66" s="7" t="e">
-        <f t="shared" si="22"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD66" s="7" t="e">
-        <f t="shared" si="22"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE66" s="7" t="e">
-        <f t="shared" si="22"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF66" s="7" t="e">
-        <f t="shared" si="22"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG66" s="7" t="e">
-        <f t="shared" si="22"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH66" s="7" t="e">
-        <f t="shared" si="22"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI66" s="7" t="e">
-        <f t="shared" si="22"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ66" s="7" t="e">
-        <f t="shared" si="22"/>
-        <v>#N/A</v>
+      <c r="V66" s="7" t="e" cm="1">
+        <f t="array" ref="V66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(D66,2-INT(LOG10(ABS(D66))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W66" s="7" t="e" cm="1">
+        <f t="array" ref="W66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(E66,2-INT(LOG10(ABS(E66))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X66" s="7" t="e" cm="1">
+        <f t="array" ref="X66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(F66,2-INT(LOG10(ABS(F66))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y66" s="7" t="e" cm="1">
+        <f t="array" ref="Y66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(G66,2-INT(LOG10(ABS(G66))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z66" s="7" t="e" cm="1">
+        <f t="array" ref="Z66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(H66,2-INT(LOG10(ABS(H66))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA66" s="7" t="e" cm="1">
+        <f t="array" ref="AA66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(I66,2-INT(LOG10(ABS(I66))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB66" s="7" t="e" cm="1">
+        <f t="array" ref="AB66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(J66,2-INT(LOG10(ABS(J66))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC66" s="7" t="e" cm="1">
+        <f t="array" ref="AC66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(K66,2-INT(LOG10(ABS(K66))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD66" s="7" t="e" cm="1">
+        <f t="array" ref="AD66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(L66,2-INT(LOG10(ABS(L66))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE66" s="7" t="e" cm="1">
+        <f t="array" ref="AE66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(M66,2-INT(LOG10(ABS(M66))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF66" s="7" t="e" cm="1">
+        <f t="array" ref="AF66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(N66,2-INT(LOG10(ABS(N66))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG66" s="7" t="e" cm="1">
+        <f t="array" ref="AG66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(O66,2-INT(LOG10(ABS(O66))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH66" s="7" t="e" cm="1">
+        <f t="array" ref="AH66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(P66,2-INT(LOG10(ABS(P66))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI66" s="7" t="e" cm="1">
+        <f t="array" ref="AI66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(Q66,2-INT(LOG10(ABS(Q66))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ66" s="7" t="e" cm="1">
+        <f t="array" ref="AJ66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(R66,2-INT(LOG10(ABS(R66))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="67" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A67" s="21"/>
-      <c r="B67" s="9" t="s">
+      <c r="A67" s="24"/>
+      <c r="B67" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="C67" s="20" t="s">
         <v>159</v>
       </c>
       <c r="D67" s="8"/>
@@ -5724,7 +5998,7 @@
       <c r="Q67" s="8"/>
       <c r="R67" s="8"/>
       <c r="S67" s="14"/>
-      <c r="T67" s="9" t="s">
+      <c r="T67" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V67" s="7"/>
@@ -5740,11 +6014,11 @@
       <c r="AF67" s="7"/>
     </row>
     <row r="68" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A68" s="24"/>
-      <c r="B68" s="5" t="s">
+      <c r="A68" s="27"/>
+      <c r="B68" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="C68" s="21" t="s">
         <v>160</v>
       </c>
       <c r="D68" s="6"/>
@@ -5763,7 +6037,7 @@
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
       <c r="S68" s="4"/>
-      <c r="T68" s="5" t="s">
+      <c r="T68" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V68" s="7"/>
@@ -5779,13 +6053,13 @@
       <c r="AF68" s="7"/>
     </row>
     <row r="69" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="26" t="s">
+      <c r="A69" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="22" t="s">
         <v>161</v>
       </c>
       <c r="D69" s="3"/>
@@ -5806,76 +6080,76 @@
       <c r="S69" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="T69" s="2" t="s">
+      <c r="T69" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V69" s="7" t="e">
-        <f t="shared" ref="V69:AJ69" si="23">_xlfn.RANK.EQ(D69,$D69:$R69,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W69" s="7" t="e">
-        <f t="shared" si="23"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X69" s="7" t="e">
-        <f t="shared" si="23"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y69" s="7" t="e">
-        <f t="shared" si="23"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z69" s="7" t="e">
-        <f t="shared" si="23"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA69" s="7" t="e">
-        <f t="shared" si="23"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB69" s="7" t="e">
-        <f t="shared" si="23"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC69" s="7" t="e">
-        <f t="shared" si="23"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD69" s="7" t="e">
-        <f t="shared" si="23"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE69" s="7" t="e">
-        <f t="shared" si="23"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF69" s="7" t="e">
-        <f t="shared" si="23"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG69" s="7" t="e">
-        <f t="shared" si="23"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH69" s="7" t="e">
-        <f t="shared" si="23"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI69" s="7" t="e">
-        <f t="shared" si="23"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ69" s="7" t="e">
-        <f t="shared" si="23"/>
-        <v>#N/A</v>
+      <c r="V69" s="7" t="e" cm="1">
+        <f t="array" ref="V69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(D69,2-INT(LOG10(ABS(D69))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W69" s="7" t="e" cm="1">
+        <f t="array" ref="W69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(E69,2-INT(LOG10(ABS(E69))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X69" s="7" t="e" cm="1">
+        <f t="array" ref="X69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(F69,2-INT(LOG10(ABS(F69))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y69" s="7" t="e" cm="1">
+        <f t="array" ref="Y69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(G69,2-INT(LOG10(ABS(G69))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z69" s="7" t="e" cm="1">
+        <f t="array" ref="Z69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(H69,2-INT(LOG10(ABS(H69))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA69" s="7" t="e" cm="1">
+        <f t="array" ref="AA69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(I69,2-INT(LOG10(ABS(I69))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB69" s="7" t="e" cm="1">
+        <f t="array" ref="AB69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(J69,2-INT(LOG10(ABS(J69))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC69" s="7" t="e" cm="1">
+        <f t="array" ref="AC69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(K69,2-INT(LOG10(ABS(K69))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD69" s="7" t="e" cm="1">
+        <f t="array" ref="AD69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(L69,2-INT(LOG10(ABS(L69))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE69" s="7" t="e" cm="1">
+        <f t="array" ref="AE69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(M69,2-INT(LOG10(ABS(M69))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF69" s="7" t="e" cm="1">
+        <f t="array" ref="AF69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(N69,2-INT(LOG10(ABS(N69))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG69" s="7" t="e" cm="1">
+        <f t="array" ref="AG69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(O69,2-INT(LOG10(ABS(O69))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH69" s="7" t="e" cm="1">
+        <f t="array" ref="AH69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(P69,2-INT(LOG10(ABS(P69))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI69" s="7" t="e" cm="1">
+        <f t="array" ref="AI69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(Q69,2-INT(LOG10(ABS(Q69))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ69" s="7" t="e" cm="1">
+        <f t="array" ref="AJ69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(R69,2-INT(LOG10(ABS(R69))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="70" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A70" s="21"/>
-      <c r="B70" s="9" t="s">
+      <c r="A70" s="24"/>
+      <c r="B70" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="C70" s="9" t="s">
+      <c r="C70" s="20" t="s">
         <v>162</v>
       </c>
       <c r="D70" s="8"/>
@@ -5894,7 +6168,7 @@
       <c r="Q70" s="8"/>
       <c r="R70" s="8"/>
       <c r="S70" s="14"/>
-      <c r="T70" s="9" t="s">
+      <c r="T70" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V70" s="7"/>
@@ -5910,11 +6184,11 @@
       <c r="AF70" s="7"/>
     </row>
     <row r="71" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A71" s="21"/>
-      <c r="B71" s="5" t="s">
+      <c r="A71" s="24"/>
+      <c r="B71" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C71" s="21" t="s">
         <v>163</v>
       </c>
       <c r="D71" s="6"/>
@@ -5933,7 +6207,7 @@
       <c r="Q71" s="6"/>
       <c r="R71" s="6"/>
       <c r="S71" s="4"/>
-      <c r="T71" s="5" t="s">
+      <c r="T71" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V71" s="7"/>
@@ -5949,11 +6223,11 @@
       <c r="AF71" s="7"/>
     </row>
     <row r="72" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A72" s="21"/>
-      <c r="B72" s="2" t="s">
+      <c r="A72" s="24"/>
+      <c r="B72" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="22" t="s">
         <v>164</v>
       </c>
       <c r="D72" s="3"/>
@@ -5974,76 +6248,76 @@
       <c r="S72" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T72" s="2" t="s">
+      <c r="T72" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V72" s="7" t="e">
-        <f t="shared" ref="V72:AJ72" si="24">_xlfn.RANK.EQ(D72,$D72:$R72,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W72" s="7" t="e">
-        <f t="shared" si="24"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X72" s="7" t="e">
-        <f t="shared" si="24"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y72" s="7" t="e">
-        <f t="shared" si="24"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z72" s="7" t="e">
-        <f t="shared" si="24"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA72" s="7" t="e">
-        <f t="shared" si="24"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB72" s="7" t="e">
-        <f t="shared" si="24"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC72" s="7" t="e">
-        <f t="shared" si="24"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD72" s="7" t="e">
-        <f t="shared" si="24"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE72" s="7" t="e">
-        <f t="shared" si="24"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF72" s="7" t="e">
-        <f t="shared" si="24"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG72" s="7" t="e">
-        <f t="shared" si="24"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH72" s="7" t="e">
-        <f t="shared" si="24"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI72" s="7" t="e">
-        <f t="shared" si="24"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ72" s="7" t="e">
-        <f t="shared" si="24"/>
-        <v>#N/A</v>
+      <c r="V72" s="7" t="e" cm="1">
+        <f t="array" ref="V72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(D72,2-INT(LOG10(ABS(D72))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W72" s="7" t="e" cm="1">
+        <f t="array" ref="W72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(E72,2-INT(LOG10(ABS(E72))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X72" s="7" t="e" cm="1">
+        <f t="array" ref="X72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(F72,2-INT(LOG10(ABS(F72))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y72" s="7" t="e" cm="1">
+        <f t="array" ref="Y72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(G72,2-INT(LOG10(ABS(G72))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z72" s="7" t="e" cm="1">
+        <f t="array" ref="Z72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(H72,2-INT(LOG10(ABS(H72))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA72" s="7" t="e" cm="1">
+        <f t="array" ref="AA72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(I72,2-INT(LOG10(ABS(I72))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB72" s="7" t="e" cm="1">
+        <f t="array" ref="AB72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(J72,2-INT(LOG10(ABS(J72))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC72" s="7" t="e" cm="1">
+        <f t="array" ref="AC72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(K72,2-INT(LOG10(ABS(K72))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD72" s="7" t="e" cm="1">
+        <f t="array" ref="AD72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(L72,2-INT(LOG10(ABS(L72))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE72" s="7" t="e" cm="1">
+        <f t="array" ref="AE72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(M72,2-INT(LOG10(ABS(M72))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF72" s="7" t="e" cm="1">
+        <f t="array" ref="AF72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(N72,2-INT(LOG10(ABS(N72))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG72" s="7" t="e" cm="1">
+        <f t="array" ref="AG72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(O72,2-INT(LOG10(ABS(O72))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH72" s="7" t="e" cm="1">
+        <f t="array" ref="AH72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(P72,2-INT(LOG10(ABS(P72))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI72" s="7" t="e" cm="1">
+        <f t="array" ref="AI72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(Q72,2-INT(LOG10(ABS(Q72))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ72" s="7" t="e" cm="1">
+        <f t="array" ref="AJ72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(R72,2-INT(LOG10(ABS(R72))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="73" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A73" s="21"/>
-      <c r="B73" s="9" t="s">
+      <c r="A73" s="24"/>
+      <c r="B73" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="C73" s="9" t="s">
+      <c r="C73" s="20" t="s">
         <v>165</v>
       </c>
       <c r="D73" s="8"/>
@@ -6062,7 +6336,7 @@
       <c r="Q73" s="8"/>
       <c r="R73" s="8"/>
       <c r="S73" s="14"/>
-      <c r="T73" s="9" t="s">
+      <c r="T73" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V73" s="7"/>
@@ -6078,11 +6352,11 @@
       <c r="AF73" s="7"/>
     </row>
     <row r="74" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A74" s="21"/>
-      <c r="B74" s="5" t="s">
+      <c r="A74" s="24"/>
+      <c r="B74" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="21" t="s">
         <v>166</v>
       </c>
       <c r="D74" s="6"/>
@@ -6101,7 +6375,7 @@
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
       <c r="S74" s="4"/>
-      <c r="T74" s="5" t="s">
+      <c r="T74" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V74" s="7"/>
@@ -6117,11 +6391,11 @@
       <c r="AF74" s="7"/>
     </row>
     <row r="75" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A75" s="21"/>
-      <c r="B75" s="2" t="s">
+      <c r="A75" s="24"/>
+      <c r="B75" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="22" t="s">
         <v>167</v>
       </c>
       <c r="D75" s="3"/>
@@ -6142,76 +6416,76 @@
       <c r="S75" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="T75" s="2" t="s">
+      <c r="T75" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V75" s="7" t="e">
-        <f t="shared" ref="V75:AJ75" si="25">_xlfn.RANK.EQ(D75,$D75:$R75,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W75" s="7" t="e">
-        <f t="shared" si="25"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X75" s="7" t="e">
-        <f t="shared" si="25"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y75" s="7" t="e">
-        <f t="shared" si="25"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z75" s="7" t="e">
-        <f t="shared" si="25"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA75" s="7" t="e">
-        <f t="shared" si="25"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB75" s="7" t="e">
-        <f t="shared" si="25"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC75" s="7" t="e">
-        <f t="shared" si="25"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD75" s="7" t="e">
-        <f t="shared" si="25"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE75" s="7" t="e">
-        <f t="shared" si="25"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF75" s="7" t="e">
-        <f t="shared" si="25"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG75" s="7" t="e">
-        <f t="shared" si="25"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH75" s="7" t="e">
-        <f t="shared" si="25"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI75" s="7" t="e">
-        <f t="shared" si="25"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ75" s="7" t="e">
-        <f t="shared" si="25"/>
-        <v>#N/A</v>
+      <c r="V75" s="7" t="e" cm="1">
+        <f t="array" ref="V75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(D75,2-INT(LOG10(ABS(D75))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W75" s="7" t="e" cm="1">
+        <f t="array" ref="W75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(E75,2-INT(LOG10(ABS(E75))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X75" s="7" t="e" cm="1">
+        <f t="array" ref="X75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(F75,2-INT(LOG10(ABS(F75))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y75" s="7" t="e" cm="1">
+        <f t="array" ref="Y75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(G75,2-INT(LOG10(ABS(G75))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z75" s="7" t="e" cm="1">
+        <f t="array" ref="Z75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(H75,2-INT(LOG10(ABS(H75))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA75" s="7" t="e" cm="1">
+        <f t="array" ref="AA75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(I75,2-INT(LOG10(ABS(I75))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB75" s="7" t="e" cm="1">
+        <f t="array" ref="AB75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(J75,2-INT(LOG10(ABS(J75))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC75" s="7" t="e" cm="1">
+        <f t="array" ref="AC75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(K75,2-INT(LOG10(ABS(K75))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD75" s="7" t="e" cm="1">
+        <f t="array" ref="AD75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(L75,2-INT(LOG10(ABS(L75))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE75" s="7" t="e" cm="1">
+        <f t="array" ref="AE75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(M75,2-INT(LOG10(ABS(M75))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF75" s="7" t="e" cm="1">
+        <f t="array" ref="AF75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(N75,2-INT(LOG10(ABS(N75))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG75" s="7" t="e" cm="1">
+        <f t="array" ref="AG75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(O75,2-INT(LOG10(ABS(O75))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH75" s="7" t="e" cm="1">
+        <f t="array" ref="AH75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(P75,2-INT(LOG10(ABS(P75))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI75" s="7" t="e" cm="1">
+        <f t="array" ref="AI75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(Q75,2-INT(LOG10(ABS(Q75))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ75" s="7" t="e" cm="1">
+        <f t="array" ref="AJ75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(R75,2-INT(LOG10(ABS(R75))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="76" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A76" s="21"/>
-      <c r="B76" s="9" t="s">
+      <c r="A76" s="24"/>
+      <c r="B76" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C76" s="20" t="s">
         <v>168</v>
       </c>
       <c r="D76" s="8"/>
@@ -6230,7 +6504,7 @@
       <c r="Q76" s="8"/>
       <c r="R76" s="8"/>
       <c r="S76" s="14"/>
-      <c r="T76" s="9" t="s">
+      <c r="T76" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V76" s="7"/>
@@ -6246,11 +6520,11 @@
       <c r="AF76" s="7"/>
     </row>
     <row r="77" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A77" s="21"/>
-      <c r="B77" s="5" t="s">
+      <c r="A77" s="24"/>
+      <c r="B77" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="C77" s="21" t="s">
         <v>169</v>
       </c>
       <c r="D77" s="6"/>
@@ -6269,7 +6543,7 @@
       <c r="Q77" s="6"/>
       <c r="R77" s="6"/>
       <c r="S77" s="4"/>
-      <c r="T77" s="5" t="s">
+      <c r="T77" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V77" s="7"/>
@@ -6285,11 +6559,11 @@
       <c r="AF77" s="7"/>
     </row>
     <row r="78" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A78" s="21"/>
-      <c r="B78" s="2" t="s">
+      <c r="A78" s="24"/>
+      <c r="B78" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="22" t="s">
         <v>170</v>
       </c>
       <c r="D78" s="3"/>
@@ -6310,76 +6584,76 @@
       <c r="S78" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="T78" s="2" t="s">
+      <c r="T78" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V78" s="7" t="e">
-        <f t="shared" ref="V78:AJ78" si="26">_xlfn.RANK.EQ(D78,$D78:$R78,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W78" s="7" t="e">
-        <f t="shared" si="26"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X78" s="7" t="e">
-        <f t="shared" si="26"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y78" s="7" t="e">
-        <f t="shared" si="26"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z78" s="7" t="e">
-        <f t="shared" si="26"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA78" s="7" t="e">
-        <f t="shared" si="26"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB78" s="7" t="e">
-        <f t="shared" si="26"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC78" s="7" t="e">
-        <f t="shared" si="26"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD78" s="7" t="e">
-        <f t="shared" si="26"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE78" s="7" t="e">
-        <f t="shared" si="26"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF78" s="7" t="e">
-        <f t="shared" si="26"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG78" s="7" t="e">
-        <f t="shared" si="26"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH78" s="7" t="e">
-        <f t="shared" si="26"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI78" s="7" t="e">
-        <f t="shared" si="26"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ78" s="7" t="e">
-        <f t="shared" si="26"/>
-        <v>#N/A</v>
+      <c r="V78" s="7" t="e" cm="1">
+        <f t="array" ref="V78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(D78,2-INT(LOG10(ABS(D78))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W78" s="7" t="e" cm="1">
+        <f t="array" ref="W78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(E78,2-INT(LOG10(ABS(E78))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X78" s="7" t="e" cm="1">
+        <f t="array" ref="X78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(F78,2-INT(LOG10(ABS(F78))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y78" s="7" t="e" cm="1">
+        <f t="array" ref="Y78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(G78,2-INT(LOG10(ABS(G78))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z78" s="7" t="e" cm="1">
+        <f t="array" ref="Z78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(H78,2-INT(LOG10(ABS(H78))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA78" s="7" t="e" cm="1">
+        <f t="array" ref="AA78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(I78,2-INT(LOG10(ABS(I78))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB78" s="7" t="e" cm="1">
+        <f t="array" ref="AB78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(J78,2-INT(LOG10(ABS(J78))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC78" s="7" t="e" cm="1">
+        <f t="array" ref="AC78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(K78,2-INT(LOG10(ABS(K78))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD78" s="7" t="e" cm="1">
+        <f t="array" ref="AD78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(L78,2-INT(LOG10(ABS(L78))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE78" s="7" t="e" cm="1">
+        <f t="array" ref="AE78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(M78,2-INT(LOG10(ABS(M78))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF78" s="7" t="e" cm="1">
+        <f t="array" ref="AF78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(N78,2-INT(LOG10(ABS(N78))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG78" s="7" t="e" cm="1">
+        <f t="array" ref="AG78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(O78,2-INT(LOG10(ABS(O78))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH78" s="7" t="e" cm="1">
+        <f t="array" ref="AH78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(P78,2-INT(LOG10(ABS(P78))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI78" s="7" t="e" cm="1">
+        <f t="array" ref="AI78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(Q78,2-INT(LOG10(ABS(Q78))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ78" s="7" t="e" cm="1">
+        <f t="array" ref="AJ78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(R78,2-INT(LOG10(ABS(R78))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="79" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A79" s="21"/>
-      <c r="B79" s="9" t="s">
+      <c r="A79" s="24"/>
+      <c r="B79" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="C79" s="9" t="s">
+      <c r="C79" s="20" t="s">
         <v>171</v>
       </c>
       <c r="D79" s="8"/>
@@ -6398,7 +6672,7 @@
       <c r="Q79" s="8"/>
       <c r="R79" s="8"/>
       <c r="S79" s="14"/>
-      <c r="T79" s="9" t="s">
+      <c r="T79" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V79" s="7"/>
@@ -6414,11 +6688,11 @@
       <c r="AF79" s="7"/>
     </row>
     <row r="80" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A80" s="21"/>
-      <c r="B80" s="5" t="s">
+      <c r="A80" s="24"/>
+      <c r="B80" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="C80" s="21" t="s">
         <v>172</v>
       </c>
       <c r="D80" s="6"/>
@@ -6437,7 +6711,7 @@
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
       <c r="S80" s="4"/>
-      <c r="T80" s="5" t="s">
+      <c r="T80" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V80" s="7"/>
@@ -6453,11 +6727,11 @@
       <c r="AF80" s="7"/>
     </row>
     <row r="81" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A81" s="21"/>
-      <c r="B81" s="2" t="s">
+      <c r="A81" s="24"/>
+      <c r="B81" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="22" t="s">
         <v>173</v>
       </c>
       <c r="D81" s="3"/>
@@ -6478,76 +6752,76 @@
       <c r="S81" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="T81" s="2" t="s">
+      <c r="T81" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V81" s="7" t="e">
-        <f t="shared" ref="V81:AJ81" si="27">_xlfn.RANK.EQ(D81,$D81:$R81,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W81" s="7" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X81" s="7" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y81" s="7" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z81" s="7" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA81" s="7" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB81" s="7" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC81" s="7" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD81" s="7" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE81" s="7" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF81" s="7" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG81" s="7" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH81" s="7" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI81" s="7" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ81" s="7" t="e">
-        <f t="shared" si="27"/>
-        <v>#N/A</v>
+      <c r="V81" s="7" t="e" cm="1">
+        <f t="array" ref="V81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(D81,2-INT(LOG10(ABS(D81))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W81" s="7" t="e" cm="1">
+        <f t="array" ref="W81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(E81,2-INT(LOG10(ABS(E81))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X81" s="7" t="e" cm="1">
+        <f t="array" ref="X81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(F81,2-INT(LOG10(ABS(F81))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y81" s="7" t="e" cm="1">
+        <f t="array" ref="Y81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(G81,2-INT(LOG10(ABS(G81))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z81" s="7" t="e" cm="1">
+        <f t="array" ref="Z81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(H81,2-INT(LOG10(ABS(H81))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA81" s="7" t="e" cm="1">
+        <f t="array" ref="AA81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(I81,2-INT(LOG10(ABS(I81))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB81" s="7" t="e" cm="1">
+        <f t="array" ref="AB81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(J81,2-INT(LOG10(ABS(J81))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC81" s="7" t="e" cm="1">
+        <f t="array" ref="AC81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(K81,2-INT(LOG10(ABS(K81))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD81" s="7" t="e" cm="1">
+        <f t="array" ref="AD81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(L81,2-INT(LOG10(ABS(L81))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE81" s="7" t="e" cm="1">
+        <f t="array" ref="AE81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(M81,2-INT(LOG10(ABS(M81))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF81" s="7" t="e" cm="1">
+        <f t="array" ref="AF81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(N81,2-INT(LOG10(ABS(N81))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG81" s="7" t="e" cm="1">
+        <f t="array" ref="AG81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(O81,2-INT(LOG10(ABS(O81))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH81" s="7" t="e" cm="1">
+        <f t="array" ref="AH81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(P81,2-INT(LOG10(ABS(P81))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI81" s="7" t="e" cm="1">
+        <f t="array" ref="AI81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(Q81,2-INT(LOG10(ABS(Q81))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ81" s="7" t="e" cm="1">
+        <f t="array" ref="AJ81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(R81,2-INT(LOG10(ABS(R81))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="82" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A82" s="21"/>
-      <c r="B82" s="9" t="s">
+      <c r="A82" s="24"/>
+      <c r="B82" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="C82" s="9" t="s">
+      <c r="C82" s="20" t="s">
         <v>174</v>
       </c>
       <c r="D82" s="8"/>
@@ -6566,7 +6840,7 @@
       <c r="Q82" s="8"/>
       <c r="R82" s="8"/>
       <c r="S82" s="14"/>
-      <c r="T82" s="9" t="s">
+      <c r="T82" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V82" s="7"/>
@@ -6582,11 +6856,11 @@
       <c r="AF82" s="7"/>
     </row>
     <row r="83" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A83" s="21"/>
-      <c r="B83" s="5" t="s">
+      <c r="A83" s="24"/>
+      <c r="B83" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="C83" s="5" t="s">
+      <c r="C83" s="21" t="s">
         <v>175</v>
       </c>
       <c r="D83" s="6"/>
@@ -6605,7 +6879,7 @@
       <c r="Q83" s="6"/>
       <c r="R83" s="6"/>
       <c r="S83" s="4"/>
-      <c r="T83" s="5" t="s">
+      <c r="T83" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V83" s="7"/>
@@ -6621,11 +6895,11 @@
       <c r="AF83" s="7"/>
     </row>
     <row r="84" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A84" s="21"/>
-      <c r="B84" s="2" t="s">
+      <c r="A84" s="24"/>
+      <c r="B84" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="22" t="s">
         <v>176</v>
       </c>
       <c r="D84" s="3"/>
@@ -6646,76 +6920,76 @@
       <c r="S84" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="T84" s="2" t="s">
+      <c r="T84" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V84" s="7" t="e">
-        <f t="shared" ref="V84:AJ84" si="28">_xlfn.RANK.EQ(D84,$D84:$R84,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W84" s="7" t="e">
-        <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X84" s="7" t="e">
-        <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y84" s="7" t="e">
-        <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z84" s="7" t="e">
-        <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA84" s="7" t="e">
-        <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB84" s="7" t="e">
-        <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC84" s="7" t="e">
-        <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD84" s="7" t="e">
-        <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE84" s="7" t="e">
-        <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF84" s="7" t="e">
-        <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG84" s="7" t="e">
-        <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH84" s="7" t="e">
-        <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI84" s="7" t="e">
-        <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ84" s="7" t="e">
-        <f t="shared" si="28"/>
-        <v>#N/A</v>
+      <c r="V84" s="7" t="e" cm="1">
+        <f t="array" ref="V84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(D84,2-INT(LOG10(ABS(D84))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W84" s="7" t="e" cm="1">
+        <f t="array" ref="W84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(E84,2-INT(LOG10(ABS(E84))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X84" s="7" t="e" cm="1">
+        <f t="array" ref="X84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(F84,2-INT(LOG10(ABS(F84))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y84" s="7" t="e" cm="1">
+        <f t="array" ref="Y84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(G84,2-INT(LOG10(ABS(G84))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z84" s="7" t="e" cm="1">
+        <f t="array" ref="Z84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(H84,2-INT(LOG10(ABS(H84))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA84" s="7" t="e" cm="1">
+        <f t="array" ref="AA84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(I84,2-INT(LOG10(ABS(I84))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB84" s="7" t="e" cm="1">
+        <f t="array" ref="AB84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(J84,2-INT(LOG10(ABS(J84))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC84" s="7" t="e" cm="1">
+        <f t="array" ref="AC84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(K84,2-INT(LOG10(ABS(K84))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD84" s="7" t="e" cm="1">
+        <f t="array" ref="AD84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(L84,2-INT(LOG10(ABS(L84))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE84" s="7" t="e" cm="1">
+        <f t="array" ref="AE84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(M84,2-INT(LOG10(ABS(M84))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF84" s="7" t="e" cm="1">
+        <f t="array" ref="AF84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(N84,2-INT(LOG10(ABS(N84))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG84" s="7" t="e" cm="1">
+        <f t="array" ref="AG84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(O84,2-INT(LOG10(ABS(O84))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH84" s="7" t="e" cm="1">
+        <f t="array" ref="AH84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(P84,2-INT(LOG10(ABS(P84))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI84" s="7" t="e" cm="1">
+        <f t="array" ref="AI84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(Q84,2-INT(LOG10(ABS(Q84))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ84" s="7" t="e" cm="1">
+        <f t="array" ref="AJ84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(R84,2-INT(LOG10(ABS(R84))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="85" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A85" s="21"/>
-      <c r="B85" s="9" t="s">
+      <c r="A85" s="24"/>
+      <c r="B85" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="C85" s="9" t="s">
+      <c r="C85" s="20" t="s">
         <v>177</v>
       </c>
       <c r="D85" s="8"/>
@@ -6734,7 +7008,7 @@
       <c r="Q85" s="8"/>
       <c r="R85" s="8"/>
       <c r="S85" s="14"/>
-      <c r="T85" s="9" t="s">
+      <c r="T85" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V85" s="7"/>
@@ -6750,11 +7024,11 @@
       <c r="AF85" s="7"/>
     </row>
     <row r="86" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A86" s="21"/>
-      <c r="B86" s="5" t="s">
+      <c r="A86" s="24"/>
+      <c r="B86" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="C86" s="5" t="s">
+      <c r="C86" s="21" t="s">
         <v>178</v>
       </c>
       <c r="D86" s="6"/>
@@ -6773,7 +7047,7 @@
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
       <c r="S86" s="4"/>
-      <c r="T86" s="5" t="s">
+      <c r="T86" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V86" s="7"/>
@@ -6789,11 +7063,11 @@
       <c r="AF86" s="7"/>
     </row>
     <row r="87" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A87" s="21"/>
-      <c r="B87" s="2" t="s">
+      <c r="A87" s="24"/>
+      <c r="B87" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="22" t="s">
         <v>179</v>
       </c>
       <c r="D87" s="3"/>
@@ -6814,76 +7088,76 @@
       <c r="S87" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T87" s="2" t="s">
+      <c r="T87" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V87" s="7" t="e">
-        <f t="shared" ref="V87:AJ87" si="29">_xlfn.RANK.EQ(D87,$D87:$R87,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W87" s="7" t="e">
-        <f t="shared" si="29"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X87" s="7" t="e">
-        <f t="shared" si="29"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y87" s="7" t="e">
-        <f t="shared" si="29"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z87" s="7" t="e">
-        <f t="shared" si="29"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA87" s="7" t="e">
-        <f t="shared" si="29"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB87" s="7" t="e">
-        <f t="shared" si="29"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC87" s="7" t="e">
-        <f t="shared" si="29"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD87" s="7" t="e">
-        <f t="shared" si="29"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE87" s="7" t="e">
-        <f t="shared" si="29"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF87" s="7" t="e">
-        <f t="shared" si="29"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG87" s="7" t="e">
-        <f t="shared" si="29"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH87" s="7" t="e">
-        <f t="shared" si="29"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI87" s="7" t="e">
-        <f t="shared" si="29"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ87" s="7" t="e">
-        <f t="shared" si="29"/>
-        <v>#N/A</v>
+      <c r="V87" s="7" t="e" cm="1">
+        <f t="array" ref="V87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(D87,2-INT(LOG10(ABS(D87))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W87" s="7" t="e" cm="1">
+        <f t="array" ref="W87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(E87,2-INT(LOG10(ABS(E87))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X87" s="7" t="e" cm="1">
+        <f t="array" ref="X87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(F87,2-INT(LOG10(ABS(F87))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y87" s="7" t="e" cm="1">
+        <f t="array" ref="Y87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(G87,2-INT(LOG10(ABS(G87))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z87" s="7" t="e" cm="1">
+        <f t="array" ref="Z87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(H87,2-INT(LOG10(ABS(H87))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA87" s="7" t="e" cm="1">
+        <f t="array" ref="AA87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(I87,2-INT(LOG10(ABS(I87))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB87" s="7" t="e" cm="1">
+        <f t="array" ref="AB87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(J87,2-INT(LOG10(ABS(J87))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC87" s="7" t="e" cm="1">
+        <f t="array" ref="AC87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(K87,2-INT(LOG10(ABS(K87))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD87" s="7" t="e" cm="1">
+        <f t="array" ref="AD87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(L87,2-INT(LOG10(ABS(L87))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE87" s="7" t="e" cm="1">
+        <f t="array" ref="AE87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(M87,2-INT(LOG10(ABS(M87))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF87" s="7" t="e" cm="1">
+        <f t="array" ref="AF87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(N87,2-INT(LOG10(ABS(N87))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG87" s="7" t="e" cm="1">
+        <f t="array" ref="AG87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(O87,2-INT(LOG10(ABS(O87))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH87" s="7" t="e" cm="1">
+        <f t="array" ref="AH87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(P87,2-INT(LOG10(ABS(P87))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI87" s="7" t="e" cm="1">
+        <f t="array" ref="AI87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(Q87,2-INT(LOG10(ABS(Q87))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ87" s="7" t="e" cm="1">
+        <f t="array" ref="AJ87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(R87,2-INT(LOG10(ABS(R87))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="88" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A88" s="21"/>
-      <c r="B88" s="9" t="s">
+      <c r="A88" s="24"/>
+      <c r="B88" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="C88" s="9" t="s">
+      <c r="C88" s="20" t="s">
         <v>180</v>
       </c>
       <c r="D88" s="8"/>
@@ -6902,7 +7176,7 @@
       <c r="Q88" s="8"/>
       <c r="R88" s="8"/>
       <c r="S88" s="14"/>
-      <c r="T88" s="9" t="s">
+      <c r="T88" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V88" s="7"/>
@@ -6918,11 +7192,11 @@
       <c r="AF88" s="7"/>
     </row>
     <row r="89" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A89" s="21"/>
-      <c r="B89" s="5" t="s">
+      <c r="A89" s="24"/>
+      <c r="B89" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C89" s="5" t="s">
+      <c r="C89" s="21" t="s">
         <v>181</v>
       </c>
       <c r="D89" s="6"/>
@@ -6941,7 +7215,7 @@
       <c r="Q89" s="6"/>
       <c r="R89" s="6"/>
       <c r="S89" s="4"/>
-      <c r="T89" s="5" t="s">
+      <c r="T89" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V89" s="7"/>
@@ -6957,11 +7231,11 @@
       <c r="AF89" s="7"/>
     </row>
     <row r="90" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A90" s="21"/>
-      <c r="B90" s="2" t="s">
+      <c r="A90" s="24"/>
+      <c r="B90" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="22" t="s">
         <v>182</v>
       </c>
       <c r="D90" s="3"/>
@@ -6982,76 +7256,76 @@
       <c r="S90" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="T90" s="2" t="s">
+      <c r="T90" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="V90" s="7" t="e">
-        <f t="shared" ref="V90:AJ90" si="30">_xlfn.RANK.EQ(D90,$D90:$R90,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W90" s="7" t="e">
-        <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X90" s="7" t="e">
-        <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y90" s="7" t="e">
-        <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z90" s="7" t="e">
-        <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA90" s="7" t="e">
-        <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB90" s="7" t="e">
-        <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC90" s="7" t="e">
-        <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD90" s="7" t="e">
-        <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE90" s="7" t="e">
-        <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF90" s="7" t="e">
-        <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG90" s="7" t="e">
-        <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH90" s="7" t="e">
-        <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI90" s="7" t="e">
-        <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ90" s="7" t="e">
-        <f t="shared" si="30"/>
-        <v>#N/A</v>
+      <c r="V90" s="7" t="e" cm="1">
+        <f t="array" ref="V90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(D90,2-INT(LOG10(ABS(D90))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W90" s="7" t="e" cm="1">
+        <f t="array" ref="W90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(E90,2-INT(LOG10(ABS(E90))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X90" s="7" t="e" cm="1">
+        <f t="array" ref="X90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(F90,2-INT(LOG10(ABS(F90))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y90" s="7" t="e" cm="1">
+        <f t="array" ref="Y90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(G90,2-INT(LOG10(ABS(G90))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z90" s="7" t="e" cm="1">
+        <f t="array" ref="Z90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(H90,2-INT(LOG10(ABS(H90))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA90" s="7" t="e" cm="1">
+        <f t="array" ref="AA90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(I90,2-INT(LOG10(ABS(I90))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB90" s="7" t="e" cm="1">
+        <f t="array" ref="AB90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(J90,2-INT(LOG10(ABS(J90))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC90" s="7" t="e" cm="1">
+        <f t="array" ref="AC90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(K90,2-INT(LOG10(ABS(K90))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD90" s="7" t="e" cm="1">
+        <f t="array" ref="AD90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(L90,2-INT(LOG10(ABS(L90))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE90" s="7" t="e" cm="1">
+        <f t="array" ref="AE90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(M90,2-INT(LOG10(ABS(M90))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF90" s="7" t="e" cm="1">
+        <f t="array" ref="AF90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(N90,2-INT(LOG10(ABS(N90))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG90" s="7" t="e" cm="1">
+        <f t="array" ref="AG90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(O90,2-INT(LOG10(ABS(O90))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH90" s="7" t="e" cm="1">
+        <f t="array" ref="AH90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(P90,2-INT(LOG10(ABS(P90))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI90" s="7" t="e" cm="1">
+        <f t="array" ref="AI90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(Q90,2-INT(LOG10(ABS(Q90))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ90" s="7" t="e" cm="1">
+        <f t="array" ref="AJ90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(R90,2-INT(LOG10(ABS(R90))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="91" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A91" s="21"/>
-      <c r="B91" s="9" t="s">
+      <c r="A91" s="24"/>
+      <c r="B91" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="C91" s="9" t="s">
+      <c r="C91" s="20" t="s">
         <v>183</v>
       </c>
       <c r="D91" s="8"/>
@@ -7070,7 +7344,7 @@
       <c r="Q91" s="8"/>
       <c r="R91" s="8"/>
       <c r="S91" s="14"/>
-      <c r="T91" s="9" t="s">
+      <c r="T91" s="20" t="s">
         <v>31</v>
       </c>
       <c r="V91" s="7"/>
@@ -7086,11 +7360,11 @@
       <c r="AF91" s="7"/>
     </row>
     <row r="92" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A92" s="24"/>
-      <c r="B92" s="5" t="s">
+      <c r="A92" s="27"/>
+      <c r="B92" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="C92" s="5" t="s">
+      <c r="C92" s="21" t="s">
         <v>184</v>
       </c>
       <c r="D92" s="6"/>
@@ -7109,7 +7383,7 @@
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
       <c r="S92" s="14"/>
-      <c r="T92" s="9" t="s">
+      <c r="T92" s="20" t="s">
         <v>32</v>
       </c>
       <c r="V92" s="7"/>
@@ -7125,271 +7399,271 @@
       <c r="AF92" s="7"/>
     </row>
     <row r="93" spans="1:36" s="7" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="26" t="s">
+      <c r="A93" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="B93" s="27"/>
-      <c r="C93" s="27"/>
-      <c r="D93" s="2">
+      <c r="B93" s="30"/>
+      <c r="C93" s="30"/>
+      <c r="D93" s="22">
         <f>COUNTIF(V3:V92,1)</f>
         <v>0</v>
       </c>
-      <c r="E93" s="2">
-        <f t="shared" ref="E93:R93" si="31">COUNTIF(W3:W92,1)</f>
+      <c r="E93" s="22">
+        <f t="shared" ref="E93:R93" si="1">COUNTIF(W3:W92,1)</f>
         <v>0</v>
       </c>
-      <c r="F93" s="2">
-        <f t="shared" si="31"/>
+      <c r="F93" s="22">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G93" s="2">
-        <f t="shared" si="31"/>
+      <c r="G93" s="22">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H93" s="2">
-        <f t="shared" si="31"/>
+      <c r="H93" s="22">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I93" s="2">
-        <f t="shared" si="31"/>
+      <c r="I93" s="22">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J93" s="2">
-        <f t="shared" si="31"/>
+      <c r="J93" s="22">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K93" s="2">
-        <f t="shared" si="31"/>
+      <c r="K93" s="22">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L93" s="2">
-        <f t="shared" si="31"/>
+      <c r="L93" s="22">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M93" s="2">
-        <f t="shared" si="31"/>
+      <c r="M93" s="22">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N93" s="2">
-        <f t="shared" si="31"/>
+      <c r="N93" s="22">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O93" s="2">
-        <f t="shared" si="31"/>
+      <c r="O93" s="22">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P93" s="2">
-        <f t="shared" si="31"/>
+      <c r="P93" s="22">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q93" s="2">
-        <f t="shared" si="31"/>
+      <c r="Q93" s="22">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R93" s="2">
-        <f t="shared" si="31"/>
+      <c r="R93" s="22">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:36" s="7" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="21" t="s">
+      <c r="A94" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B94" s="22"/>
-      <c r="C94" s="22"/>
-      <c r="D94" s="9">
+      <c r="B94" s="25"/>
+      <c r="C94" s="25"/>
+      <c r="D94" s="20">
         <f>_xlfn.RANK.EQ(D93,$D93:$R93,0)</f>
         <v>1</v>
       </c>
-      <c r="E94" s="9">
-        <f t="shared" ref="E94:R94" si="32">_xlfn.RANK.EQ(E93,$D93:$R93,0)</f>
+      <c r="E94" s="20">
+        <f t="shared" ref="E94:R94" si="2">_xlfn.RANK.EQ(E93,$D93:$R93,0)</f>
         <v>1</v>
       </c>
-      <c r="F94" s="9">
-        <f t="shared" si="32"/>
+      <c r="F94" s="20">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="G94" s="9">
-        <f t="shared" si="32"/>
+      <c r="G94" s="20">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H94" s="9">
-        <f t="shared" si="32"/>
+      <c r="H94" s="20">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="I94" s="9">
-        <f t="shared" si="32"/>
+      <c r="I94" s="20">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J94" s="9">
-        <f t="shared" si="32"/>
+      <c r="J94" s="20">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K94" s="9">
-        <f t="shared" si="32"/>
+      <c r="K94" s="20">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="L94" s="9">
-        <f t="shared" si="32"/>
+      <c r="L94" s="20">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="M94" s="9">
-        <f t="shared" si="32"/>
+      <c r="M94" s="20">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N94" s="9">
-        <f t="shared" si="32"/>
+      <c r="N94" s="20">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="O94" s="9">
-        <f t="shared" si="32"/>
+      <c r="O94" s="20">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P94" s="9">
-        <f t="shared" si="32"/>
+      <c r="P94" s="20">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="Q94" s="9">
-        <f t="shared" si="32"/>
+      <c r="Q94" s="20">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="R94" s="9">
-        <f t="shared" si="32"/>
+      <c r="R94" s="20">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:36" s="7" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="23" t="s">
+      <c r="A95" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="B95" s="22"/>
-      <c r="C95" s="22"/>
+      <c r="B95" s="25"/>
+      <c r="C95" s="25"/>
       <c r="D95" s="15" t="e">
         <f>AVERAGE(V3:V92)</f>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="E95" s="15" t="e">
-        <f t="shared" ref="E95:R95" si="33">AVERAGE(W3:W92)</f>
-        <v>#N/A</v>
+        <f t="shared" ref="E95:R95" si="3">AVERAGE(W3:W92)</f>
+        <v>#NUM!</v>
       </c>
       <c r="F95" s="15" t="e">
-        <f t="shared" si="33"/>
-        <v>#N/A</v>
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
       </c>
       <c r="G95" s="15" t="e">
-        <f t="shared" si="33"/>
-        <v>#N/A</v>
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
       </c>
       <c r="H95" s="15" t="e">
-        <f t="shared" si="33"/>
-        <v>#N/A</v>
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
       </c>
       <c r="I95" s="15" t="e">
-        <f t="shared" si="33"/>
-        <v>#N/A</v>
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
       </c>
       <c r="J95" s="15" t="e">
-        <f t="shared" si="33"/>
-        <v>#N/A</v>
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
       </c>
       <c r="K95" s="15" t="e">
-        <f t="shared" si="33"/>
-        <v>#N/A</v>
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
       </c>
       <c r="L95" s="15" t="e">
-        <f t="shared" si="33"/>
-        <v>#N/A</v>
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
       </c>
       <c r="M95" s="15" t="e">
-        <f t="shared" si="33"/>
-        <v>#N/A</v>
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
       </c>
       <c r="N95" s="15" t="e">
-        <f t="shared" si="33"/>
-        <v>#N/A</v>
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
       </c>
       <c r="O95" s="15" t="e">
-        <f t="shared" si="33"/>
-        <v>#N/A</v>
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
       </c>
       <c r="P95" s="15" t="e">
-        <f t="shared" si="33"/>
-        <v>#N/A</v>
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
       </c>
       <c r="Q95" s="15" t="e">
-        <f t="shared" si="33"/>
-        <v>#N/A</v>
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
       </c>
       <c r="R95" s="15" t="e">
-        <f t="shared" si="33"/>
-        <v>#N/A</v>
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="96" spans="1:36" s="7" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="24" t="s">
+      <c r="A96" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="B96" s="25"/>
-      <c r="C96" s="25"/>
-      <c r="D96" s="5" t="e">
+      <c r="B96" s="28"/>
+      <c r="C96" s="28"/>
+      <c r="D96" s="21" t="e">
         <f>_xlfn.RANK.EQ(D95,$D95:$R95,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E96" s="5" t="e">
-        <f t="shared" ref="E96:R96" si="34">_xlfn.RANK.EQ(E95,$D95:$R95,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F96" s="5" t="e">
-        <f t="shared" si="34"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G96" s="5" t="e">
-        <f t="shared" si="34"/>
-        <v>#N/A</v>
-      </c>
-      <c r="H96" s="5" t="e">
-        <f t="shared" si="34"/>
-        <v>#N/A</v>
-      </c>
-      <c r="I96" s="5" t="e">
-        <f t="shared" si="34"/>
-        <v>#N/A</v>
-      </c>
-      <c r="J96" s="5" t="e">
-        <f t="shared" si="34"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K96" s="5" t="e">
-        <f t="shared" si="34"/>
-        <v>#N/A</v>
-      </c>
-      <c r="L96" s="5" t="e">
-        <f t="shared" si="34"/>
-        <v>#N/A</v>
-      </c>
-      <c r="M96" s="5" t="e">
-        <f t="shared" si="34"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N96" s="5" t="e">
-        <f t="shared" si="34"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O96" s="5" t="e">
-        <f t="shared" si="34"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P96" s="5" t="e">
-        <f t="shared" si="34"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q96" s="5" t="e">
-        <f t="shared" si="34"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R96" s="5" t="e">
-        <f t="shared" si="34"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
+      </c>
+      <c r="E96" s="21" t="e">
+        <f t="shared" ref="E96:R96" si="4">_xlfn.RANK.EQ(E95,$D95:$R95,1)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F96" s="21" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="G96" s="21" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="H96" s="21" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="I96" s="21" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="J96" s="21" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="K96" s="21" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L96" s="21" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="M96" s="21" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="N96" s="21" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O96" s="21" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P96" s="21" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q96" s="21" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R96" s="21" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
       </c>
     </row>
   </sheetData>
@@ -7406,94 +7680,154 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="D3:R3">
-    <cfRule type="top10" dxfId="33" priority="30" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="32" priority="30">
+      <formula>ROUND(D3,2-INT(LOG10(ABS(D3))))= ROUND(MIN($D3:$R3),2-INT(LOG10(ABS(MIN($D3:$R3)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:R6">
-    <cfRule type="top10" dxfId="32" priority="29" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="31" priority="29">
+      <formula>ROUND(D6,2-INT(LOG10(ABS(D6))))= ROUND(MIN($D6:$R6),2-INT(LOG10(ABS(MIN($D6:$R6)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:R9">
-    <cfRule type="top10" dxfId="31" priority="28" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="30" priority="28">
+      <formula>ROUND(D9,2-INT(LOG10(ABS(D9))))= ROUND(MIN($D9:$R9),2-INT(LOG10(ABS(MIN($D9:$R9)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12:R12">
-    <cfRule type="top10" dxfId="30" priority="27" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="29" priority="27">
+      <formula>ROUND(D12,2-INT(LOG10(ABS(D12))))= ROUND(MIN($D12:$R12),2-INT(LOG10(ABS(MIN($D12:$R12)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:R15">
-    <cfRule type="top10" dxfId="29" priority="26" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="28" priority="26">
+      <formula>ROUND(D15,2-INT(LOG10(ABS(D15))))= ROUND(MIN($D15:$R15),2-INT(LOG10(ABS(MIN($D15:$R15)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:R18">
-    <cfRule type="top10" dxfId="28" priority="25" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="27" priority="25">
+      <formula>ROUND(D18,2-INT(LOG10(ABS(D18))))= ROUND(MIN($D18:$R18),2-INT(LOG10(ABS(MIN($D18:$R18)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D21:R21">
-    <cfRule type="top10" dxfId="27" priority="24" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="26" priority="24">
+      <formula>ROUND(D21,2-INT(LOG10(ABS(D21))))= ROUND(MIN($D21:$R21),2-INT(LOG10(ABS(MIN($D21:$R21)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D24:R24">
-    <cfRule type="top10" dxfId="26" priority="23" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="25" priority="23">
+      <formula>ROUND(D24,2-INT(LOG10(ABS(D24))))= ROUND(MIN($D24:$R24),2-INT(LOG10(ABS(MIN($D24:$R24)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27:R27">
-    <cfRule type="top10" dxfId="25" priority="22" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="24" priority="22">
+      <formula>ROUND(D27,2-INT(LOG10(ABS(D27))))= ROUND(MIN($D27:$R27),2-INT(LOG10(ABS(MIN($D27:$R27)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:R30">
-    <cfRule type="top10" dxfId="24" priority="21" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="23" priority="21">
+      <formula>ROUND(D30,2-INT(LOG10(ABS(D30))))= ROUND(MIN($D30:$R30),2-INT(LOG10(ABS(MIN($D30:$R30)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D33:R33">
-    <cfRule type="top10" dxfId="23" priority="20" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="22" priority="20">
+      <formula>ROUND(D33,2-INT(LOG10(ABS(D33))))= ROUND(MIN($D33:$R33),2-INT(LOG10(ABS(MIN($D33:$R33)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D36:R36">
-    <cfRule type="top10" dxfId="22" priority="19" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="21" priority="19">
+      <formula>ROUND(D36,2-INT(LOG10(ABS(D36))))= ROUND(MIN($D36:$R36),2-INT(LOG10(ABS(MIN($D36:$R36)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D39:R39">
-    <cfRule type="top10" dxfId="21" priority="18" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="20" priority="18">
+      <formula>ROUND(D39,2-INT(LOG10(ABS(D39))))= ROUND(MIN($D39:$R39),2-INT(LOG10(ABS(MIN($D39:$R39)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D42:R42">
-    <cfRule type="top10" dxfId="20" priority="17" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="19" priority="17">
+      <formula>ROUND(D42,2-INT(LOG10(ABS(D42))))= ROUND(MIN($D42:$R42),2-INT(LOG10(ABS(MIN($D42:$R42)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45:R45">
-    <cfRule type="top10" dxfId="19" priority="16" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="18" priority="16">
+      <formula>ROUND(D45,2-INT(LOG10(ABS(D45))))= ROUND(MIN($D45:$R45),2-INT(LOG10(ABS(MIN($D45:$R45)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D48:R48">
-    <cfRule type="top10" dxfId="18" priority="15" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="17" priority="15">
+      <formula>ROUND(D48,2-INT(LOG10(ABS(D48))))= ROUND(MIN($D48:$R48),2-INT(LOG10(ABS(MIN($D48:$R48)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51:R51">
-    <cfRule type="top10" dxfId="17" priority="14" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="16" priority="14">
+      <formula>ROUND(D51,2-INT(LOG10(ABS(D51))))= ROUND(MIN($D51:$R51),2-INT(LOG10(ABS(MIN($D51:$R51)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54:R54">
-    <cfRule type="top10" dxfId="16" priority="13" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="15" priority="13">
+      <formula>ROUND(D54,2-INT(LOG10(ABS(D54))))= ROUND(MIN($D54:$R54),2-INT(LOG10(ABS(MIN($D54:$R54)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D57:R57">
-    <cfRule type="top10" dxfId="15" priority="12" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="14" priority="12">
+      <formula>ROUND(D57,2-INT(LOG10(ABS(D57))))= ROUND(MIN($D57:$R57),2-INT(LOG10(ABS(MIN($D57:$R57)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D60:R60">
-    <cfRule type="top10" dxfId="14" priority="11" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="13" priority="11">
+      <formula>ROUND(D60,2-INT(LOG10(ABS(D60))))= ROUND(MIN($D60:$R60),2-INT(LOG10(ABS(MIN($D60:$R60)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:R63">
-    <cfRule type="top10" dxfId="13" priority="10" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="12" priority="10">
+      <formula>ROUND(D63,2-INT(LOG10(ABS(D63))))= ROUND(MIN($D63:$R63),2-INT(LOG10(ABS(MIN($D63:$R63)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D66:R66">
-    <cfRule type="top10" dxfId="12" priority="9" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="11" priority="9">
+      <formula>ROUND(D66,2-INT(LOG10(ABS(D66))))= ROUND(MIN($D66:$R66),2-INT(LOG10(ABS(MIN($D66:$R66)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69:R69">
-    <cfRule type="top10" dxfId="11" priority="8" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="10" priority="8">
+      <formula>ROUND(D69,2-INT(LOG10(ABS(D69))))= ROUND(MIN($D69:$R69),2-INT(LOG10(ABS(MIN($D69:$R69)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D72:R72">
-    <cfRule type="top10" dxfId="10" priority="7" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="9" priority="7">
+      <formula>ROUND(D72,2-INT(LOG10(ABS(D72))))= ROUND(MIN($D72:$R72),2-INT(LOG10(ABS(MIN($D72:$R72)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D75:R75">
-    <cfRule type="top10" dxfId="9" priority="6" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="8" priority="6">
+      <formula>ROUND(D75,2-INT(LOG10(ABS(D75))))= ROUND(MIN($D75:$R75),2-INT(LOG10(ABS(MIN($D75:$R75)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D78:R78">
-    <cfRule type="top10" dxfId="8" priority="5" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="7" priority="5">
+      <formula>ROUND(D78,2-INT(LOG10(ABS(D78))))= ROUND(MIN($D78:$R78),2-INT(LOG10(ABS(MIN($D78:$R78)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D81:R81">
-    <cfRule type="top10" dxfId="7" priority="4" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="6" priority="4">
+      <formula>ROUND(D81,2-INT(LOG10(ABS(D81))))= ROUND(MIN($D81:$R81),2-INT(LOG10(ABS(MIN($D81:$R81)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D84:R84">
-    <cfRule type="top10" dxfId="6" priority="3" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>ROUND(D84,2-INT(LOG10(ABS(D84))))= ROUND(MIN($D84:$R84),2-INT(LOG10(ABS(MIN($D84:$R84)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:R87">
-    <cfRule type="top10" dxfId="5" priority="2" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>ROUND(D87,2-INT(LOG10(ABS(D87))))= ROUND(MIN($D87:$R87),2-INT(LOG10(ABS(MIN($D87:$R87)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D90:R90">
-    <cfRule type="top10" dxfId="4" priority="1" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>ROUND(D90,2-INT(LOG10(ABS(D90))))= ROUND(MIN($D90:$R90),2-INT(LOG10(ABS(MIN($D90:$R90)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -7514,23 +7848,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -8155,7 +8489,7 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B3:N32">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="greaterThan">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8175,23 +8509,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -8815,7 +9149,7 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:O32">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8835,23 +9169,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -9475,7 +9809,7 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:O32">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="greaterThan">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9495,23 +9829,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -10135,7 +10469,7 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:O32">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10155,23 +10489,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">

--- a/src/results_template/CEC2014/30Dim.xlsx
+++ b/src/results_template/CEC2014/30Dim.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GtiHub\Repositories\Base-Optimization-Framework\src\results_template\CEC2014\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GtiHub\Repositories\Base-Optimization-Framework\src\results\results_template\CEC2014\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E0BEC6-40BE-48F0-99DC-7544D0C0DABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFBEAB7-EA47-4191-9696-995CBC43CD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conclusions" sheetId="2" r:id="rId1"/>
@@ -34,33 +34,8 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1234,7 +1209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1287,15 +1262,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1327,256 +1293,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="68">
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
+  <dxfs count="38">
     <dxf>
       <font>
         <b/>
@@ -1846,6 +1563,12 @@
       </font>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="thin">
           <color indexed="64"/>
@@ -1854,6 +1577,9 @@
           <color indexed="64"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1869,11 +1595,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="S2:T92" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="67">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="S2:T92" totalsRowShown="0" headerRowDxfId="37" tableBorderDxfId="36">
   <autoFilter ref="S2:T92" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2211,26 +1937,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
     </row>
     <row r="2" spans="1:36" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -2283,10 +2009,10 @@
       <c r="R2" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="S2" s="20" t="s">
+      <c r="S2" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="T2" s="20" t="s">
+      <c r="T2" s="9" t="s">
         <v>39</v>
       </c>
       <c r="V2" s="12" t="str">
@@ -2351,13 +2077,13 @@
       </c>
     </row>
     <row r="3" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D3" s="3"/>
@@ -2378,76 +2104,76 @@
       <c r="S3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="T3" s="22" t="s">
+      <c r="T3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="7" t="e" cm="1">
-        <f t="array" ref="V3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(D3,2-INT(LOG10(ABS(D3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W3" s="7" t="e" cm="1">
-        <f t="array" ref="W3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(E3,2-INT(LOG10(ABS(E3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X3" s="7" t="e" cm="1">
-        <f t="array" ref="X3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(F3,2-INT(LOG10(ABS(F3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y3" s="7" t="e" cm="1">
-        <f t="array" ref="Y3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(G3,2-INT(LOG10(ABS(G3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z3" s="7" t="e" cm="1">
-        <f t="array" ref="Z3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(H3,2-INT(LOG10(ABS(H3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA3" s="7" t="e" cm="1">
-        <f t="array" ref="AA3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(I3,2-INT(LOG10(ABS(I3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB3" s="7" t="e" cm="1">
-        <f t="array" ref="AB3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(J3,2-INT(LOG10(ABS(J3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC3" s="7" t="e" cm="1">
-        <f t="array" ref="AC3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(K3,2-INT(LOG10(ABS(K3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD3" s="7" t="e" cm="1">
-        <f t="array" ref="AD3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(L3,2-INT(LOG10(ABS(L3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE3" s="7" t="e" cm="1">
-        <f t="array" ref="AE3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(M3,2-INT(LOG10(ABS(M3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF3" s="7" t="e" cm="1">
-        <f t="array" ref="AF3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(N3,2-INT(LOG10(ABS(N3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG3" s="7" t="e" cm="1">
-        <f t="array" ref="AG3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(O3,2-INT(LOG10(ABS(O3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH3" s="7" t="e" cm="1">
-        <f t="array" ref="AH3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(P3,2-INT(LOG10(ABS(P3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI3" s="7" t="e" cm="1">
-        <f t="array" ref="AI3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(Q3,2-INT(LOG10(ABS(Q3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ3" s="7" t="e" cm="1">
-        <f t="array" ref="AJ3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(R3,2-INT(LOG10(ABS(R3))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V3" s="7" t="e">
+        <f t="shared" ref="V3:AJ3" si="1">_xlfn.RANK.EQ(D3,$D3:$R3,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W3" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X3" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y3" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z3" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA3" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB3" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC3" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD3" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE3" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF3" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG3" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH3" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI3" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ3" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A4" s="24"/>
-      <c r="B4" s="20" t="s">
+      <c r="A4" s="21"/>
+      <c r="B4" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="9" t="s">
         <v>96</v>
       </c>
       <c r="D4" s="8"/>
@@ -2466,7 +2192,7 @@
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
       <c r="S4" s="14"/>
-      <c r="T4" s="20" t="s">
+      <c r="T4" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V4" s="7"/>
@@ -2482,11 +2208,11 @@
       <c r="AF4" s="7"/>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="21"/>
+      <c r="B5" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="5" t="s">
         <v>97</v>
       </c>
       <c r="D5" s="6"/>
@@ -2505,7 +2231,7 @@
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="21" t="s">
+      <c r="T5" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V5" s="7"/>
@@ -2521,11 +2247,11 @@
       <c r="AF5" s="7"/>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="22" t="s">
+      <c r="A6" s="21"/>
+      <c r="B6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D6" s="3"/>
@@ -2546,76 +2272,76 @@
       <c r="S6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="T6" s="22" t="s">
+      <c r="T6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V6" s="7" t="e" cm="1">
-        <f t="array" ref="V6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(D6,2-INT(LOG10(ABS(D6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W6" s="7" t="e" cm="1">
-        <f t="array" ref="W6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(E6,2-INT(LOG10(ABS(E6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X6" s="7" t="e" cm="1">
-        <f t="array" ref="X6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(F6,2-INT(LOG10(ABS(F6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y6" s="7" t="e" cm="1">
-        <f t="array" ref="Y6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(G6,2-INT(LOG10(ABS(G6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z6" s="7" t="e" cm="1">
-        <f t="array" ref="Z6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(H6,2-INT(LOG10(ABS(H6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA6" s="7" t="e" cm="1">
-        <f t="array" ref="AA6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(I6,2-INT(LOG10(ABS(I6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB6" s="7" t="e" cm="1">
-        <f t="array" ref="AB6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(J6,2-INT(LOG10(ABS(J6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC6" s="7" t="e" cm="1">
-        <f t="array" ref="AC6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(K6,2-INT(LOG10(ABS(K6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD6" s="7" t="e" cm="1">
-        <f t="array" ref="AD6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(L6,2-INT(LOG10(ABS(L6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE6" s="7" t="e" cm="1">
-        <f t="array" ref="AE6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(M6,2-INT(LOG10(ABS(M6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF6" s="7" t="e" cm="1">
-        <f t="array" ref="AF6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(N6,2-INT(LOG10(ABS(N6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG6" s="7" t="e" cm="1">
-        <f t="array" ref="AG6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(O6,2-INT(LOG10(ABS(O6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH6" s="7" t="e" cm="1">
-        <f t="array" ref="AH6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(P6,2-INT(LOG10(ABS(P6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI6" s="7" t="e" cm="1">
-        <f t="array" ref="AI6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(Q6,2-INT(LOG10(ABS(Q6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ6" s="7" t="e" cm="1">
-        <f t="array" ref="AJ6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(R6,2-INT(LOG10(ABS(R6))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V6" s="7" t="e">
+        <f t="shared" ref="V6:AJ6" si="2">_xlfn.RANK.EQ(D6,$D6:$R6,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W6" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X6" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y6" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z6" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA6" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB6" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC6" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD6" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE6" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF6" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG6" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH6" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI6" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ6" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A7" s="24"/>
-      <c r="B7" s="20" t="s">
+      <c r="A7" s="21"/>
+      <c r="B7" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="9" t="s">
         <v>99</v>
       </c>
       <c r="D7" s="8"/>
@@ -2634,7 +2360,7 @@
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
       <c r="S7" s="14"/>
-      <c r="T7" s="20" t="s">
+      <c r="T7" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V7" s="7"/>
@@ -2650,11 +2376,11 @@
       <c r="AF7" s="7"/>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A8" s="24"/>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="21"/>
+      <c r="B8" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="5" t="s">
         <v>100</v>
       </c>
       <c r="D8" s="6"/>
@@ -2673,7 +2399,7 @@
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
       <c r="S8" s="4"/>
-      <c r="T8" s="21" t="s">
+      <c r="T8" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V8" s="7"/>
@@ -2689,11 +2415,11 @@
       <c r="AF8" s="7"/>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A9" s="24"/>
-      <c r="B9" s="22" t="s">
+      <c r="A9" s="21"/>
+      <c r="B9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="2" t="s">
         <v>101</v>
       </c>
       <c r="D9" s="3"/>
@@ -2714,76 +2440,76 @@
       <c r="S9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="T9" s="22" t="s">
+      <c r="T9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V9" s="7" t="e" cm="1">
-        <f t="array" ref="V9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(D9,2-INT(LOG10(ABS(D9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W9" s="7" t="e" cm="1">
-        <f t="array" ref="W9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(E9,2-INT(LOG10(ABS(E9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X9" s="7" t="e" cm="1">
-        <f t="array" ref="X9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(F9,2-INT(LOG10(ABS(F9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y9" s="7" t="e" cm="1">
-        <f t="array" ref="Y9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(G9,2-INT(LOG10(ABS(G9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z9" s="7" t="e" cm="1">
-        <f t="array" ref="Z9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(H9,2-INT(LOG10(ABS(H9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA9" s="7" t="e" cm="1">
-        <f t="array" ref="AA9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(I9,2-INT(LOG10(ABS(I9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB9" s="7" t="e" cm="1">
-        <f t="array" ref="AB9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(J9,2-INT(LOG10(ABS(J9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC9" s="7" t="e" cm="1">
-        <f t="array" ref="AC9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(K9,2-INT(LOG10(ABS(K9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD9" s="7" t="e" cm="1">
-        <f t="array" ref="AD9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(L9,2-INT(LOG10(ABS(L9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE9" s="7" t="e" cm="1">
-        <f t="array" ref="AE9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(M9,2-INT(LOG10(ABS(M9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF9" s="7" t="e" cm="1">
-        <f t="array" ref="AF9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(N9,2-INT(LOG10(ABS(N9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG9" s="7" t="e" cm="1">
-        <f t="array" ref="AG9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(O9,2-INT(LOG10(ABS(O9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH9" s="7" t="e" cm="1">
-        <f t="array" ref="AH9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(P9,2-INT(LOG10(ABS(P9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI9" s="7" t="e" cm="1">
-        <f t="array" ref="AI9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(Q9,2-INT(LOG10(ABS(Q9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ9" s="7" t="e" cm="1">
-        <f t="array" ref="AJ9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(R9,2-INT(LOG10(ABS(R9))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V9" s="7" t="e">
+        <f t="shared" ref="V9:AJ9" si="3">_xlfn.RANK.EQ(D9,$D9:$R9,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W9" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X9" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y9" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z9" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA9" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB9" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC9" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD9" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE9" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF9" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG9" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH9" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI9" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ9" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A10" s="24"/>
-      <c r="B10" s="20" t="s">
+      <c r="A10" s="21"/>
+      <c r="B10" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="9" t="s">
         <v>102</v>
       </c>
       <c r="D10" s="8"/>
@@ -2802,7 +2528,7 @@
       <c r="Q10" s="8"/>
       <c r="R10" s="8"/>
       <c r="S10" s="14"/>
-      <c r="T10" s="20" t="s">
+      <c r="T10" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V10" s="7"/>
@@ -2818,11 +2544,11 @@
       <c r="AF10" s="7"/>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A11" s="27"/>
-      <c r="B11" s="21" t="s">
+      <c r="A11" s="24"/>
+      <c r="B11" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="5" t="s">
         <v>103</v>
       </c>
       <c r="D11" s="6"/>
@@ -2841,7 +2567,7 @@
       <c r="Q11" s="6"/>
       <c r="R11" s="6"/>
       <c r="S11" s="4"/>
-      <c r="T11" s="21" t="s">
+      <c r="T11" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V11" s="7"/>
@@ -2857,13 +2583,13 @@
       <c r="AF11" s="7"/>
     </row>
     <row r="12" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="2" t="s">
         <v>104</v>
       </c>
       <c r="D12" s="3"/>
@@ -2884,76 +2610,76 @@
       <c r="S12" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="T12" s="22" t="s">
+      <c r="T12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V12" s="7" t="e" cm="1">
-        <f t="array" ref="V12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(D12,2-INT(LOG10(ABS(D12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W12" s="7" t="e" cm="1">
-        <f t="array" ref="W12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(E12,2-INT(LOG10(ABS(E12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X12" s="7" t="e" cm="1">
-        <f t="array" ref="X12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(F12,2-INT(LOG10(ABS(F12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y12" s="7" t="e" cm="1">
-        <f t="array" ref="Y12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(G12,2-INT(LOG10(ABS(G12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z12" s="7" t="e" cm="1">
-        <f t="array" ref="Z12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(H12,2-INT(LOG10(ABS(H12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA12" s="7" t="e" cm="1">
-        <f t="array" ref="AA12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(I12,2-INT(LOG10(ABS(I12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB12" s="7" t="e" cm="1">
-        <f t="array" ref="AB12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(J12,2-INT(LOG10(ABS(J12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC12" s="7" t="e" cm="1">
-        <f t="array" ref="AC12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(K12,2-INT(LOG10(ABS(K12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD12" s="7" t="e" cm="1">
-        <f t="array" ref="AD12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(L12,2-INT(LOG10(ABS(L12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE12" s="7" t="e" cm="1">
-        <f t="array" ref="AE12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(M12,2-INT(LOG10(ABS(M12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF12" s="7" t="e" cm="1">
-        <f t="array" ref="AF12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(N12,2-INT(LOG10(ABS(N12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG12" s="7" t="e" cm="1">
-        <f t="array" ref="AG12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(O12,2-INT(LOG10(ABS(O12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH12" s="7" t="e" cm="1">
-        <f t="array" ref="AH12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(P12,2-INT(LOG10(ABS(P12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI12" s="7" t="e" cm="1">
-        <f t="array" ref="AI12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(Q12,2-INT(LOG10(ABS(Q12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ12" s="7" t="e" cm="1">
-        <f t="array" ref="AJ12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(R12,2-INT(LOG10(ABS(R12))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V12" s="7" t="e">
+        <f t="shared" ref="V12:AJ12" si="4">_xlfn.RANK.EQ(D12,$D12:$R12,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W12" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X12" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y12" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z12" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA12" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB12" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC12" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD12" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE12" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF12" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG12" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH12" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI12" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ12" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A13" s="24"/>
-      <c r="B13" s="20" t="s">
+      <c r="A13" s="21"/>
+      <c r="B13" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="9" t="s">
         <v>105</v>
       </c>
       <c r="D13" s="8"/>
@@ -2972,7 +2698,7 @@
       <c r="Q13" s="8"/>
       <c r="R13" s="8"/>
       <c r="S13" s="14"/>
-      <c r="T13" s="20" t="s">
+      <c r="T13" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V13" s="7"/>
@@ -2988,11 +2714,11 @@
       <c r="AF13" s="7"/>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A14" s="24"/>
-      <c r="B14" s="21" t="s">
+      <c r="A14" s="21"/>
+      <c r="B14" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="5" t="s">
         <v>106</v>
       </c>
       <c r="D14" s="6"/>
@@ -3011,7 +2737,7 @@
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
       <c r="S14" s="4"/>
-      <c r="T14" s="21" t="s">
+      <c r="T14" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V14" s="7"/>
@@ -3027,11 +2753,11 @@
       <c r="AF14" s="7"/>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A15" s="24"/>
-      <c r="B15" s="22" t="s">
+      <c r="A15" s="21"/>
+      <c r="B15" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="2" t="s">
         <v>107</v>
       </c>
       <c r="D15" s="3"/>
@@ -3052,76 +2778,76 @@
       <c r="S15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="T15" s="22" t="s">
+      <c r="T15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V15" s="7" t="e" cm="1">
-        <f t="array" ref="V15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(D15,2-INT(LOG10(ABS(D15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W15" s="7" t="e" cm="1">
-        <f t="array" ref="W15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(E15,2-INT(LOG10(ABS(E15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X15" s="7" t="e" cm="1">
-        <f t="array" ref="X15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(F15,2-INT(LOG10(ABS(F15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y15" s="7" t="e" cm="1">
-        <f t="array" ref="Y15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(G15,2-INT(LOG10(ABS(G15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z15" s="7" t="e" cm="1">
-        <f t="array" ref="Z15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(H15,2-INT(LOG10(ABS(H15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA15" s="7" t="e" cm="1">
-        <f t="array" ref="AA15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(I15,2-INT(LOG10(ABS(I15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB15" s="7" t="e" cm="1">
-        <f t="array" ref="AB15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(J15,2-INT(LOG10(ABS(J15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC15" s="7" t="e" cm="1">
-        <f t="array" ref="AC15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(K15,2-INT(LOG10(ABS(K15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD15" s="7" t="e" cm="1">
-        <f t="array" ref="AD15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(L15,2-INT(LOG10(ABS(L15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE15" s="7" t="e" cm="1">
-        <f t="array" ref="AE15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(M15,2-INT(LOG10(ABS(M15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF15" s="7" t="e" cm="1">
-        <f t="array" ref="AF15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(N15,2-INT(LOG10(ABS(N15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG15" s="7" t="e" cm="1">
-        <f t="array" ref="AG15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(O15,2-INT(LOG10(ABS(O15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH15" s="7" t="e" cm="1">
-        <f t="array" ref="AH15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(P15,2-INT(LOG10(ABS(P15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI15" s="7" t="e" cm="1">
-        <f t="array" ref="AI15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(Q15,2-INT(LOG10(ABS(Q15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ15" s="7" t="e" cm="1">
-        <f t="array" ref="AJ15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(R15,2-INT(LOG10(ABS(R15))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V15" s="7" t="e">
+        <f t="shared" ref="V15:AJ15" si="5">_xlfn.RANK.EQ(D15,$D15:$R15,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W15" s="7" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X15" s="7" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y15" s="7" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z15" s="7" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA15" s="7" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB15" s="7" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC15" s="7" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD15" s="7" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE15" s="7" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF15" s="7" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG15" s="7" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH15" s="7" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI15" s="7" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ15" s="7" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A16" s="24"/>
-      <c r="B16" s="20" t="s">
+      <c r="A16" s="21"/>
+      <c r="B16" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="9" t="s">
         <v>108</v>
       </c>
       <c r="D16" s="8"/>
@@ -3140,7 +2866,7 @@
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
       <c r="S16" s="14"/>
-      <c r="T16" s="20" t="s">
+      <c r="T16" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V16" s="7"/>
@@ -3156,11 +2882,11 @@
       <c r="AF16" s="7"/>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A17" s="24"/>
-      <c r="B17" s="21" t="s">
+      <c r="A17" s="21"/>
+      <c r="B17" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="5" t="s">
         <v>109</v>
       </c>
       <c r="D17" s="6"/>
@@ -3179,7 +2905,7 @@
       <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
       <c r="S17" s="4"/>
-      <c r="T17" s="21" t="s">
+      <c r="T17" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V17" s="7"/>
@@ -3195,11 +2921,11 @@
       <c r="AF17" s="7"/>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A18" s="24"/>
-      <c r="B18" s="22" t="s">
+      <c r="A18" s="21"/>
+      <c r="B18" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D18" s="3"/>
@@ -3220,76 +2946,76 @@
       <c r="S18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="T18" s="22" t="s">
+      <c r="T18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V18" s="7" t="e" cm="1">
-        <f t="array" ref="V18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(D18,2-INT(LOG10(ABS(D18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W18" s="7" t="e" cm="1">
-        <f t="array" ref="W18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(E18,2-INT(LOG10(ABS(E18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X18" s="7" t="e" cm="1">
-        <f t="array" ref="X18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(F18,2-INT(LOG10(ABS(F18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y18" s="7" t="e" cm="1">
-        <f t="array" ref="Y18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(G18,2-INT(LOG10(ABS(G18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z18" s="7" t="e" cm="1">
-        <f t="array" ref="Z18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(H18,2-INT(LOG10(ABS(H18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA18" s="7" t="e" cm="1">
-        <f t="array" ref="AA18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(I18,2-INT(LOG10(ABS(I18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB18" s="7" t="e" cm="1">
-        <f t="array" ref="AB18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(J18,2-INT(LOG10(ABS(J18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC18" s="7" t="e" cm="1">
-        <f t="array" ref="AC18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(K18,2-INT(LOG10(ABS(K18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD18" s="7" t="e" cm="1">
-        <f t="array" ref="AD18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(L18,2-INT(LOG10(ABS(L18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE18" s="7" t="e" cm="1">
-        <f t="array" ref="AE18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(M18,2-INT(LOG10(ABS(M18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF18" s="7" t="e" cm="1">
-        <f t="array" ref="AF18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(N18,2-INT(LOG10(ABS(N18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG18" s="7" t="e" cm="1">
-        <f t="array" ref="AG18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(O18,2-INT(LOG10(ABS(O18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH18" s="7" t="e" cm="1">
-        <f t="array" ref="AH18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(P18,2-INT(LOG10(ABS(P18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI18" s="7" t="e" cm="1">
-        <f t="array" ref="AI18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(Q18,2-INT(LOG10(ABS(Q18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ18" s="7" t="e" cm="1">
-        <f t="array" ref="AJ18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(R18,2-INT(LOG10(ABS(R18))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V18" s="7" t="e">
+        <f t="shared" ref="V18:AJ18" si="6">_xlfn.RANK.EQ(D18,$D18:$R18,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W18" s="7" t="e">
+        <f t="shared" si="6"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X18" s="7" t="e">
+        <f t="shared" si="6"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y18" s="7" t="e">
+        <f t="shared" si="6"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z18" s="7" t="e">
+        <f t="shared" si="6"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA18" s="7" t="e">
+        <f t="shared" si="6"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB18" s="7" t="e">
+        <f t="shared" si="6"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC18" s="7" t="e">
+        <f t="shared" si="6"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD18" s="7" t="e">
+        <f t="shared" si="6"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE18" s="7" t="e">
+        <f t="shared" si="6"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF18" s="7" t="e">
+        <f t="shared" si="6"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG18" s="7" t="e">
+        <f t="shared" si="6"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH18" s="7" t="e">
+        <f t="shared" si="6"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI18" s="7" t="e">
+        <f t="shared" si="6"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ18" s="7" t="e">
+        <f t="shared" si="6"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="20" t="s">
+      <c r="A19" s="21"/>
+      <c r="B19" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D19" s="8"/>
@@ -3308,7 +3034,7 @@
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
       <c r="S19" s="14"/>
-      <c r="T19" s="20" t="s">
+      <c r="T19" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V19" s="7"/>
@@ -3324,11 +3050,11 @@
       <c r="AF19" s="7"/>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A20" s="24"/>
-      <c r="B20" s="21" t="s">
+      <c r="A20" s="21"/>
+      <c r="B20" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="5" t="s">
         <v>112</v>
       </c>
       <c r="D20" s="6"/>
@@ -3347,7 +3073,7 @@
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
       <c r="S20" s="4"/>
-      <c r="T20" s="21" t="s">
+      <c r="T20" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V20" s="7"/>
@@ -3363,11 +3089,11 @@
       <c r="AF20" s="7"/>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A21" s="24"/>
-      <c r="B21" s="22" t="s">
+      <c r="A21" s="21"/>
+      <c r="B21" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="2" t="s">
         <v>113</v>
       </c>
       <c r="D21" s="3"/>
@@ -3388,76 +3114,76 @@
       <c r="S21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="T21" s="22" t="s">
+      <c r="T21" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V21" s="7" t="e" cm="1">
-        <f t="array" ref="V21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(D21,2-INT(LOG10(ABS(D21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W21" s="7" t="e" cm="1">
-        <f t="array" ref="W21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(E21,2-INT(LOG10(ABS(E21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X21" s="7" t="e" cm="1">
-        <f t="array" ref="X21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(F21,2-INT(LOG10(ABS(F21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y21" s="7" t="e" cm="1">
-        <f t="array" ref="Y21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(G21,2-INT(LOG10(ABS(G21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z21" s="7" t="e" cm="1">
-        <f t="array" ref="Z21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(H21,2-INT(LOG10(ABS(H21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA21" s="7" t="e" cm="1">
-        <f t="array" ref="AA21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(I21,2-INT(LOG10(ABS(I21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB21" s="7" t="e" cm="1">
-        <f t="array" ref="AB21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(J21,2-INT(LOG10(ABS(J21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC21" s="7" t="e" cm="1">
-        <f t="array" ref="AC21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(K21,2-INT(LOG10(ABS(K21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD21" s="7" t="e" cm="1">
-        <f t="array" ref="AD21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(L21,2-INT(LOG10(ABS(L21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE21" s="7" t="e" cm="1">
-        <f t="array" ref="AE21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(M21,2-INT(LOG10(ABS(M21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF21" s="7" t="e" cm="1">
-        <f t="array" ref="AF21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(N21,2-INT(LOG10(ABS(N21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG21" s="7" t="e" cm="1">
-        <f t="array" ref="AG21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(O21,2-INT(LOG10(ABS(O21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH21" s="7" t="e" cm="1">
-        <f t="array" ref="AH21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(P21,2-INT(LOG10(ABS(P21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI21" s="7" t="e" cm="1">
-        <f t="array" ref="AI21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(Q21,2-INT(LOG10(ABS(Q21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ21" s="7" t="e" cm="1">
-        <f t="array" ref="AJ21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(R21,2-INT(LOG10(ABS(R21))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V21" s="7" t="e">
+        <f t="shared" ref="V21:AJ21" si="7">_xlfn.RANK.EQ(D21,$D21:$R21,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W21" s="7" t="e">
+        <f t="shared" si="7"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X21" s="7" t="e">
+        <f t="shared" si="7"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y21" s="7" t="e">
+        <f t="shared" si="7"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z21" s="7" t="e">
+        <f t="shared" si="7"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA21" s="7" t="e">
+        <f t="shared" si="7"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB21" s="7" t="e">
+        <f t="shared" si="7"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC21" s="7" t="e">
+        <f t="shared" si="7"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD21" s="7" t="e">
+        <f t="shared" si="7"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE21" s="7" t="e">
+        <f t="shared" si="7"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF21" s="7" t="e">
+        <f t="shared" si="7"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG21" s="7" t="e">
+        <f t="shared" si="7"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH21" s="7" t="e">
+        <f t="shared" si="7"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI21" s="7" t="e">
+        <f t="shared" si="7"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ21" s="7" t="e">
+        <f t="shared" si="7"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A22" s="24"/>
-      <c r="B22" s="20" t="s">
+      <c r="A22" s="21"/>
+      <c r="B22" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="9" t="s">
         <v>114</v>
       </c>
       <c r="D22" s="8"/>
@@ -3476,7 +3202,7 @@
       <c r="Q22" s="8"/>
       <c r="R22" s="8"/>
       <c r="S22" s="14"/>
-      <c r="T22" s="20" t="s">
+      <c r="T22" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V22" s="7"/>
@@ -3492,11 +3218,11 @@
       <c r="AF22" s="7"/>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A23" s="24"/>
-      <c r="B23" s="21" t="s">
+      <c r="A23" s="21"/>
+      <c r="B23" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="5" t="s">
         <v>115</v>
       </c>
       <c r="D23" s="6"/>
@@ -3515,7 +3241,7 @@
       <c r="Q23" s="6"/>
       <c r="R23" s="6"/>
       <c r="S23" s="4"/>
-      <c r="T23" s="21" t="s">
+      <c r="T23" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V23" s="7"/>
@@ -3531,11 +3257,11 @@
       <c r="AF23" s="7"/>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A24" s="24"/>
-      <c r="B24" s="22" t="s">
+      <c r="A24" s="21"/>
+      <c r="B24" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="2" t="s">
         <v>116</v>
       </c>
       <c r="D24" s="3"/>
@@ -3556,76 +3282,76 @@
       <c r="S24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="T24" s="22" t="s">
+      <c r="T24" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V24" s="7" t="e" cm="1">
-        <f t="array" ref="V24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(D24,2-INT(LOG10(ABS(D24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W24" s="7" t="e" cm="1">
-        <f t="array" ref="W24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(E24,2-INT(LOG10(ABS(E24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X24" s="7" t="e" cm="1">
-        <f t="array" ref="X24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(F24,2-INT(LOG10(ABS(F24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y24" s="7" t="e" cm="1">
-        <f t="array" ref="Y24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(G24,2-INT(LOG10(ABS(G24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z24" s="7" t="e" cm="1">
-        <f t="array" ref="Z24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(H24,2-INT(LOG10(ABS(H24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA24" s="7" t="e" cm="1">
-        <f t="array" ref="AA24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(I24,2-INT(LOG10(ABS(I24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB24" s="7" t="e" cm="1">
-        <f t="array" ref="AB24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(J24,2-INT(LOG10(ABS(J24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC24" s="7" t="e" cm="1">
-        <f t="array" ref="AC24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(K24,2-INT(LOG10(ABS(K24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD24" s="7" t="e" cm="1">
-        <f t="array" ref="AD24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(L24,2-INT(LOG10(ABS(L24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE24" s="7" t="e" cm="1">
-        <f t="array" ref="AE24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(M24,2-INT(LOG10(ABS(M24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF24" s="7" t="e" cm="1">
-        <f t="array" ref="AF24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(N24,2-INT(LOG10(ABS(N24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG24" s="7" t="e" cm="1">
-        <f t="array" ref="AG24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(O24,2-INT(LOG10(ABS(O24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH24" s="7" t="e" cm="1">
-        <f t="array" ref="AH24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(P24,2-INT(LOG10(ABS(P24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI24" s="7" t="e" cm="1">
-        <f t="array" ref="AI24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(Q24,2-INT(LOG10(ABS(Q24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ24" s="7" t="e" cm="1">
-        <f t="array" ref="AJ24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(R24,2-INT(LOG10(ABS(R24))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V24" s="7" t="e">
+        <f t="shared" ref="V24:AJ24" si="8">_xlfn.RANK.EQ(D24,$D24:$R24,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W24" s="7" t="e">
+        <f t="shared" si="8"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X24" s="7" t="e">
+        <f t="shared" si="8"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y24" s="7" t="e">
+        <f t="shared" si="8"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z24" s="7" t="e">
+        <f t="shared" si="8"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA24" s="7" t="e">
+        <f t="shared" si="8"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB24" s="7" t="e">
+        <f t="shared" si="8"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC24" s="7" t="e">
+        <f t="shared" si="8"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD24" s="7" t="e">
+        <f t="shared" si="8"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE24" s="7" t="e">
+        <f t="shared" si="8"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF24" s="7" t="e">
+        <f t="shared" si="8"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG24" s="7" t="e">
+        <f t="shared" si="8"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH24" s="7" t="e">
+        <f t="shared" si="8"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI24" s="7" t="e">
+        <f t="shared" si="8"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ24" s="7" t="e">
+        <f t="shared" si="8"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="20" t="s">
+      <c r="A25" s="21"/>
+      <c r="B25" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="C25" s="9" t="s">
         <v>117</v>
       </c>
       <c r="D25" s="8"/>
@@ -3644,7 +3370,7 @@
       <c r="Q25" s="8"/>
       <c r="R25" s="8"/>
       <c r="S25" s="14"/>
-      <c r="T25" s="20" t="s">
+      <c r="T25" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V25" s="7"/>
@@ -3660,11 +3386,11 @@
       <c r="AF25" s="7"/>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A26" s="24"/>
-      <c r="B26" s="21" t="s">
+      <c r="A26" s="21"/>
+      <c r="B26" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="21" t="s">
+      <c r="C26" s="5" t="s">
         <v>118</v>
       </c>
       <c r="D26" s="6"/>
@@ -3683,7 +3409,7 @@
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="4"/>
-      <c r="T26" s="21" t="s">
+      <c r="T26" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V26" s="7"/>
@@ -3699,11 +3425,11 @@
       <c r="AF26" s="7"/>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A27" s="24"/>
-      <c r="B27" s="22" t="s">
+      <c r="A27" s="21"/>
+      <c r="B27" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="2" t="s">
         <v>119</v>
       </c>
       <c r="D27" s="3"/>
@@ -3724,76 +3450,76 @@
       <c r="S27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="T27" s="22" t="s">
+      <c r="T27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V27" s="7" t="e" cm="1">
-        <f t="array" ref="V27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(D27,2-INT(LOG10(ABS(D27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W27" s="7" t="e" cm="1">
-        <f t="array" ref="W27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(E27,2-INT(LOG10(ABS(E27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X27" s="7" t="e" cm="1">
-        <f t="array" ref="X27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(F27,2-INT(LOG10(ABS(F27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y27" s="7" t="e" cm="1">
-        <f t="array" ref="Y27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(G27,2-INT(LOG10(ABS(G27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z27" s="7" t="e" cm="1">
-        <f t="array" ref="Z27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(H27,2-INT(LOG10(ABS(H27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA27" s="7" t="e" cm="1">
-        <f t="array" ref="AA27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(I27,2-INT(LOG10(ABS(I27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB27" s="7" t="e" cm="1">
-        <f t="array" ref="AB27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(J27,2-INT(LOG10(ABS(J27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC27" s="7" t="e" cm="1">
-        <f t="array" ref="AC27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(K27,2-INT(LOG10(ABS(K27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD27" s="7" t="e" cm="1">
-        <f t="array" ref="AD27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(L27,2-INT(LOG10(ABS(L27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE27" s="7" t="e" cm="1">
-        <f t="array" ref="AE27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(M27,2-INT(LOG10(ABS(M27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF27" s="7" t="e" cm="1">
-        <f t="array" ref="AF27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(N27,2-INT(LOG10(ABS(N27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG27" s="7" t="e" cm="1">
-        <f t="array" ref="AG27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(O27,2-INT(LOG10(ABS(O27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH27" s="7" t="e" cm="1">
-        <f t="array" ref="AH27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(P27,2-INT(LOG10(ABS(P27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI27" s="7" t="e" cm="1">
-        <f t="array" ref="AI27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(Q27,2-INT(LOG10(ABS(Q27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ27" s="7" t="e" cm="1">
-        <f t="array" ref="AJ27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(R27,2-INT(LOG10(ABS(R27))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V27" s="7" t="e">
+        <f t="shared" ref="V27:AJ27" si="9">_xlfn.RANK.EQ(D27,$D27:$R27,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W27" s="7" t="e">
+        <f t="shared" si="9"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X27" s="7" t="e">
+        <f t="shared" si="9"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y27" s="7" t="e">
+        <f t="shared" si="9"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z27" s="7" t="e">
+        <f t="shared" si="9"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA27" s="7" t="e">
+        <f t="shared" si="9"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB27" s="7" t="e">
+        <f t="shared" si="9"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC27" s="7" t="e">
+        <f t="shared" si="9"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD27" s="7" t="e">
+        <f t="shared" si="9"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE27" s="7" t="e">
+        <f t="shared" si="9"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF27" s="7" t="e">
+        <f t="shared" si="9"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG27" s="7" t="e">
+        <f t="shared" si="9"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH27" s="7" t="e">
+        <f t="shared" si="9"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI27" s="7" t="e">
+        <f t="shared" si="9"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ27" s="7" t="e">
+        <f t="shared" si="9"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A28" s="24"/>
-      <c r="B28" s="20" t="s">
+      <c r="A28" s="21"/>
+      <c r="B28" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="9" t="s">
         <v>120</v>
       </c>
       <c r="D28" s="8"/>
@@ -3812,7 +3538,7 @@
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
       <c r="S28" s="14"/>
-      <c r="T28" s="20" t="s">
+      <c r="T28" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V28" s="7"/>
@@ -3828,11 +3554,11 @@
       <c r="AF28" s="7"/>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A29" s="24"/>
-      <c r="B29" s="21" t="s">
+      <c r="A29" s="21"/>
+      <c r="B29" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="21" t="s">
+      <c r="C29" s="5" t="s">
         <v>121</v>
       </c>
       <c r="D29" s="6"/>
@@ -3851,7 +3577,7 @@
       <c r="Q29" s="6"/>
       <c r="R29" s="6"/>
       <c r="S29" s="4"/>
-      <c r="T29" s="21" t="s">
+      <c r="T29" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V29" s="7"/>
@@ -3867,11 +3593,11 @@
       <c r="AF29" s="7"/>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A30" s="24"/>
-      <c r="B30" s="22" t="s">
+      <c r="A30" s="21"/>
+      <c r="B30" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C30" s="22" t="s">
+      <c r="C30" s="2" t="s">
         <v>122</v>
       </c>
       <c r="D30" s="3"/>
@@ -3892,76 +3618,76 @@
       <c r="S30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="T30" s="22" t="s">
+      <c r="T30" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V30" s="7" t="e" cm="1">
-        <f t="array" ref="V30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(D30,2-INT(LOG10(ABS(D30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W30" s="7" t="e" cm="1">
-        <f t="array" ref="W30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(E30,2-INT(LOG10(ABS(E30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X30" s="7" t="e" cm="1">
-        <f t="array" ref="X30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(F30,2-INT(LOG10(ABS(F30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y30" s="7" t="e" cm="1">
-        <f t="array" ref="Y30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(G30,2-INT(LOG10(ABS(G30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z30" s="7" t="e" cm="1">
-        <f t="array" ref="Z30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(H30,2-INT(LOG10(ABS(H30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA30" s="7" t="e" cm="1">
-        <f t="array" ref="AA30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(I30,2-INT(LOG10(ABS(I30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB30" s="7" t="e" cm="1">
-        <f t="array" ref="AB30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(J30,2-INT(LOG10(ABS(J30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC30" s="7" t="e" cm="1">
-        <f t="array" ref="AC30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(K30,2-INT(LOG10(ABS(K30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD30" s="7" t="e" cm="1">
-        <f t="array" ref="AD30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(L30,2-INT(LOG10(ABS(L30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE30" s="7" t="e" cm="1">
-        <f t="array" ref="AE30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(M30,2-INT(LOG10(ABS(M30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF30" s="7" t="e" cm="1">
-        <f t="array" ref="AF30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(N30,2-INT(LOG10(ABS(N30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG30" s="7" t="e" cm="1">
-        <f t="array" ref="AG30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(O30,2-INT(LOG10(ABS(O30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH30" s="7" t="e" cm="1">
-        <f t="array" ref="AH30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(P30,2-INT(LOG10(ABS(P30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI30" s="7" t="e" cm="1">
-        <f t="array" ref="AI30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(Q30,2-INT(LOG10(ABS(Q30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ30" s="7" t="e" cm="1">
-        <f t="array" ref="AJ30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(R30,2-INT(LOG10(ABS(R30))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V30" s="7" t="e">
+        <f t="shared" ref="V30:AJ30" si="10">_xlfn.RANK.EQ(D30,$D30:$R30,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W30" s="7" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X30" s="7" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y30" s="7" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z30" s="7" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA30" s="7" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB30" s="7" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC30" s="7" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD30" s="7" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE30" s="7" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF30" s="7" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG30" s="7" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH30" s="7" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI30" s="7" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ30" s="7" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A31" s="24"/>
-      <c r="B31" s="20" t="s">
+      <c r="A31" s="21"/>
+      <c r="B31" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="9" t="s">
         <v>123</v>
       </c>
       <c r="D31" s="8"/>
@@ -3980,7 +3706,7 @@
       <c r="Q31" s="8"/>
       <c r="R31" s="8"/>
       <c r="S31" s="14"/>
-      <c r="T31" s="20" t="s">
+      <c r="T31" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V31" s="7"/>
@@ -3996,11 +3722,11 @@
       <c r="AF31" s="7"/>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A32" s="24"/>
-      <c r="B32" s="21" t="s">
+      <c r="A32" s="21"/>
+      <c r="B32" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="5" t="s">
         <v>124</v>
       </c>
       <c r="D32" s="6"/>
@@ -4019,7 +3745,7 @@
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="4"/>
-      <c r="T32" s="21" t="s">
+      <c r="T32" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V32" s="7"/>
@@ -4035,11 +3761,11 @@
       <c r="AF32" s="7"/>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A33" s="24"/>
-      <c r="B33" s="22" t="s">
+      <c r="A33" s="21"/>
+      <c r="B33" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="2" t="s">
         <v>125</v>
       </c>
       <c r="D33" s="3"/>
@@ -4060,76 +3786,76 @@
       <c r="S33" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="T33" s="22" t="s">
+      <c r="T33" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V33" s="7" t="e" cm="1">
-        <f t="array" ref="V33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(D33,2-INT(LOG10(ABS(D33))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W33" s="7" t="e" cm="1">
-        <f t="array" ref="W33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(E33,2-INT(LOG10(ABS(E33))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X33" s="7" t="e" cm="1">
-        <f t="array" ref="X33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(F33,2-INT(LOG10(ABS(F33))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y33" s="7" t="e" cm="1">
-        <f t="array" ref="Y33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(G33,2-INT(LOG10(ABS(G33))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z33" s="7" t="e" cm="1">
-        <f t="array" ref="Z33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(H33,2-INT(LOG10(ABS(H33))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA33" s="7" t="e" cm="1">
-        <f t="array" ref="AA33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(I33,2-INT(LOG10(ABS(I33))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB33" s="7" t="e" cm="1">
-        <f t="array" ref="AB33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(J33,2-INT(LOG10(ABS(J33))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC33" s="7" t="e" cm="1">
-        <f t="array" ref="AC33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(K33,2-INT(LOG10(ABS(K33))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD33" s="7" t="e" cm="1">
-        <f t="array" ref="AD33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(L33,2-INT(LOG10(ABS(L33))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE33" s="7" t="e" cm="1">
-        <f t="array" ref="AE33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(M33,2-INT(LOG10(ABS(M33))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF33" s="7" t="e" cm="1">
-        <f t="array" ref="AF33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(N33,2-INT(LOG10(ABS(N33))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG33" s="7" t="e" cm="1">
-        <f t="array" ref="AG33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(O33,2-INT(LOG10(ABS(O33))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH33" s="7" t="e" cm="1">
-        <f t="array" ref="AH33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(P33,2-INT(LOG10(ABS(P33))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI33" s="7" t="e" cm="1">
-        <f t="array" ref="AI33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(Q33,2-INT(LOG10(ABS(Q33))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ33" s="7" t="e" cm="1">
-        <f t="array" ref="AJ33">SUMPRODUCT(--(ROUND($D33:$R33,2-INT(LOG10(ABS($D33:$R33))))&lt;ROUND(R33,2-INT(LOG10(ABS(R33))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V33" s="7" t="e">
+        <f t="shared" ref="V33:AJ33" si="11">_xlfn.RANK.EQ(D33,$D33:$R33,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W33" s="7" t="e">
+        <f t="shared" si="11"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X33" s="7" t="e">
+        <f t="shared" si="11"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y33" s="7" t="e">
+        <f t="shared" si="11"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z33" s="7" t="e">
+        <f t="shared" si="11"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA33" s="7" t="e">
+        <f t="shared" si="11"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB33" s="7" t="e">
+        <f t="shared" si="11"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC33" s="7" t="e">
+        <f t="shared" si="11"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD33" s="7" t="e">
+        <f t="shared" si="11"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE33" s="7" t="e">
+        <f t="shared" si="11"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF33" s="7" t="e">
+        <f t="shared" si="11"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG33" s="7" t="e">
+        <f t="shared" si="11"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH33" s="7" t="e">
+        <f t="shared" si="11"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI33" s="7" t="e">
+        <f t="shared" si="11"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ33" s="7" t="e">
+        <f t="shared" si="11"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A34" s="24"/>
-      <c r="B34" s="20" t="s">
+      <c r="A34" s="21"/>
+      <c r="B34" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="9" t="s">
         <v>126</v>
       </c>
       <c r="D34" s="8"/>
@@ -4148,7 +3874,7 @@
       <c r="Q34" s="8"/>
       <c r="R34" s="8"/>
       <c r="S34" s="14"/>
-      <c r="T34" s="20" t="s">
+      <c r="T34" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V34" s="7"/>
@@ -4164,11 +3890,11 @@
       <c r="AF34" s="7"/>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A35" s="24"/>
-      <c r="B35" s="21" t="s">
+      <c r="A35" s="21"/>
+      <c r="B35" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C35" s="21" t="s">
+      <c r="C35" s="5" t="s">
         <v>127</v>
       </c>
       <c r="D35" s="6"/>
@@ -4187,7 +3913,7 @@
       <c r="Q35" s="6"/>
       <c r="R35" s="6"/>
       <c r="S35" s="4"/>
-      <c r="T35" s="21" t="s">
+      <c r="T35" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V35" s="7"/>
@@ -4203,11 +3929,11 @@
       <c r="AF35" s="7"/>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A36" s="24"/>
-      <c r="B36" s="22" t="s">
+      <c r="A36" s="21"/>
+      <c r="B36" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C36" s="22" t="s">
+      <c r="C36" s="2" t="s">
         <v>128</v>
       </c>
       <c r="D36" s="3"/>
@@ -4228,76 +3954,76 @@
       <c r="S36" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="T36" s="22" t="s">
+      <c r="T36" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V36" s="7" t="e" cm="1">
-        <f t="array" ref="V36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(D36,2-INT(LOG10(ABS(D36))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W36" s="7" t="e" cm="1">
-        <f t="array" ref="W36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(E36,2-INT(LOG10(ABS(E36))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X36" s="7" t="e" cm="1">
-        <f t="array" ref="X36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(F36,2-INT(LOG10(ABS(F36))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y36" s="7" t="e" cm="1">
-        <f t="array" ref="Y36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(G36,2-INT(LOG10(ABS(G36))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z36" s="7" t="e" cm="1">
-        <f t="array" ref="Z36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(H36,2-INT(LOG10(ABS(H36))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA36" s="7" t="e" cm="1">
-        <f t="array" ref="AA36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(I36,2-INT(LOG10(ABS(I36))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB36" s="7" t="e" cm="1">
-        <f t="array" ref="AB36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(J36,2-INT(LOG10(ABS(J36))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC36" s="7" t="e" cm="1">
-        <f t="array" ref="AC36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(K36,2-INT(LOG10(ABS(K36))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD36" s="7" t="e" cm="1">
-        <f t="array" ref="AD36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(L36,2-INT(LOG10(ABS(L36))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE36" s="7" t="e" cm="1">
-        <f t="array" ref="AE36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(M36,2-INT(LOG10(ABS(M36))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF36" s="7" t="e" cm="1">
-        <f t="array" ref="AF36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(N36,2-INT(LOG10(ABS(N36))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG36" s="7" t="e" cm="1">
-        <f t="array" ref="AG36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(O36,2-INT(LOG10(ABS(O36))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH36" s="7" t="e" cm="1">
-        <f t="array" ref="AH36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(P36,2-INT(LOG10(ABS(P36))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI36" s="7" t="e" cm="1">
-        <f t="array" ref="AI36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(Q36,2-INT(LOG10(ABS(Q36))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ36" s="7" t="e" cm="1">
-        <f t="array" ref="AJ36">SUMPRODUCT(--(ROUND($D36:$R36,2-INT(LOG10(ABS($D36:$R36))))&lt;ROUND(R36,2-INT(LOG10(ABS(R36))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V36" s="7" t="e">
+        <f t="shared" ref="V36:AJ36" si="12">_xlfn.RANK.EQ(D36,$D36:$R36,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W36" s="7" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X36" s="7" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y36" s="7" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z36" s="7" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA36" s="7" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB36" s="7" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC36" s="7" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD36" s="7" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE36" s="7" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF36" s="7" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG36" s="7" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH36" s="7" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI36" s="7" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ36" s="7" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A37" s="24"/>
-      <c r="B37" s="20" t="s">
+      <c r="A37" s="21"/>
+      <c r="B37" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="20" t="s">
+      <c r="C37" s="9" t="s">
         <v>129</v>
       </c>
       <c r="D37" s="8"/>
@@ -4316,7 +4042,7 @@
       <c r="Q37" s="8"/>
       <c r="R37" s="8"/>
       <c r="S37" s="14"/>
-      <c r="T37" s="20" t="s">
+      <c r="T37" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V37" s="7"/>
@@ -4332,11 +4058,11 @@
       <c r="AF37" s="7"/>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A38" s="24"/>
-      <c r="B38" s="21" t="s">
+      <c r="A38" s="21"/>
+      <c r="B38" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="21" t="s">
+      <c r="C38" s="5" t="s">
         <v>130</v>
       </c>
       <c r="D38" s="6"/>
@@ -4355,7 +4081,7 @@
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
       <c r="S38" s="4"/>
-      <c r="T38" s="21" t="s">
+      <c r="T38" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V38" s="7"/>
@@ -4371,11 +4097,11 @@
       <c r="AF38" s="7"/>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
-      <c r="B39" s="22" t="s">
+      <c r="A39" s="21"/>
+      <c r="B39" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="22" t="s">
+      <c r="C39" s="2" t="s">
         <v>131</v>
       </c>
       <c r="D39" s="3"/>
@@ -4396,76 +4122,76 @@
       <c r="S39" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="T39" s="22" t="s">
+      <c r="T39" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V39" s="7" t="e" cm="1">
-        <f t="array" ref="V39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(D39,2-INT(LOG10(ABS(D39))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W39" s="7" t="e" cm="1">
-        <f t="array" ref="W39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(E39,2-INT(LOG10(ABS(E39))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X39" s="7" t="e" cm="1">
-        <f t="array" ref="X39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(F39,2-INT(LOG10(ABS(F39))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y39" s="7" t="e" cm="1">
-        <f t="array" ref="Y39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(G39,2-INT(LOG10(ABS(G39))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z39" s="7" t="e" cm="1">
-        <f t="array" ref="Z39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(H39,2-INT(LOG10(ABS(H39))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA39" s="7" t="e" cm="1">
-        <f t="array" ref="AA39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(I39,2-INT(LOG10(ABS(I39))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB39" s="7" t="e" cm="1">
-        <f t="array" ref="AB39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(J39,2-INT(LOG10(ABS(J39))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC39" s="7" t="e" cm="1">
-        <f t="array" ref="AC39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(K39,2-INT(LOG10(ABS(K39))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD39" s="7" t="e" cm="1">
-        <f t="array" ref="AD39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(L39,2-INT(LOG10(ABS(L39))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE39" s="7" t="e" cm="1">
-        <f t="array" ref="AE39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(M39,2-INT(LOG10(ABS(M39))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF39" s="7" t="e" cm="1">
-        <f t="array" ref="AF39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(N39,2-INT(LOG10(ABS(N39))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG39" s="7" t="e" cm="1">
-        <f t="array" ref="AG39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(O39,2-INT(LOG10(ABS(O39))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH39" s="7" t="e" cm="1">
-        <f t="array" ref="AH39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(P39,2-INT(LOG10(ABS(P39))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI39" s="7" t="e" cm="1">
-        <f t="array" ref="AI39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(Q39,2-INT(LOG10(ABS(Q39))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ39" s="7" t="e" cm="1">
-        <f t="array" ref="AJ39">SUMPRODUCT(--(ROUND($D39:$R39,2-INT(LOG10(ABS($D39:$R39))))&lt;ROUND(R39,2-INT(LOG10(ABS(R39))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V39" s="7" t="e">
+        <f t="shared" ref="V39:AJ39" si="13">_xlfn.RANK.EQ(D39,$D39:$R39,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W39" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X39" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y39" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z39" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA39" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB39" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC39" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD39" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE39" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF39" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG39" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH39" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI39" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ39" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A40" s="24"/>
-      <c r="B40" s="20" t="s">
+      <c r="A40" s="21"/>
+      <c r="B40" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C40" s="20" t="s">
+      <c r="C40" s="9" t="s">
         <v>132</v>
       </c>
       <c r="D40" s="8"/>
@@ -4484,7 +4210,7 @@
       <c r="Q40" s="8"/>
       <c r="R40" s="8"/>
       <c r="S40" s="14"/>
-      <c r="T40" s="20" t="s">
+      <c r="T40" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V40" s="7"/>
@@ -4500,11 +4226,11 @@
       <c r="AF40" s="7"/>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A41" s="24"/>
-      <c r="B41" s="21" t="s">
+      <c r="A41" s="21"/>
+      <c r="B41" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="C41" s="5" t="s">
         <v>133</v>
       </c>
       <c r="D41" s="6"/>
@@ -4523,7 +4249,7 @@
       <c r="Q41" s="6"/>
       <c r="R41" s="6"/>
       <c r="S41" s="4"/>
-      <c r="T41" s="21" t="s">
+      <c r="T41" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V41" s="7"/>
@@ -4539,11 +4265,11 @@
       <c r="AF41" s="7"/>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A42" s="24"/>
-      <c r="B42" s="22" t="s">
+      <c r="A42" s="21"/>
+      <c r="B42" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C42" s="22" t="s">
+      <c r="C42" s="2" t="s">
         <v>134</v>
       </c>
       <c r="D42" s="3"/>
@@ -4564,76 +4290,76 @@
       <c r="S42" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T42" s="22" t="s">
+      <c r="T42" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V42" s="7" t="e" cm="1">
-        <f t="array" ref="V42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(D42,2-INT(LOG10(ABS(D42))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W42" s="7" t="e" cm="1">
-        <f t="array" ref="W42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(E42,2-INT(LOG10(ABS(E42))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X42" s="7" t="e" cm="1">
-        <f t="array" ref="X42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(F42,2-INT(LOG10(ABS(F42))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y42" s="7" t="e" cm="1">
-        <f t="array" ref="Y42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(G42,2-INT(LOG10(ABS(G42))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z42" s="7" t="e" cm="1">
-        <f t="array" ref="Z42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(H42,2-INT(LOG10(ABS(H42))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA42" s="7" t="e" cm="1">
-        <f t="array" ref="AA42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(I42,2-INT(LOG10(ABS(I42))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB42" s="7" t="e" cm="1">
-        <f t="array" ref="AB42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(J42,2-INT(LOG10(ABS(J42))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC42" s="7" t="e" cm="1">
-        <f t="array" ref="AC42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(K42,2-INT(LOG10(ABS(K42))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD42" s="7" t="e" cm="1">
-        <f t="array" ref="AD42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(L42,2-INT(LOG10(ABS(L42))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE42" s="7" t="e" cm="1">
-        <f t="array" ref="AE42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(M42,2-INT(LOG10(ABS(M42))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF42" s="7" t="e" cm="1">
-        <f t="array" ref="AF42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(N42,2-INT(LOG10(ABS(N42))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG42" s="7" t="e" cm="1">
-        <f t="array" ref="AG42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(O42,2-INT(LOG10(ABS(O42))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH42" s="7" t="e" cm="1">
-        <f t="array" ref="AH42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(P42,2-INT(LOG10(ABS(P42))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI42" s="7" t="e" cm="1">
-        <f t="array" ref="AI42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(Q42,2-INT(LOG10(ABS(Q42))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ42" s="7" t="e" cm="1">
-        <f t="array" ref="AJ42">SUMPRODUCT(--(ROUND($D42:$R42,2-INT(LOG10(ABS($D42:$R42))))&lt;ROUND(R42,2-INT(LOG10(ABS(R42))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V42" s="7" t="e">
+        <f t="shared" ref="V42:AJ42" si="14">_xlfn.RANK.EQ(D42,$D42:$R42,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W42" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X42" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y42" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z42" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA42" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB42" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC42" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD42" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE42" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF42" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG42" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH42" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI42" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ42" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A43" s="24"/>
-      <c r="B43" s="20" t="s">
+      <c r="A43" s="21"/>
+      <c r="B43" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C43" s="20" t="s">
+      <c r="C43" s="9" t="s">
         <v>135</v>
       </c>
       <c r="D43" s="8"/>
@@ -4652,7 +4378,7 @@
       <c r="Q43" s="8"/>
       <c r="R43" s="8"/>
       <c r="S43" s="14"/>
-      <c r="T43" s="20" t="s">
+      <c r="T43" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V43" s="7"/>
@@ -4668,11 +4394,11 @@
       <c r="AF43" s="7"/>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A44" s="24"/>
-      <c r="B44" s="21" t="s">
+      <c r="A44" s="21"/>
+      <c r="B44" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C44" s="21" t="s">
+      <c r="C44" s="5" t="s">
         <v>136</v>
       </c>
       <c r="D44" s="6"/>
@@ -4691,7 +4417,7 @@
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
       <c r="S44" s="4"/>
-      <c r="T44" s="21" t="s">
+      <c r="T44" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V44" s="7"/>
@@ -4707,11 +4433,11 @@
       <c r="AF44" s="7"/>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A45" s="24"/>
-      <c r="B45" s="22" t="s">
+      <c r="A45" s="21"/>
+      <c r="B45" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C45" s="22" t="s">
+      <c r="C45" s="2" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="3"/>
@@ -4732,76 +4458,76 @@
       <c r="S45" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="T45" s="22" t="s">
+      <c r="T45" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V45" s="7" t="e" cm="1">
-        <f t="array" ref="V45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(D45,2-INT(LOG10(ABS(D45))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W45" s="7" t="e" cm="1">
-        <f t="array" ref="W45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(E45,2-INT(LOG10(ABS(E45))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X45" s="7" t="e" cm="1">
-        <f t="array" ref="X45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(F45,2-INT(LOG10(ABS(F45))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y45" s="7" t="e" cm="1">
-        <f t="array" ref="Y45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(G45,2-INT(LOG10(ABS(G45))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z45" s="7" t="e" cm="1">
-        <f t="array" ref="Z45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(H45,2-INT(LOG10(ABS(H45))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA45" s="7" t="e" cm="1">
-        <f t="array" ref="AA45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(I45,2-INT(LOG10(ABS(I45))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB45" s="7" t="e" cm="1">
-        <f t="array" ref="AB45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(J45,2-INT(LOG10(ABS(J45))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC45" s="7" t="e" cm="1">
-        <f t="array" ref="AC45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(K45,2-INT(LOG10(ABS(K45))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD45" s="7" t="e" cm="1">
-        <f t="array" ref="AD45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(L45,2-INT(LOG10(ABS(L45))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE45" s="7" t="e" cm="1">
-        <f t="array" ref="AE45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(M45,2-INT(LOG10(ABS(M45))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF45" s="7" t="e" cm="1">
-        <f t="array" ref="AF45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(N45,2-INT(LOG10(ABS(N45))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG45" s="7" t="e" cm="1">
-        <f t="array" ref="AG45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(O45,2-INT(LOG10(ABS(O45))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH45" s="7" t="e" cm="1">
-        <f t="array" ref="AH45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(P45,2-INT(LOG10(ABS(P45))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI45" s="7" t="e" cm="1">
-        <f t="array" ref="AI45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(Q45,2-INT(LOG10(ABS(Q45))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ45" s="7" t="e" cm="1">
-        <f t="array" ref="AJ45">SUMPRODUCT(--(ROUND($D45:$R45,2-INT(LOG10(ABS($D45:$R45))))&lt;ROUND(R45,2-INT(LOG10(ABS(R45))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V45" s="7" t="e">
+        <f t="shared" ref="V45:AJ45" si="15">_xlfn.RANK.EQ(D45,$D45:$R45,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W45" s="7" t="e">
+        <f t="shared" si="15"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X45" s="7" t="e">
+        <f t="shared" si="15"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y45" s="7" t="e">
+        <f t="shared" si="15"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z45" s="7" t="e">
+        <f t="shared" si="15"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA45" s="7" t="e">
+        <f t="shared" si="15"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB45" s="7" t="e">
+        <f t="shared" si="15"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC45" s="7" t="e">
+        <f t="shared" si="15"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD45" s="7" t="e">
+        <f t="shared" si="15"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE45" s="7" t="e">
+        <f t="shared" si="15"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF45" s="7" t="e">
+        <f t="shared" si="15"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG45" s="7" t="e">
+        <f t="shared" si="15"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH45" s="7" t="e">
+        <f t="shared" si="15"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI45" s="7" t="e">
+        <f t="shared" si="15"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ45" s="7" t="e">
+        <f t="shared" si="15"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A46" s="24"/>
-      <c r="B46" s="20" t="s">
+      <c r="A46" s="21"/>
+      <c r="B46" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="C46" s="9" t="s">
         <v>138</v>
       </c>
       <c r="D46" s="8"/>
@@ -4820,7 +4546,7 @@
       <c r="Q46" s="8"/>
       <c r="R46" s="8"/>
       <c r="S46" s="14"/>
-      <c r="T46" s="20" t="s">
+      <c r="T46" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V46" s="7"/>
@@ -4836,11 +4562,11 @@
       <c r="AF46" s="7"/>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A47" s="24"/>
-      <c r="B47" s="21" t="s">
+      <c r="A47" s="21"/>
+      <c r="B47" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C47" s="21" t="s">
+      <c r="C47" s="5" t="s">
         <v>139</v>
       </c>
       <c r="D47" s="6"/>
@@ -4859,7 +4585,7 @@
       <c r="Q47" s="6"/>
       <c r="R47" s="6"/>
       <c r="S47" s="4"/>
-      <c r="T47" s="21" t="s">
+      <c r="T47" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V47" s="7"/>
@@ -4875,11 +4601,11 @@
       <c r="AF47" s="7"/>
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A48" s="24"/>
-      <c r="B48" s="22" t="s">
+      <c r="A48" s="21"/>
+      <c r="B48" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C48" s="22" t="s">
+      <c r="C48" s="2" t="s">
         <v>140</v>
       </c>
       <c r="D48" s="3"/>
@@ -4900,76 +4626,76 @@
       <c r="S48" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="T48" s="22" t="s">
+      <c r="T48" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V48" s="7" t="e" cm="1">
-        <f t="array" ref="V48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(D48,2-INT(LOG10(ABS(D48))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W48" s="7" t="e" cm="1">
-        <f t="array" ref="W48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(E48,2-INT(LOG10(ABS(E48))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X48" s="7" t="e" cm="1">
-        <f t="array" ref="X48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(F48,2-INT(LOG10(ABS(F48))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y48" s="7" t="e" cm="1">
-        <f t="array" ref="Y48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(G48,2-INT(LOG10(ABS(G48))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z48" s="7" t="e" cm="1">
-        <f t="array" ref="Z48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(H48,2-INT(LOG10(ABS(H48))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA48" s="7" t="e" cm="1">
-        <f t="array" ref="AA48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(I48,2-INT(LOG10(ABS(I48))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB48" s="7" t="e" cm="1">
-        <f t="array" ref="AB48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(J48,2-INT(LOG10(ABS(J48))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC48" s="7" t="e" cm="1">
-        <f t="array" ref="AC48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(K48,2-INT(LOG10(ABS(K48))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD48" s="7" t="e" cm="1">
-        <f t="array" ref="AD48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(L48,2-INT(LOG10(ABS(L48))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE48" s="7" t="e" cm="1">
-        <f t="array" ref="AE48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(M48,2-INT(LOG10(ABS(M48))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF48" s="7" t="e" cm="1">
-        <f t="array" ref="AF48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(N48,2-INT(LOG10(ABS(N48))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG48" s="7" t="e" cm="1">
-        <f t="array" ref="AG48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(O48,2-INT(LOG10(ABS(O48))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH48" s="7" t="e" cm="1">
-        <f t="array" ref="AH48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(P48,2-INT(LOG10(ABS(P48))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI48" s="7" t="e" cm="1">
-        <f t="array" ref="AI48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(Q48,2-INT(LOG10(ABS(Q48))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ48" s="7" t="e" cm="1">
-        <f t="array" ref="AJ48">SUMPRODUCT(--(ROUND($D48:$R48,2-INT(LOG10(ABS($D48:$R48))))&lt;ROUND(R48,2-INT(LOG10(ABS(R48))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V48" s="7" t="e">
+        <f t="shared" ref="V48:AJ48" si="16">_xlfn.RANK.EQ(D48,$D48:$R48,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W48" s="7" t="e">
+        <f t="shared" si="16"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X48" s="7" t="e">
+        <f t="shared" si="16"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y48" s="7" t="e">
+        <f t="shared" si="16"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z48" s="7" t="e">
+        <f t="shared" si="16"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA48" s="7" t="e">
+        <f t="shared" si="16"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB48" s="7" t="e">
+        <f t="shared" si="16"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC48" s="7" t="e">
+        <f t="shared" si="16"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD48" s="7" t="e">
+        <f t="shared" si="16"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE48" s="7" t="e">
+        <f t="shared" si="16"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF48" s="7" t="e">
+        <f t="shared" si="16"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG48" s="7" t="e">
+        <f t="shared" si="16"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH48" s="7" t="e">
+        <f t="shared" si="16"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI48" s="7" t="e">
+        <f t="shared" si="16"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ48" s="7" t="e">
+        <f t="shared" si="16"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="49" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A49" s="24"/>
-      <c r="B49" s="20" t="s">
+      <c r="A49" s="21"/>
+      <c r="B49" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C49" s="20" t="s">
+      <c r="C49" s="9" t="s">
         <v>141</v>
       </c>
       <c r="D49" s="8"/>
@@ -4988,7 +4714,7 @@
       <c r="Q49" s="8"/>
       <c r="R49" s="8"/>
       <c r="S49" s="14"/>
-      <c r="T49" s="20" t="s">
+      <c r="T49" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V49" s="7"/>
@@ -5004,11 +4730,11 @@
       <c r="AF49" s="7"/>
     </row>
     <row r="50" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A50" s="27"/>
-      <c r="B50" s="21" t="s">
+      <c r="A50" s="24"/>
+      <c r="B50" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C50" s="21" t="s">
+      <c r="C50" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D50" s="6"/>
@@ -5027,7 +4753,7 @@
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
       <c r="S50" s="4"/>
-      <c r="T50" s="21" t="s">
+      <c r="T50" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V50" s="7"/>
@@ -5043,13 +4769,13 @@
       <c r="AF50" s="7"/>
     </row>
     <row r="51" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="29" t="s">
+      <c r="A51" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="B51" s="22" t="s">
+      <c r="B51" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C51" s="22" t="s">
+      <c r="C51" s="2" t="s">
         <v>143</v>
       </c>
       <c r="D51" s="3"/>
@@ -5070,76 +4796,76 @@
       <c r="S51" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T51" s="22" t="s">
+      <c r="T51" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V51" s="7" t="e" cm="1">
-        <f t="array" ref="V51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(D51,2-INT(LOG10(ABS(D51))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W51" s="7" t="e" cm="1">
-        <f t="array" ref="W51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(E51,2-INT(LOG10(ABS(E51))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X51" s="7" t="e" cm="1">
-        <f t="array" ref="X51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(F51,2-INT(LOG10(ABS(F51))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y51" s="7" t="e" cm="1">
-        <f t="array" ref="Y51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(G51,2-INT(LOG10(ABS(G51))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z51" s="7" t="e" cm="1">
-        <f t="array" ref="Z51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(H51,2-INT(LOG10(ABS(H51))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA51" s="7" t="e" cm="1">
-        <f t="array" ref="AA51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(I51,2-INT(LOG10(ABS(I51))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB51" s="7" t="e" cm="1">
-        <f t="array" ref="AB51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(J51,2-INT(LOG10(ABS(J51))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC51" s="7" t="e" cm="1">
-        <f t="array" ref="AC51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(K51,2-INT(LOG10(ABS(K51))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD51" s="7" t="e" cm="1">
-        <f t="array" ref="AD51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(L51,2-INT(LOG10(ABS(L51))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE51" s="7" t="e" cm="1">
-        <f t="array" ref="AE51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(M51,2-INT(LOG10(ABS(M51))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF51" s="7" t="e" cm="1">
-        <f t="array" ref="AF51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(N51,2-INT(LOG10(ABS(N51))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG51" s="7" t="e" cm="1">
-        <f t="array" ref="AG51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(O51,2-INT(LOG10(ABS(O51))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH51" s="7" t="e" cm="1">
-        <f t="array" ref="AH51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(P51,2-INT(LOG10(ABS(P51))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI51" s="7" t="e" cm="1">
-        <f t="array" ref="AI51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(Q51,2-INT(LOG10(ABS(Q51))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ51" s="7" t="e" cm="1">
-        <f t="array" ref="AJ51">SUMPRODUCT(--(ROUND($D51:$R51,2-INT(LOG10(ABS($D51:$R51))))&lt;ROUND(R51,2-INT(LOG10(ABS(R51))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V51" s="7" t="e">
+        <f t="shared" ref="V51:AJ51" si="17">_xlfn.RANK.EQ(D51,$D51:$R51,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W51" s="7" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X51" s="7" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y51" s="7" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z51" s="7" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA51" s="7" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB51" s="7" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC51" s="7" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD51" s="7" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE51" s="7" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF51" s="7" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG51" s="7" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH51" s="7" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI51" s="7" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ51" s="7" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="52" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A52" s="24"/>
-      <c r="B52" s="20" t="s">
+      <c r="A52" s="21"/>
+      <c r="B52" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C52" s="20" t="s">
+      <c r="C52" s="9" t="s">
         <v>144</v>
       </c>
       <c r="D52" s="8"/>
@@ -5158,7 +4884,7 @@
       <c r="Q52" s="8"/>
       <c r="R52" s="8"/>
       <c r="S52" s="14"/>
-      <c r="T52" s="20" t="s">
+      <c r="T52" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V52" s="7"/>
@@ -5174,11 +4900,11 @@
       <c r="AF52" s="7"/>
     </row>
     <row r="53" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A53" s="24"/>
-      <c r="B53" s="21" t="s">
+      <c r="A53" s="21"/>
+      <c r="B53" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C53" s="21" t="s">
+      <c r="C53" s="5" t="s">
         <v>145</v>
       </c>
       <c r="D53" s="6"/>
@@ -5197,7 +4923,7 @@
       <c r="Q53" s="6"/>
       <c r="R53" s="6"/>
       <c r="S53" s="4"/>
-      <c r="T53" s="21" t="s">
+      <c r="T53" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V53" s="7"/>
@@ -5213,11 +4939,11 @@
       <c r="AF53" s="7"/>
     </row>
     <row r="54" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A54" s="24"/>
-      <c r="B54" s="22" t="s">
+      <c r="A54" s="21"/>
+      <c r="B54" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C54" s="22" t="s">
+      <c r="C54" s="2" t="s">
         <v>146</v>
       </c>
       <c r="D54" s="3"/>
@@ -5238,76 +4964,76 @@
       <c r="S54" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="T54" s="22" t="s">
+      <c r="T54" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V54" s="7" t="e" cm="1">
-        <f t="array" ref="V54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(D54,2-INT(LOG10(ABS(D54))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W54" s="7" t="e" cm="1">
-        <f t="array" ref="W54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(E54,2-INT(LOG10(ABS(E54))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X54" s="7" t="e" cm="1">
-        <f t="array" ref="X54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(F54,2-INT(LOG10(ABS(F54))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y54" s="7" t="e" cm="1">
-        <f t="array" ref="Y54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(G54,2-INT(LOG10(ABS(G54))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z54" s="7" t="e" cm="1">
-        <f t="array" ref="Z54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(H54,2-INT(LOG10(ABS(H54))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA54" s="7" t="e" cm="1">
-        <f t="array" ref="AA54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(I54,2-INT(LOG10(ABS(I54))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB54" s="7" t="e" cm="1">
-        <f t="array" ref="AB54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(J54,2-INT(LOG10(ABS(J54))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC54" s="7" t="e" cm="1">
-        <f t="array" ref="AC54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(K54,2-INT(LOG10(ABS(K54))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD54" s="7" t="e" cm="1">
-        <f t="array" ref="AD54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(L54,2-INT(LOG10(ABS(L54))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE54" s="7" t="e" cm="1">
-        <f t="array" ref="AE54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(M54,2-INT(LOG10(ABS(M54))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF54" s="7" t="e" cm="1">
-        <f t="array" ref="AF54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(N54,2-INT(LOG10(ABS(N54))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG54" s="7" t="e" cm="1">
-        <f t="array" ref="AG54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(O54,2-INT(LOG10(ABS(O54))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH54" s="7" t="e" cm="1">
-        <f t="array" ref="AH54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(P54,2-INT(LOG10(ABS(P54))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI54" s="7" t="e" cm="1">
-        <f t="array" ref="AI54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(Q54,2-INT(LOG10(ABS(Q54))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ54" s="7" t="e" cm="1">
-        <f t="array" ref="AJ54">SUMPRODUCT(--(ROUND($D54:$R54,2-INT(LOG10(ABS($D54:$R54))))&lt;ROUND(R54,2-INT(LOG10(ABS(R54))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V54" s="7" t="e">
+        <f t="shared" ref="V54:AJ54" si="18">_xlfn.RANK.EQ(D54,$D54:$R54,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W54" s="7" t="e">
+        <f t="shared" si="18"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X54" s="7" t="e">
+        <f t="shared" si="18"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y54" s="7" t="e">
+        <f t="shared" si="18"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z54" s="7" t="e">
+        <f t="shared" si="18"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA54" s="7" t="e">
+        <f t="shared" si="18"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB54" s="7" t="e">
+        <f t="shared" si="18"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC54" s="7" t="e">
+        <f t="shared" si="18"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD54" s="7" t="e">
+        <f t="shared" si="18"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE54" s="7" t="e">
+        <f t="shared" si="18"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF54" s="7" t="e">
+        <f t="shared" si="18"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG54" s="7" t="e">
+        <f t="shared" si="18"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH54" s="7" t="e">
+        <f t="shared" si="18"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI54" s="7" t="e">
+        <f t="shared" si="18"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ54" s="7" t="e">
+        <f t="shared" si="18"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="55" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A55" s="24"/>
-      <c r="B55" s="20" t="s">
+      <c r="A55" s="21"/>
+      <c r="B55" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C55" s="20" t="s">
+      <c r="C55" s="9" t="s">
         <v>147</v>
       </c>
       <c r="D55" s="8"/>
@@ -5326,7 +5052,7 @@
       <c r="Q55" s="8"/>
       <c r="R55" s="8"/>
       <c r="S55" s="14"/>
-      <c r="T55" s="20" t="s">
+      <c r="T55" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V55" s="7"/>
@@ -5342,11 +5068,11 @@
       <c r="AF55" s="7"/>
     </row>
     <row r="56" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A56" s="24"/>
-      <c r="B56" s="21" t="s">
+      <c r="A56" s="21"/>
+      <c r="B56" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C56" s="21" t="s">
+      <c r="C56" s="5" t="s">
         <v>148</v>
       </c>
       <c r="D56" s="6"/>
@@ -5365,7 +5091,7 @@
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
       <c r="S56" s="4"/>
-      <c r="T56" s="21" t="s">
+      <c r="T56" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V56" s="7"/>
@@ -5381,11 +5107,11 @@
       <c r="AF56" s="7"/>
     </row>
     <row r="57" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A57" s="24"/>
-      <c r="B57" s="22" t="s">
+      <c r="A57" s="21"/>
+      <c r="B57" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C57" s="22" t="s">
+      <c r="C57" s="2" t="s">
         <v>149</v>
       </c>
       <c r="D57" s="3"/>
@@ -5406,76 +5132,76 @@
       <c r="S57" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T57" s="22" t="s">
+      <c r="T57" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V57" s="7" t="e" cm="1">
-        <f t="array" ref="V57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(D57,2-INT(LOG10(ABS(D57))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W57" s="7" t="e" cm="1">
-        <f t="array" ref="W57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(E57,2-INT(LOG10(ABS(E57))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X57" s="7" t="e" cm="1">
-        <f t="array" ref="X57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(F57,2-INT(LOG10(ABS(F57))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y57" s="7" t="e" cm="1">
-        <f t="array" ref="Y57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(G57,2-INT(LOG10(ABS(G57))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z57" s="7" t="e" cm="1">
-        <f t="array" ref="Z57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(H57,2-INT(LOG10(ABS(H57))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA57" s="7" t="e" cm="1">
-        <f t="array" ref="AA57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(I57,2-INT(LOG10(ABS(I57))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB57" s="7" t="e" cm="1">
-        <f t="array" ref="AB57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(J57,2-INT(LOG10(ABS(J57))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC57" s="7" t="e" cm="1">
-        <f t="array" ref="AC57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(K57,2-INT(LOG10(ABS(K57))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD57" s="7" t="e" cm="1">
-        <f t="array" ref="AD57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(L57,2-INT(LOG10(ABS(L57))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE57" s="7" t="e" cm="1">
-        <f t="array" ref="AE57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(M57,2-INT(LOG10(ABS(M57))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF57" s="7" t="e" cm="1">
-        <f t="array" ref="AF57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(N57,2-INT(LOG10(ABS(N57))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG57" s="7" t="e" cm="1">
-        <f t="array" ref="AG57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(O57,2-INT(LOG10(ABS(O57))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH57" s="7" t="e" cm="1">
-        <f t="array" ref="AH57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(P57,2-INT(LOG10(ABS(P57))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI57" s="7" t="e" cm="1">
-        <f t="array" ref="AI57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(Q57,2-INT(LOG10(ABS(Q57))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ57" s="7" t="e" cm="1">
-        <f t="array" ref="AJ57">SUMPRODUCT(--(ROUND($D57:$R57,2-INT(LOG10(ABS($D57:$R57))))&lt;ROUND(R57,2-INT(LOG10(ABS(R57))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V57" s="7" t="e">
+        <f t="shared" ref="V57:AJ57" si="19">_xlfn.RANK.EQ(D57,$D57:$R57,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W57" s="7" t="e">
+        <f t="shared" si="19"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X57" s="7" t="e">
+        <f t="shared" si="19"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y57" s="7" t="e">
+        <f t="shared" si="19"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z57" s="7" t="e">
+        <f t="shared" si="19"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA57" s="7" t="e">
+        <f t="shared" si="19"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB57" s="7" t="e">
+        <f t="shared" si="19"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC57" s="7" t="e">
+        <f t="shared" si="19"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD57" s="7" t="e">
+        <f t="shared" si="19"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE57" s="7" t="e">
+        <f t="shared" si="19"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF57" s="7" t="e">
+        <f t="shared" si="19"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG57" s="7" t="e">
+        <f t="shared" si="19"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH57" s="7" t="e">
+        <f t="shared" si="19"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI57" s="7" t="e">
+        <f t="shared" si="19"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ57" s="7" t="e">
+        <f t="shared" si="19"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="58" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A58" s="24"/>
-      <c r="B58" s="20" t="s">
+      <c r="A58" s="21"/>
+      <c r="B58" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C58" s="20" t="s">
+      <c r="C58" s="9" t="s">
         <v>150</v>
       </c>
       <c r="D58" s="8"/>
@@ -5494,7 +5220,7 @@
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
       <c r="S58" s="14"/>
-      <c r="T58" s="20" t="s">
+      <c r="T58" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V58" s="7"/>
@@ -5510,11 +5236,11 @@
       <c r="AF58" s="7"/>
     </row>
     <row r="59" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A59" s="24"/>
-      <c r="B59" s="21" t="s">
+      <c r="A59" s="21"/>
+      <c r="B59" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C59" s="21" t="s">
+      <c r="C59" s="5" t="s">
         <v>151</v>
       </c>
       <c r="D59" s="6"/>
@@ -5533,7 +5259,7 @@
       <c r="Q59" s="6"/>
       <c r="R59" s="6"/>
       <c r="S59" s="4"/>
-      <c r="T59" s="21" t="s">
+      <c r="T59" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V59" s="7"/>
@@ -5549,11 +5275,11 @@
       <c r="AF59" s="7"/>
     </row>
     <row r="60" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A60" s="24"/>
-      <c r="B60" s="22" t="s">
+      <c r="A60" s="21"/>
+      <c r="B60" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C60" s="22" t="s">
+      <c r="C60" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D60" s="3"/>
@@ -5574,76 +5300,76 @@
       <c r="S60" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="T60" s="22" t="s">
+      <c r="T60" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V60" s="7" t="e" cm="1">
-        <f t="array" ref="V60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(D60,2-INT(LOG10(ABS(D60))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W60" s="7" t="e" cm="1">
-        <f t="array" ref="W60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(E60,2-INT(LOG10(ABS(E60))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X60" s="7" t="e" cm="1">
-        <f t="array" ref="X60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(F60,2-INT(LOG10(ABS(F60))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y60" s="7" t="e" cm="1">
-        <f t="array" ref="Y60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(G60,2-INT(LOG10(ABS(G60))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z60" s="7" t="e" cm="1">
-        <f t="array" ref="Z60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(H60,2-INT(LOG10(ABS(H60))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA60" s="7" t="e" cm="1">
-        <f t="array" ref="AA60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(I60,2-INT(LOG10(ABS(I60))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB60" s="7" t="e" cm="1">
-        <f t="array" ref="AB60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(J60,2-INT(LOG10(ABS(J60))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC60" s="7" t="e" cm="1">
-        <f t="array" ref="AC60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(K60,2-INT(LOG10(ABS(K60))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD60" s="7" t="e" cm="1">
-        <f t="array" ref="AD60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(L60,2-INT(LOG10(ABS(L60))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE60" s="7" t="e" cm="1">
-        <f t="array" ref="AE60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(M60,2-INT(LOG10(ABS(M60))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF60" s="7" t="e" cm="1">
-        <f t="array" ref="AF60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(N60,2-INT(LOG10(ABS(N60))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG60" s="7" t="e" cm="1">
-        <f t="array" ref="AG60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(O60,2-INT(LOG10(ABS(O60))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH60" s="7" t="e" cm="1">
-        <f t="array" ref="AH60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(P60,2-INT(LOG10(ABS(P60))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI60" s="7" t="e" cm="1">
-        <f t="array" ref="AI60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(Q60,2-INT(LOG10(ABS(Q60))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ60" s="7" t="e" cm="1">
-        <f t="array" ref="AJ60">SUMPRODUCT(--(ROUND($D60:$R60,2-INT(LOG10(ABS($D60:$R60))))&lt;ROUND(R60,2-INT(LOG10(ABS(R60))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V60" s="7" t="e">
+        <f t="shared" ref="V60:AJ60" si="20">_xlfn.RANK.EQ(D60,$D60:$R60,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W60" s="7" t="e">
+        <f t="shared" si="20"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X60" s="7" t="e">
+        <f t="shared" si="20"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y60" s="7" t="e">
+        <f t="shared" si="20"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z60" s="7" t="e">
+        <f t="shared" si="20"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA60" s="7" t="e">
+        <f t="shared" si="20"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB60" s="7" t="e">
+        <f t="shared" si="20"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC60" s="7" t="e">
+        <f t="shared" si="20"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD60" s="7" t="e">
+        <f t="shared" si="20"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE60" s="7" t="e">
+        <f t="shared" si="20"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF60" s="7" t="e">
+        <f t="shared" si="20"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG60" s="7" t="e">
+        <f t="shared" si="20"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH60" s="7" t="e">
+        <f t="shared" si="20"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI60" s="7" t="e">
+        <f t="shared" si="20"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ60" s="7" t="e">
+        <f t="shared" si="20"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="61" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A61" s="24"/>
-      <c r="B61" s="20" t="s">
+      <c r="A61" s="21"/>
+      <c r="B61" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C61" s="20" t="s">
+      <c r="C61" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D61" s="8"/>
@@ -5662,7 +5388,7 @@
       <c r="Q61" s="8"/>
       <c r="R61" s="8"/>
       <c r="S61" s="14"/>
-      <c r="T61" s="20" t="s">
+      <c r="T61" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V61" s="7"/>
@@ -5678,11 +5404,11 @@
       <c r="AF61" s="7"/>
     </row>
     <row r="62" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A62" s="24"/>
-      <c r="B62" s="21" t="s">
+      <c r="A62" s="21"/>
+      <c r="B62" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C62" s="21" t="s">
+      <c r="C62" s="5" t="s">
         <v>154</v>
       </c>
       <c r="D62" s="6"/>
@@ -5701,7 +5427,7 @@
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
       <c r="S62" s="4"/>
-      <c r="T62" s="21" t="s">
+      <c r="T62" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V62" s="7"/>
@@ -5717,11 +5443,11 @@
       <c r="AF62" s="7"/>
     </row>
     <row r="63" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A63" s="24"/>
-      <c r="B63" s="22" t="s">
+      <c r="A63" s="21"/>
+      <c r="B63" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C63" s="22" t="s">
+      <c r="C63" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D63" s="3"/>
@@ -5742,76 +5468,76 @@
       <c r="S63" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T63" s="22" t="s">
+      <c r="T63" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V63" s="7" t="e" cm="1">
-        <f t="array" ref="V63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(D63,2-INT(LOG10(ABS(D63))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W63" s="7" t="e" cm="1">
-        <f t="array" ref="W63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(E63,2-INT(LOG10(ABS(E63))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X63" s="7" t="e" cm="1">
-        <f t="array" ref="X63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(F63,2-INT(LOG10(ABS(F63))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y63" s="7" t="e" cm="1">
-        <f t="array" ref="Y63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(G63,2-INT(LOG10(ABS(G63))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z63" s="7" t="e" cm="1">
-        <f t="array" ref="Z63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(H63,2-INT(LOG10(ABS(H63))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA63" s="7" t="e" cm="1">
-        <f t="array" ref="AA63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(I63,2-INT(LOG10(ABS(I63))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB63" s="7" t="e" cm="1">
-        <f t="array" ref="AB63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(J63,2-INT(LOG10(ABS(J63))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC63" s="7" t="e" cm="1">
-        <f t="array" ref="AC63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(K63,2-INT(LOG10(ABS(K63))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD63" s="7" t="e" cm="1">
-        <f t="array" ref="AD63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(L63,2-INT(LOG10(ABS(L63))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE63" s="7" t="e" cm="1">
-        <f t="array" ref="AE63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(M63,2-INT(LOG10(ABS(M63))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF63" s="7" t="e" cm="1">
-        <f t="array" ref="AF63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(N63,2-INT(LOG10(ABS(N63))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG63" s="7" t="e" cm="1">
-        <f t="array" ref="AG63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(O63,2-INT(LOG10(ABS(O63))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH63" s="7" t="e" cm="1">
-        <f t="array" ref="AH63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(P63,2-INT(LOG10(ABS(P63))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI63" s="7" t="e" cm="1">
-        <f t="array" ref="AI63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(Q63,2-INT(LOG10(ABS(Q63))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ63" s="7" t="e" cm="1">
-        <f t="array" ref="AJ63">SUMPRODUCT(--(ROUND($D63:$R63,2-INT(LOG10(ABS($D63:$R63))))&lt;ROUND(R63,2-INT(LOG10(ABS(R63))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V63" s="7" t="e">
+        <f t="shared" ref="V63:AJ63" si="21">_xlfn.RANK.EQ(D63,$D63:$R63,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W63" s="7" t="e">
+        <f t="shared" si="21"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X63" s="7" t="e">
+        <f t="shared" si="21"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y63" s="7" t="e">
+        <f t="shared" si="21"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z63" s="7" t="e">
+        <f t="shared" si="21"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA63" s="7" t="e">
+        <f t="shared" si="21"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB63" s="7" t="e">
+        <f t="shared" si="21"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC63" s="7" t="e">
+        <f t="shared" si="21"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD63" s="7" t="e">
+        <f t="shared" si="21"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE63" s="7" t="e">
+        <f t="shared" si="21"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF63" s="7" t="e">
+        <f t="shared" si="21"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG63" s="7" t="e">
+        <f t="shared" si="21"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH63" s="7" t="e">
+        <f t="shared" si="21"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI63" s="7" t="e">
+        <f t="shared" si="21"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ63" s="7" t="e">
+        <f t="shared" si="21"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="64" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A64" s="24"/>
-      <c r="B64" s="20" t="s">
+      <c r="A64" s="21"/>
+      <c r="B64" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C64" s="20" t="s">
+      <c r="C64" s="9" t="s">
         <v>156</v>
       </c>
       <c r="D64" s="8"/>
@@ -5830,7 +5556,7 @@
       <c r="Q64" s="8"/>
       <c r="R64" s="8"/>
       <c r="S64" s="14"/>
-      <c r="T64" s="20" t="s">
+      <c r="T64" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V64" s="7"/>
@@ -5846,11 +5572,11 @@
       <c r="AF64" s="7"/>
     </row>
     <row r="65" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A65" s="24"/>
-      <c r="B65" s="21" t="s">
+      <c r="A65" s="21"/>
+      <c r="B65" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C65" s="21" t="s">
+      <c r="C65" s="5" t="s">
         <v>157</v>
       </c>
       <c r="D65" s="6"/>
@@ -5869,7 +5595,7 @@
       <c r="Q65" s="6"/>
       <c r="R65" s="6"/>
       <c r="S65" s="4"/>
-      <c r="T65" s="21" t="s">
+      <c r="T65" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V65" s="7"/>
@@ -5885,11 +5611,11 @@
       <c r="AF65" s="7"/>
     </row>
     <row r="66" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A66" s="24"/>
-      <c r="B66" s="22" t="s">
+      <c r="A66" s="21"/>
+      <c r="B66" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C66" s="22" t="s">
+      <c r="C66" s="2" t="s">
         <v>158</v>
       </c>
       <c r="D66" s="3"/>
@@ -5910,76 +5636,76 @@
       <c r="S66" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="T66" s="22" t="s">
+      <c r="T66" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V66" s="7" t="e" cm="1">
-        <f t="array" ref="V66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(D66,2-INT(LOG10(ABS(D66))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W66" s="7" t="e" cm="1">
-        <f t="array" ref="W66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(E66,2-INT(LOG10(ABS(E66))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X66" s="7" t="e" cm="1">
-        <f t="array" ref="X66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(F66,2-INT(LOG10(ABS(F66))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y66" s="7" t="e" cm="1">
-        <f t="array" ref="Y66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(G66,2-INT(LOG10(ABS(G66))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z66" s="7" t="e" cm="1">
-        <f t="array" ref="Z66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(H66,2-INT(LOG10(ABS(H66))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA66" s="7" t="e" cm="1">
-        <f t="array" ref="AA66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(I66,2-INT(LOG10(ABS(I66))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB66" s="7" t="e" cm="1">
-        <f t="array" ref="AB66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(J66,2-INT(LOG10(ABS(J66))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC66" s="7" t="e" cm="1">
-        <f t="array" ref="AC66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(K66,2-INT(LOG10(ABS(K66))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD66" s="7" t="e" cm="1">
-        <f t="array" ref="AD66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(L66,2-INT(LOG10(ABS(L66))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE66" s="7" t="e" cm="1">
-        <f t="array" ref="AE66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(M66,2-INT(LOG10(ABS(M66))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF66" s="7" t="e" cm="1">
-        <f t="array" ref="AF66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(N66,2-INT(LOG10(ABS(N66))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG66" s="7" t="e" cm="1">
-        <f t="array" ref="AG66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(O66,2-INT(LOG10(ABS(O66))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH66" s="7" t="e" cm="1">
-        <f t="array" ref="AH66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(P66,2-INT(LOG10(ABS(P66))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI66" s="7" t="e" cm="1">
-        <f t="array" ref="AI66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(Q66,2-INT(LOG10(ABS(Q66))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ66" s="7" t="e" cm="1">
-        <f t="array" ref="AJ66">SUMPRODUCT(--(ROUND($D66:$R66,2-INT(LOG10(ABS($D66:$R66))))&lt;ROUND(R66,2-INT(LOG10(ABS(R66))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V66" s="7" t="e">
+        <f t="shared" ref="V66:AJ66" si="22">_xlfn.RANK.EQ(D66,$D66:$R66,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W66" s="7" t="e">
+        <f t="shared" si="22"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X66" s="7" t="e">
+        <f t="shared" si="22"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y66" s="7" t="e">
+        <f t="shared" si="22"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z66" s="7" t="e">
+        <f t="shared" si="22"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA66" s="7" t="e">
+        <f t="shared" si="22"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB66" s="7" t="e">
+        <f t="shared" si="22"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC66" s="7" t="e">
+        <f t="shared" si="22"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD66" s="7" t="e">
+        <f t="shared" si="22"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE66" s="7" t="e">
+        <f t="shared" si="22"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF66" s="7" t="e">
+        <f t="shared" si="22"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG66" s="7" t="e">
+        <f t="shared" si="22"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH66" s="7" t="e">
+        <f t="shared" si="22"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI66" s="7" t="e">
+        <f t="shared" si="22"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ66" s="7" t="e">
+        <f t="shared" si="22"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="67" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A67" s="24"/>
-      <c r="B67" s="20" t="s">
+      <c r="A67" s="21"/>
+      <c r="B67" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C67" s="20" t="s">
+      <c r="C67" s="9" t="s">
         <v>159</v>
       </c>
       <c r="D67" s="8"/>
@@ -5998,7 +5724,7 @@
       <c r="Q67" s="8"/>
       <c r="R67" s="8"/>
       <c r="S67" s="14"/>
-      <c r="T67" s="20" t="s">
+      <c r="T67" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V67" s="7"/>
@@ -6014,11 +5740,11 @@
       <c r="AF67" s="7"/>
     </row>
     <row r="68" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A68" s="27"/>
-      <c r="B68" s="21" t="s">
+      <c r="A68" s="24"/>
+      <c r="B68" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C68" s="21" t="s">
+      <c r="C68" s="5" t="s">
         <v>160</v>
       </c>
       <c r="D68" s="6"/>
@@ -6037,7 +5763,7 @@
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
       <c r="S68" s="4"/>
-      <c r="T68" s="21" t="s">
+      <c r="T68" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V68" s="7"/>
@@ -6053,13 +5779,13 @@
       <c r="AF68" s="7"/>
     </row>
     <row r="69" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="29" t="s">
+      <c r="A69" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B69" s="22" t="s">
+      <c r="B69" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C69" s="22" t="s">
+      <c r="C69" s="2" t="s">
         <v>161</v>
       </c>
       <c r="D69" s="3"/>
@@ -6080,76 +5806,76 @@
       <c r="S69" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="T69" s="22" t="s">
+      <c r="T69" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V69" s="7" t="e" cm="1">
-        <f t="array" ref="V69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(D69,2-INT(LOG10(ABS(D69))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W69" s="7" t="e" cm="1">
-        <f t="array" ref="W69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(E69,2-INT(LOG10(ABS(E69))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X69" s="7" t="e" cm="1">
-        <f t="array" ref="X69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(F69,2-INT(LOG10(ABS(F69))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y69" s="7" t="e" cm="1">
-        <f t="array" ref="Y69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(G69,2-INT(LOG10(ABS(G69))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z69" s="7" t="e" cm="1">
-        <f t="array" ref="Z69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(H69,2-INT(LOG10(ABS(H69))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA69" s="7" t="e" cm="1">
-        <f t="array" ref="AA69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(I69,2-INT(LOG10(ABS(I69))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB69" s="7" t="e" cm="1">
-        <f t="array" ref="AB69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(J69,2-INT(LOG10(ABS(J69))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC69" s="7" t="e" cm="1">
-        <f t="array" ref="AC69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(K69,2-INT(LOG10(ABS(K69))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD69" s="7" t="e" cm="1">
-        <f t="array" ref="AD69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(L69,2-INT(LOG10(ABS(L69))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE69" s="7" t="e" cm="1">
-        <f t="array" ref="AE69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(M69,2-INT(LOG10(ABS(M69))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF69" s="7" t="e" cm="1">
-        <f t="array" ref="AF69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(N69,2-INT(LOG10(ABS(N69))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG69" s="7" t="e" cm="1">
-        <f t="array" ref="AG69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(O69,2-INT(LOG10(ABS(O69))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH69" s="7" t="e" cm="1">
-        <f t="array" ref="AH69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(P69,2-INT(LOG10(ABS(P69))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI69" s="7" t="e" cm="1">
-        <f t="array" ref="AI69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(Q69,2-INT(LOG10(ABS(Q69))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ69" s="7" t="e" cm="1">
-        <f t="array" ref="AJ69">SUMPRODUCT(--(ROUND($D69:$R69,2-INT(LOG10(ABS($D69:$R69))))&lt;ROUND(R69,2-INT(LOG10(ABS(R69))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V69" s="7" t="e">
+        <f t="shared" ref="V69:AJ69" si="23">_xlfn.RANK.EQ(D69,$D69:$R69,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W69" s="7" t="e">
+        <f t="shared" si="23"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X69" s="7" t="e">
+        <f t="shared" si="23"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y69" s="7" t="e">
+        <f t="shared" si="23"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z69" s="7" t="e">
+        <f t="shared" si="23"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA69" s="7" t="e">
+        <f t="shared" si="23"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB69" s="7" t="e">
+        <f t="shared" si="23"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC69" s="7" t="e">
+        <f t="shared" si="23"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD69" s="7" t="e">
+        <f t="shared" si="23"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE69" s="7" t="e">
+        <f t="shared" si="23"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF69" s="7" t="e">
+        <f t="shared" si="23"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG69" s="7" t="e">
+        <f t="shared" si="23"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH69" s="7" t="e">
+        <f t="shared" si="23"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI69" s="7" t="e">
+        <f t="shared" si="23"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ69" s="7" t="e">
+        <f t="shared" si="23"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="70" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A70" s="24"/>
-      <c r="B70" s="20" t="s">
+      <c r="A70" s="21"/>
+      <c r="B70" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C70" s="20" t="s">
+      <c r="C70" s="9" t="s">
         <v>162</v>
       </c>
       <c r="D70" s="8"/>
@@ -6168,7 +5894,7 @@
       <c r="Q70" s="8"/>
       <c r="R70" s="8"/>
       <c r="S70" s="14"/>
-      <c r="T70" s="20" t="s">
+      <c r="T70" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V70" s="7"/>
@@ -6184,11 +5910,11 @@
       <c r="AF70" s="7"/>
     </row>
     <row r="71" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A71" s="24"/>
-      <c r="B71" s="21" t="s">
+      <c r="A71" s="21"/>
+      <c r="B71" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C71" s="21" t="s">
+      <c r="C71" s="5" t="s">
         <v>163</v>
       </c>
       <c r="D71" s="6"/>
@@ -6207,7 +5933,7 @@
       <c r="Q71" s="6"/>
       <c r="R71" s="6"/>
       <c r="S71" s="4"/>
-      <c r="T71" s="21" t="s">
+      <c r="T71" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V71" s="7"/>
@@ -6223,11 +5949,11 @@
       <c r="AF71" s="7"/>
     </row>
     <row r="72" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A72" s="24"/>
-      <c r="B72" s="22" t="s">
+      <c r="A72" s="21"/>
+      <c r="B72" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C72" s="22" t="s">
+      <c r="C72" s="2" t="s">
         <v>164</v>
       </c>
       <c r="D72" s="3"/>
@@ -6248,76 +5974,76 @@
       <c r="S72" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T72" s="22" t="s">
+      <c r="T72" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V72" s="7" t="e" cm="1">
-        <f t="array" ref="V72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(D72,2-INT(LOG10(ABS(D72))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W72" s="7" t="e" cm="1">
-        <f t="array" ref="W72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(E72,2-INT(LOG10(ABS(E72))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X72" s="7" t="e" cm="1">
-        <f t="array" ref="X72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(F72,2-INT(LOG10(ABS(F72))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y72" s="7" t="e" cm="1">
-        <f t="array" ref="Y72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(G72,2-INT(LOG10(ABS(G72))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z72" s="7" t="e" cm="1">
-        <f t="array" ref="Z72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(H72,2-INT(LOG10(ABS(H72))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA72" s="7" t="e" cm="1">
-        <f t="array" ref="AA72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(I72,2-INT(LOG10(ABS(I72))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB72" s="7" t="e" cm="1">
-        <f t="array" ref="AB72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(J72,2-INT(LOG10(ABS(J72))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC72" s="7" t="e" cm="1">
-        <f t="array" ref="AC72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(K72,2-INT(LOG10(ABS(K72))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD72" s="7" t="e" cm="1">
-        <f t="array" ref="AD72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(L72,2-INT(LOG10(ABS(L72))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE72" s="7" t="e" cm="1">
-        <f t="array" ref="AE72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(M72,2-INT(LOG10(ABS(M72))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF72" s="7" t="e" cm="1">
-        <f t="array" ref="AF72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(N72,2-INT(LOG10(ABS(N72))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG72" s="7" t="e" cm="1">
-        <f t="array" ref="AG72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(O72,2-INT(LOG10(ABS(O72))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH72" s="7" t="e" cm="1">
-        <f t="array" ref="AH72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(P72,2-INT(LOG10(ABS(P72))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI72" s="7" t="e" cm="1">
-        <f t="array" ref="AI72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(Q72,2-INT(LOG10(ABS(Q72))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ72" s="7" t="e" cm="1">
-        <f t="array" ref="AJ72">SUMPRODUCT(--(ROUND($D72:$R72,2-INT(LOG10(ABS($D72:$R72))))&lt;ROUND(R72,2-INT(LOG10(ABS(R72))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V72" s="7" t="e">
+        <f t="shared" ref="V72:AJ72" si="24">_xlfn.RANK.EQ(D72,$D72:$R72,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W72" s="7" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X72" s="7" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y72" s="7" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z72" s="7" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA72" s="7" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB72" s="7" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC72" s="7" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD72" s="7" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE72" s="7" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF72" s="7" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG72" s="7" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH72" s="7" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI72" s="7" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ72" s="7" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="73" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A73" s="24"/>
-      <c r="B73" s="20" t="s">
+      <c r="A73" s="21"/>
+      <c r="B73" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="C73" s="20" t="s">
+      <c r="C73" s="9" t="s">
         <v>165</v>
       </c>
       <c r="D73" s="8"/>
@@ -6336,7 +6062,7 @@
       <c r="Q73" s="8"/>
       <c r="R73" s="8"/>
       <c r="S73" s="14"/>
-      <c r="T73" s="20" t="s">
+      <c r="T73" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V73" s="7"/>
@@ -6352,11 +6078,11 @@
       <c r="AF73" s="7"/>
     </row>
     <row r="74" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A74" s="24"/>
-      <c r="B74" s="21" t="s">
+      <c r="A74" s="21"/>
+      <c r="B74" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C74" s="21" t="s">
+      <c r="C74" s="5" t="s">
         <v>166</v>
       </c>
       <c r="D74" s="6"/>
@@ -6375,7 +6101,7 @@
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
       <c r="S74" s="4"/>
-      <c r="T74" s="21" t="s">
+      <c r="T74" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V74" s="7"/>
@@ -6391,11 +6117,11 @@
       <c r="AF74" s="7"/>
     </row>
     <row r="75" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A75" s="24"/>
-      <c r="B75" s="22" t="s">
+      <c r="A75" s="21"/>
+      <c r="B75" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C75" s="22" t="s">
+      <c r="C75" s="2" t="s">
         <v>167</v>
       </c>
       <c r="D75" s="3"/>
@@ -6416,76 +6142,76 @@
       <c r="S75" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="T75" s="22" t="s">
+      <c r="T75" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V75" s="7" t="e" cm="1">
-        <f t="array" ref="V75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(D75,2-INT(LOG10(ABS(D75))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W75" s="7" t="e" cm="1">
-        <f t="array" ref="W75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(E75,2-INT(LOG10(ABS(E75))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X75" s="7" t="e" cm="1">
-        <f t="array" ref="X75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(F75,2-INT(LOG10(ABS(F75))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y75" s="7" t="e" cm="1">
-        <f t="array" ref="Y75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(G75,2-INT(LOG10(ABS(G75))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z75" s="7" t="e" cm="1">
-        <f t="array" ref="Z75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(H75,2-INT(LOG10(ABS(H75))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA75" s="7" t="e" cm="1">
-        <f t="array" ref="AA75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(I75,2-INT(LOG10(ABS(I75))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB75" s="7" t="e" cm="1">
-        <f t="array" ref="AB75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(J75,2-INT(LOG10(ABS(J75))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC75" s="7" t="e" cm="1">
-        <f t="array" ref="AC75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(K75,2-INT(LOG10(ABS(K75))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD75" s="7" t="e" cm="1">
-        <f t="array" ref="AD75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(L75,2-INT(LOG10(ABS(L75))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE75" s="7" t="e" cm="1">
-        <f t="array" ref="AE75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(M75,2-INT(LOG10(ABS(M75))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF75" s="7" t="e" cm="1">
-        <f t="array" ref="AF75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(N75,2-INT(LOG10(ABS(N75))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG75" s="7" t="e" cm="1">
-        <f t="array" ref="AG75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(O75,2-INT(LOG10(ABS(O75))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH75" s="7" t="e" cm="1">
-        <f t="array" ref="AH75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(P75,2-INT(LOG10(ABS(P75))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI75" s="7" t="e" cm="1">
-        <f t="array" ref="AI75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(Q75,2-INT(LOG10(ABS(Q75))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ75" s="7" t="e" cm="1">
-        <f t="array" ref="AJ75">SUMPRODUCT(--(ROUND($D75:$R75,2-INT(LOG10(ABS($D75:$R75))))&lt;ROUND(R75,2-INT(LOG10(ABS(R75))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V75" s="7" t="e">
+        <f t="shared" ref="V75:AJ75" si="25">_xlfn.RANK.EQ(D75,$D75:$R75,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W75" s="7" t="e">
+        <f t="shared" si="25"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X75" s="7" t="e">
+        <f t="shared" si="25"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y75" s="7" t="e">
+        <f t="shared" si="25"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z75" s="7" t="e">
+        <f t="shared" si="25"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA75" s="7" t="e">
+        <f t="shared" si="25"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB75" s="7" t="e">
+        <f t="shared" si="25"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC75" s="7" t="e">
+        <f t="shared" si="25"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD75" s="7" t="e">
+        <f t="shared" si="25"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE75" s="7" t="e">
+        <f t="shared" si="25"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF75" s="7" t="e">
+        <f t="shared" si="25"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG75" s="7" t="e">
+        <f t="shared" si="25"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH75" s="7" t="e">
+        <f t="shared" si="25"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI75" s="7" t="e">
+        <f t="shared" si="25"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ75" s="7" t="e">
+        <f t="shared" si="25"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="76" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A76" s="24"/>
-      <c r="B76" s="20" t="s">
+      <c r="A76" s="21"/>
+      <c r="B76" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C76" s="20" t="s">
+      <c r="C76" s="9" t="s">
         <v>168</v>
       </c>
       <c r="D76" s="8"/>
@@ -6504,7 +6230,7 @@
       <c r="Q76" s="8"/>
       <c r="R76" s="8"/>
       <c r="S76" s="14"/>
-      <c r="T76" s="20" t="s">
+      <c r="T76" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V76" s="7"/>
@@ -6520,11 +6246,11 @@
       <c r="AF76" s="7"/>
     </row>
     <row r="77" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A77" s="24"/>
-      <c r="B77" s="21" t="s">
+      <c r="A77" s="21"/>
+      <c r="B77" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C77" s="21" t="s">
+      <c r="C77" s="5" t="s">
         <v>169</v>
       </c>
       <c r="D77" s="6"/>
@@ -6543,7 +6269,7 @@
       <c r="Q77" s="6"/>
       <c r="R77" s="6"/>
       <c r="S77" s="4"/>
-      <c r="T77" s="21" t="s">
+      <c r="T77" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V77" s="7"/>
@@ -6559,11 +6285,11 @@
       <c r="AF77" s="7"/>
     </row>
     <row r="78" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A78" s="24"/>
-      <c r="B78" s="22" t="s">
+      <c r="A78" s="21"/>
+      <c r="B78" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C78" s="22" t="s">
+      <c r="C78" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D78" s="3"/>
@@ -6584,76 +6310,76 @@
       <c r="S78" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="T78" s="22" t="s">
+      <c r="T78" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V78" s="7" t="e" cm="1">
-        <f t="array" ref="V78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(D78,2-INT(LOG10(ABS(D78))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W78" s="7" t="e" cm="1">
-        <f t="array" ref="W78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(E78,2-INT(LOG10(ABS(E78))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X78" s="7" t="e" cm="1">
-        <f t="array" ref="X78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(F78,2-INT(LOG10(ABS(F78))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y78" s="7" t="e" cm="1">
-        <f t="array" ref="Y78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(G78,2-INT(LOG10(ABS(G78))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z78" s="7" t="e" cm="1">
-        <f t="array" ref="Z78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(H78,2-INT(LOG10(ABS(H78))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA78" s="7" t="e" cm="1">
-        <f t="array" ref="AA78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(I78,2-INT(LOG10(ABS(I78))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB78" s="7" t="e" cm="1">
-        <f t="array" ref="AB78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(J78,2-INT(LOG10(ABS(J78))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC78" s="7" t="e" cm="1">
-        <f t="array" ref="AC78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(K78,2-INT(LOG10(ABS(K78))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD78" s="7" t="e" cm="1">
-        <f t="array" ref="AD78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(L78,2-INT(LOG10(ABS(L78))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE78" s="7" t="e" cm="1">
-        <f t="array" ref="AE78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(M78,2-INT(LOG10(ABS(M78))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF78" s="7" t="e" cm="1">
-        <f t="array" ref="AF78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(N78,2-INT(LOG10(ABS(N78))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG78" s="7" t="e" cm="1">
-        <f t="array" ref="AG78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(O78,2-INT(LOG10(ABS(O78))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH78" s="7" t="e" cm="1">
-        <f t="array" ref="AH78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(P78,2-INT(LOG10(ABS(P78))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI78" s="7" t="e" cm="1">
-        <f t="array" ref="AI78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(Q78,2-INT(LOG10(ABS(Q78))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ78" s="7" t="e" cm="1">
-        <f t="array" ref="AJ78">SUMPRODUCT(--(ROUND($D78:$R78,2-INT(LOG10(ABS($D78:$R78))))&lt;ROUND(R78,2-INT(LOG10(ABS(R78))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V78" s="7" t="e">
+        <f t="shared" ref="V78:AJ78" si="26">_xlfn.RANK.EQ(D78,$D78:$R78,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W78" s="7" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X78" s="7" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y78" s="7" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z78" s="7" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA78" s="7" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB78" s="7" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC78" s="7" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD78" s="7" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE78" s="7" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF78" s="7" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG78" s="7" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH78" s="7" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI78" s="7" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ78" s="7" t="e">
+        <f t="shared" si="26"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="79" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A79" s="24"/>
-      <c r="B79" s="20" t="s">
+      <c r="A79" s="21"/>
+      <c r="B79" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C79" s="20" t="s">
+      <c r="C79" s="9" t="s">
         <v>171</v>
       </c>
       <c r="D79" s="8"/>
@@ -6672,7 +6398,7 @@
       <c r="Q79" s="8"/>
       <c r="R79" s="8"/>
       <c r="S79" s="14"/>
-      <c r="T79" s="20" t="s">
+      <c r="T79" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V79" s="7"/>
@@ -6688,11 +6414,11 @@
       <c r="AF79" s="7"/>
     </row>
     <row r="80" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A80" s="24"/>
-      <c r="B80" s="21" t="s">
+      <c r="A80" s="21"/>
+      <c r="B80" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C80" s="21" t="s">
+      <c r="C80" s="5" t="s">
         <v>172</v>
       </c>
       <c r="D80" s="6"/>
@@ -6711,7 +6437,7 @@
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
       <c r="S80" s="4"/>
-      <c r="T80" s="21" t="s">
+      <c r="T80" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V80" s="7"/>
@@ -6727,11 +6453,11 @@
       <c r="AF80" s="7"/>
     </row>
     <row r="81" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A81" s="24"/>
-      <c r="B81" s="22" t="s">
+      <c r="A81" s="21"/>
+      <c r="B81" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C81" s="22" t="s">
+      <c r="C81" s="2" t="s">
         <v>173</v>
       </c>
       <c r="D81" s="3"/>
@@ -6752,76 +6478,76 @@
       <c r="S81" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="T81" s="22" t="s">
+      <c r="T81" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V81" s="7" t="e" cm="1">
-        <f t="array" ref="V81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(D81,2-INT(LOG10(ABS(D81))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W81" s="7" t="e" cm="1">
-        <f t="array" ref="W81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(E81,2-INT(LOG10(ABS(E81))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X81" s="7" t="e" cm="1">
-        <f t="array" ref="X81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(F81,2-INT(LOG10(ABS(F81))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y81" s="7" t="e" cm="1">
-        <f t="array" ref="Y81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(G81,2-INT(LOG10(ABS(G81))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z81" s="7" t="e" cm="1">
-        <f t="array" ref="Z81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(H81,2-INT(LOG10(ABS(H81))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA81" s="7" t="e" cm="1">
-        <f t="array" ref="AA81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(I81,2-INT(LOG10(ABS(I81))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB81" s="7" t="e" cm="1">
-        <f t="array" ref="AB81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(J81,2-INT(LOG10(ABS(J81))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC81" s="7" t="e" cm="1">
-        <f t="array" ref="AC81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(K81,2-INT(LOG10(ABS(K81))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD81" s="7" t="e" cm="1">
-        <f t="array" ref="AD81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(L81,2-INT(LOG10(ABS(L81))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE81" s="7" t="e" cm="1">
-        <f t="array" ref="AE81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(M81,2-INT(LOG10(ABS(M81))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF81" s="7" t="e" cm="1">
-        <f t="array" ref="AF81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(N81,2-INT(LOG10(ABS(N81))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG81" s="7" t="e" cm="1">
-        <f t="array" ref="AG81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(O81,2-INT(LOG10(ABS(O81))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH81" s="7" t="e" cm="1">
-        <f t="array" ref="AH81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(P81,2-INT(LOG10(ABS(P81))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI81" s="7" t="e" cm="1">
-        <f t="array" ref="AI81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(Q81,2-INT(LOG10(ABS(Q81))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ81" s="7" t="e" cm="1">
-        <f t="array" ref="AJ81">SUMPRODUCT(--(ROUND($D81:$R81,2-INT(LOG10(ABS($D81:$R81))))&lt;ROUND(R81,2-INT(LOG10(ABS(R81))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V81" s="7" t="e">
+        <f t="shared" ref="V81:AJ81" si="27">_xlfn.RANK.EQ(D81,$D81:$R81,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W81" s="7" t="e">
+        <f t="shared" si="27"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X81" s="7" t="e">
+        <f t="shared" si="27"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y81" s="7" t="e">
+        <f t="shared" si="27"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z81" s="7" t="e">
+        <f t="shared" si="27"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA81" s="7" t="e">
+        <f t="shared" si="27"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB81" s="7" t="e">
+        <f t="shared" si="27"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC81" s="7" t="e">
+        <f t="shared" si="27"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD81" s="7" t="e">
+        <f t="shared" si="27"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE81" s="7" t="e">
+        <f t="shared" si="27"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF81" s="7" t="e">
+        <f t="shared" si="27"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG81" s="7" t="e">
+        <f t="shared" si="27"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH81" s="7" t="e">
+        <f t="shared" si="27"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI81" s="7" t="e">
+        <f t="shared" si="27"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ81" s="7" t="e">
+        <f t="shared" si="27"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="82" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A82" s="24"/>
-      <c r="B82" s="20" t="s">
+      <c r="A82" s="21"/>
+      <c r="B82" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="C82" s="20" t="s">
+      <c r="C82" s="9" t="s">
         <v>174</v>
       </c>
       <c r="D82" s="8"/>
@@ -6840,7 +6566,7 @@
       <c r="Q82" s="8"/>
       <c r="R82" s="8"/>
       <c r="S82" s="14"/>
-      <c r="T82" s="20" t="s">
+      <c r="T82" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V82" s="7"/>
@@ -6856,11 +6582,11 @@
       <c r="AF82" s="7"/>
     </row>
     <row r="83" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A83" s="24"/>
-      <c r="B83" s="21" t="s">
+      <c r="A83" s="21"/>
+      <c r="B83" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C83" s="21" t="s">
+      <c r="C83" s="5" t="s">
         <v>175</v>
       </c>
       <c r="D83" s="6"/>
@@ -6879,7 +6605,7 @@
       <c r="Q83" s="6"/>
       <c r="R83" s="6"/>
       <c r="S83" s="4"/>
-      <c r="T83" s="21" t="s">
+      <c r="T83" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V83" s="7"/>
@@ -6895,11 +6621,11 @@
       <c r="AF83" s="7"/>
     </row>
     <row r="84" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A84" s="24"/>
-      <c r="B84" s="22" t="s">
+      <c r="A84" s="21"/>
+      <c r="B84" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C84" s="22" t="s">
+      <c r="C84" s="2" t="s">
         <v>176</v>
       </c>
       <c r="D84" s="3"/>
@@ -6920,76 +6646,76 @@
       <c r="S84" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="T84" s="22" t="s">
+      <c r="T84" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V84" s="7" t="e" cm="1">
-        <f t="array" ref="V84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(D84,2-INT(LOG10(ABS(D84))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W84" s="7" t="e" cm="1">
-        <f t="array" ref="W84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(E84,2-INT(LOG10(ABS(E84))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X84" s="7" t="e" cm="1">
-        <f t="array" ref="X84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(F84,2-INT(LOG10(ABS(F84))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y84" s="7" t="e" cm="1">
-        <f t="array" ref="Y84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(G84,2-INT(LOG10(ABS(G84))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z84" s="7" t="e" cm="1">
-        <f t="array" ref="Z84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(H84,2-INT(LOG10(ABS(H84))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA84" s="7" t="e" cm="1">
-        <f t="array" ref="AA84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(I84,2-INT(LOG10(ABS(I84))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB84" s="7" t="e" cm="1">
-        <f t="array" ref="AB84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(J84,2-INT(LOG10(ABS(J84))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC84" s="7" t="e" cm="1">
-        <f t="array" ref="AC84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(K84,2-INT(LOG10(ABS(K84))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD84" s="7" t="e" cm="1">
-        <f t="array" ref="AD84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(L84,2-INT(LOG10(ABS(L84))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE84" s="7" t="e" cm="1">
-        <f t="array" ref="AE84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(M84,2-INT(LOG10(ABS(M84))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF84" s="7" t="e" cm="1">
-        <f t="array" ref="AF84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(N84,2-INT(LOG10(ABS(N84))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG84" s="7" t="e" cm="1">
-        <f t="array" ref="AG84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(O84,2-INT(LOG10(ABS(O84))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH84" s="7" t="e" cm="1">
-        <f t="array" ref="AH84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(P84,2-INT(LOG10(ABS(P84))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI84" s="7" t="e" cm="1">
-        <f t="array" ref="AI84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(Q84,2-INT(LOG10(ABS(Q84))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ84" s="7" t="e" cm="1">
-        <f t="array" ref="AJ84">SUMPRODUCT(--(ROUND($D84:$R84,2-INT(LOG10(ABS($D84:$R84))))&lt;ROUND(R84,2-INT(LOG10(ABS(R84))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V84" s="7" t="e">
+        <f t="shared" ref="V84:AJ84" si="28">_xlfn.RANK.EQ(D84,$D84:$R84,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W84" s="7" t="e">
+        <f t="shared" si="28"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X84" s="7" t="e">
+        <f t="shared" si="28"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y84" s="7" t="e">
+        <f t="shared" si="28"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z84" s="7" t="e">
+        <f t="shared" si="28"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA84" s="7" t="e">
+        <f t="shared" si="28"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB84" s="7" t="e">
+        <f t="shared" si="28"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC84" s="7" t="e">
+        <f t="shared" si="28"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD84" s="7" t="e">
+        <f t="shared" si="28"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE84" s="7" t="e">
+        <f t="shared" si="28"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF84" s="7" t="e">
+        <f t="shared" si="28"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG84" s="7" t="e">
+        <f t="shared" si="28"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH84" s="7" t="e">
+        <f t="shared" si="28"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI84" s="7" t="e">
+        <f t="shared" si="28"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ84" s="7" t="e">
+        <f t="shared" si="28"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="85" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A85" s="24"/>
-      <c r="B85" s="20" t="s">
+      <c r="A85" s="21"/>
+      <c r="B85" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C85" s="20" t="s">
+      <c r="C85" s="9" t="s">
         <v>177</v>
       </c>
       <c r="D85" s="8"/>
@@ -7008,7 +6734,7 @@
       <c r="Q85" s="8"/>
       <c r="R85" s="8"/>
       <c r="S85" s="14"/>
-      <c r="T85" s="20" t="s">
+      <c r="T85" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V85" s="7"/>
@@ -7024,11 +6750,11 @@
       <c r="AF85" s="7"/>
     </row>
     <row r="86" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A86" s="24"/>
-      <c r="B86" s="21" t="s">
+      <c r="A86" s="21"/>
+      <c r="B86" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C86" s="21" t="s">
+      <c r="C86" s="5" t="s">
         <v>178</v>
       </c>
       <c r="D86" s="6"/>
@@ -7047,7 +6773,7 @@
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
       <c r="S86" s="4"/>
-      <c r="T86" s="21" t="s">
+      <c r="T86" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V86" s="7"/>
@@ -7063,11 +6789,11 @@
       <c r="AF86" s="7"/>
     </row>
     <row r="87" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A87" s="24"/>
-      <c r="B87" s="22" t="s">
+      <c r="A87" s="21"/>
+      <c r="B87" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C87" s="22" t="s">
+      <c r="C87" s="2" t="s">
         <v>179</v>
       </c>
       <c r="D87" s="3"/>
@@ -7088,76 +6814,76 @@
       <c r="S87" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T87" s="22" t="s">
+      <c r="T87" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V87" s="7" t="e" cm="1">
-        <f t="array" ref="V87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(D87,2-INT(LOG10(ABS(D87))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W87" s="7" t="e" cm="1">
-        <f t="array" ref="W87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(E87,2-INT(LOG10(ABS(E87))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X87" s="7" t="e" cm="1">
-        <f t="array" ref="X87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(F87,2-INT(LOG10(ABS(F87))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y87" s="7" t="e" cm="1">
-        <f t="array" ref="Y87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(G87,2-INT(LOG10(ABS(G87))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z87" s="7" t="e" cm="1">
-        <f t="array" ref="Z87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(H87,2-INT(LOG10(ABS(H87))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA87" s="7" t="e" cm="1">
-        <f t="array" ref="AA87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(I87,2-INT(LOG10(ABS(I87))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB87" s="7" t="e" cm="1">
-        <f t="array" ref="AB87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(J87,2-INT(LOG10(ABS(J87))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC87" s="7" t="e" cm="1">
-        <f t="array" ref="AC87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(K87,2-INT(LOG10(ABS(K87))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD87" s="7" t="e" cm="1">
-        <f t="array" ref="AD87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(L87,2-INT(LOG10(ABS(L87))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE87" s="7" t="e" cm="1">
-        <f t="array" ref="AE87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(M87,2-INT(LOG10(ABS(M87))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF87" s="7" t="e" cm="1">
-        <f t="array" ref="AF87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(N87,2-INT(LOG10(ABS(N87))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG87" s="7" t="e" cm="1">
-        <f t="array" ref="AG87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(O87,2-INT(LOG10(ABS(O87))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH87" s="7" t="e" cm="1">
-        <f t="array" ref="AH87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(P87,2-INT(LOG10(ABS(P87))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI87" s="7" t="e" cm="1">
-        <f t="array" ref="AI87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(Q87,2-INT(LOG10(ABS(Q87))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ87" s="7" t="e" cm="1">
-        <f t="array" ref="AJ87">SUMPRODUCT(--(ROUND($D87:$R87,2-INT(LOG10(ABS($D87:$R87))))&lt;ROUND(R87,2-INT(LOG10(ABS(R87))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V87" s="7" t="e">
+        <f t="shared" ref="V87:AJ87" si="29">_xlfn.RANK.EQ(D87,$D87:$R87,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W87" s="7" t="e">
+        <f t="shared" si="29"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X87" s="7" t="e">
+        <f t="shared" si="29"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y87" s="7" t="e">
+        <f t="shared" si="29"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z87" s="7" t="e">
+        <f t="shared" si="29"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA87" s="7" t="e">
+        <f t="shared" si="29"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB87" s="7" t="e">
+        <f t="shared" si="29"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC87" s="7" t="e">
+        <f t="shared" si="29"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD87" s="7" t="e">
+        <f t="shared" si="29"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE87" s="7" t="e">
+        <f t="shared" si="29"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF87" s="7" t="e">
+        <f t="shared" si="29"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG87" s="7" t="e">
+        <f t="shared" si="29"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH87" s="7" t="e">
+        <f t="shared" si="29"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI87" s="7" t="e">
+        <f t="shared" si="29"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ87" s="7" t="e">
+        <f t="shared" si="29"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="88" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A88" s="24"/>
-      <c r="B88" s="20" t="s">
+      <c r="A88" s="21"/>
+      <c r="B88" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C88" s="20" t="s">
+      <c r="C88" s="9" t="s">
         <v>180</v>
       </c>
       <c r="D88" s="8"/>
@@ -7176,7 +6902,7 @@
       <c r="Q88" s="8"/>
       <c r="R88" s="8"/>
       <c r="S88" s="14"/>
-      <c r="T88" s="20" t="s">
+      <c r="T88" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V88" s="7"/>
@@ -7192,11 +6918,11 @@
       <c r="AF88" s="7"/>
     </row>
     <row r="89" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A89" s="24"/>
-      <c r="B89" s="21" t="s">
+      <c r="A89" s="21"/>
+      <c r="B89" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C89" s="21" t="s">
+      <c r="C89" s="5" t="s">
         <v>181</v>
       </c>
       <c r="D89" s="6"/>
@@ -7215,7 +6941,7 @@
       <c r="Q89" s="6"/>
       <c r="R89" s="6"/>
       <c r="S89" s="4"/>
-      <c r="T89" s="21" t="s">
+      <c r="T89" s="5" t="s">
         <v>32</v>
       </c>
       <c r="V89" s="7"/>
@@ -7231,11 +6957,11 @@
       <c r="AF89" s="7"/>
     </row>
     <row r="90" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A90" s="24"/>
-      <c r="B90" s="22" t="s">
+      <c r="A90" s="21"/>
+      <c r="B90" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C90" s="22" t="s">
+      <c r="C90" s="2" t="s">
         <v>182</v>
       </c>
       <c r="D90" s="3"/>
@@ -7256,76 +6982,76 @@
       <c r="S90" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="T90" s="22" t="s">
+      <c r="T90" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V90" s="7" t="e" cm="1">
-        <f t="array" ref="V90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(D90,2-INT(LOG10(ABS(D90))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W90" s="7" t="e" cm="1">
-        <f t="array" ref="W90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(E90,2-INT(LOG10(ABS(E90))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X90" s="7" t="e" cm="1">
-        <f t="array" ref="X90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(F90,2-INT(LOG10(ABS(F90))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y90" s="7" t="e" cm="1">
-        <f t="array" ref="Y90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(G90,2-INT(LOG10(ABS(G90))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z90" s="7" t="e" cm="1">
-        <f t="array" ref="Z90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(H90,2-INT(LOG10(ABS(H90))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA90" s="7" t="e" cm="1">
-        <f t="array" ref="AA90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(I90,2-INT(LOG10(ABS(I90))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB90" s="7" t="e" cm="1">
-        <f t="array" ref="AB90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(J90,2-INT(LOG10(ABS(J90))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC90" s="7" t="e" cm="1">
-        <f t="array" ref="AC90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(K90,2-INT(LOG10(ABS(K90))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD90" s="7" t="e" cm="1">
-        <f t="array" ref="AD90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(L90,2-INT(LOG10(ABS(L90))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE90" s="7" t="e" cm="1">
-        <f t="array" ref="AE90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(M90,2-INT(LOG10(ABS(M90))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF90" s="7" t="e" cm="1">
-        <f t="array" ref="AF90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(N90,2-INT(LOG10(ABS(N90))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG90" s="7" t="e" cm="1">
-        <f t="array" ref="AG90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(O90,2-INT(LOG10(ABS(O90))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH90" s="7" t="e" cm="1">
-        <f t="array" ref="AH90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(P90,2-INT(LOG10(ABS(P90))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI90" s="7" t="e" cm="1">
-        <f t="array" ref="AI90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(Q90,2-INT(LOG10(ABS(Q90))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ90" s="7" t="e" cm="1">
-        <f t="array" ref="AJ90">SUMPRODUCT(--(ROUND($D90:$R90,2-INT(LOG10(ABS($D90:$R90))))&lt;ROUND(R90,2-INT(LOG10(ABS(R90))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V90" s="7" t="e">
+        <f t="shared" ref="V90:AJ90" si="30">_xlfn.RANK.EQ(D90,$D90:$R90,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W90" s="7" t="e">
+        <f t="shared" si="30"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X90" s="7" t="e">
+        <f t="shared" si="30"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y90" s="7" t="e">
+        <f t="shared" si="30"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z90" s="7" t="e">
+        <f t="shared" si="30"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA90" s="7" t="e">
+        <f t="shared" si="30"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB90" s="7" t="e">
+        <f t="shared" si="30"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC90" s="7" t="e">
+        <f t="shared" si="30"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD90" s="7" t="e">
+        <f t="shared" si="30"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE90" s="7" t="e">
+        <f t="shared" si="30"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF90" s="7" t="e">
+        <f t="shared" si="30"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG90" s="7" t="e">
+        <f t="shared" si="30"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH90" s="7" t="e">
+        <f t="shared" si="30"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI90" s="7" t="e">
+        <f t="shared" si="30"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ90" s="7" t="e">
+        <f t="shared" si="30"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="91" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A91" s="24"/>
-      <c r="B91" s="20" t="s">
+      <c r="A91" s="21"/>
+      <c r="B91" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="C91" s="20" t="s">
+      <c r="C91" s="9" t="s">
         <v>183</v>
       </c>
       <c r="D91" s="8"/>
@@ -7344,7 +7070,7 @@
       <c r="Q91" s="8"/>
       <c r="R91" s="8"/>
       <c r="S91" s="14"/>
-      <c r="T91" s="20" t="s">
+      <c r="T91" s="9" t="s">
         <v>31</v>
       </c>
       <c r="V91" s="7"/>
@@ -7360,11 +7086,11 @@
       <c r="AF91" s="7"/>
     </row>
     <row r="92" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A92" s="27"/>
-      <c r="B92" s="21" t="s">
+      <c r="A92" s="24"/>
+      <c r="B92" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C92" s="21" t="s">
+      <c r="C92" s="5" t="s">
         <v>184</v>
       </c>
       <c r="D92" s="6"/>
@@ -7383,7 +7109,7 @@
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
       <c r="S92" s="14"/>
-      <c r="T92" s="20" t="s">
+      <c r="T92" s="9" t="s">
         <v>32</v>
       </c>
       <c r="V92" s="7"/>
@@ -7399,271 +7125,271 @@
       <c r="AF92" s="7"/>
     </row>
     <row r="93" spans="1:36" s="7" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="29" t="s">
+      <c r="A93" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="B93" s="30"/>
-      <c r="C93" s="30"/>
-      <c r="D93" s="22">
+      <c r="B93" s="27"/>
+      <c r="C93" s="27"/>
+      <c r="D93" s="2">
         <f>COUNTIF(V3:V92,1)</f>
         <v>0</v>
       </c>
-      <c r="E93" s="22">
-        <f t="shared" ref="E93:R93" si="1">COUNTIF(W3:W92,1)</f>
+      <c r="E93" s="2">
+        <f t="shared" ref="E93:R93" si="31">COUNTIF(W3:W92,1)</f>
         <v>0</v>
       </c>
-      <c r="F93" s="22">
-        <f t="shared" si="1"/>
+      <c r="F93" s="2">
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G93" s="22">
-        <f t="shared" si="1"/>
+      <c r="G93" s="2">
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="H93" s="22">
-        <f t="shared" si="1"/>
+      <c r="H93" s="2">
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="I93" s="22">
-        <f t="shared" si="1"/>
+      <c r="I93" s="2">
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="J93" s="22">
-        <f t="shared" si="1"/>
+      <c r="J93" s="2">
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="K93" s="22">
-        <f t="shared" si="1"/>
+      <c r="K93" s="2">
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="L93" s="22">
-        <f t="shared" si="1"/>
+      <c r="L93" s="2">
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M93" s="22">
-        <f t="shared" si="1"/>
+      <c r="M93" s="2">
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="N93" s="22">
-        <f t="shared" si="1"/>
+      <c r="N93" s="2">
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="O93" s="22">
-        <f t="shared" si="1"/>
+      <c r="O93" s="2">
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="P93" s="22">
-        <f t="shared" si="1"/>
+      <c r="P93" s="2">
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="Q93" s="22">
-        <f t="shared" si="1"/>
+      <c r="Q93" s="2">
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="R93" s="22">
-        <f t="shared" si="1"/>
+      <c r="R93" s="2">
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:36" s="7" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="24" t="s">
+      <c r="A94" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B94" s="25"/>
-      <c r="C94" s="25"/>
-      <c r="D94" s="20">
+      <c r="B94" s="22"/>
+      <c r="C94" s="22"/>
+      <c r="D94" s="9">
         <f>_xlfn.RANK.EQ(D93,$D93:$R93,0)</f>
         <v>1</v>
       </c>
-      <c r="E94" s="20">
-        <f t="shared" ref="E94:R94" si="2">_xlfn.RANK.EQ(E93,$D93:$R93,0)</f>
+      <c r="E94" s="9">
+        <f t="shared" ref="E94:R94" si="32">_xlfn.RANK.EQ(E93,$D93:$R93,0)</f>
         <v>1</v>
       </c>
-      <c r="F94" s="20">
-        <f t="shared" si="2"/>
+      <c r="F94" s="9">
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
-      <c r="G94" s="20">
-        <f t="shared" si="2"/>
+      <c r="G94" s="9">
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
-      <c r="H94" s="20">
-        <f t="shared" si="2"/>
+      <c r="H94" s="9">
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
-      <c r="I94" s="20">
-        <f t="shared" si="2"/>
+      <c r="I94" s="9">
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
-      <c r="J94" s="20">
-        <f t="shared" si="2"/>
+      <c r="J94" s="9">
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
-      <c r="K94" s="20">
-        <f t="shared" si="2"/>
+      <c r="K94" s="9">
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
-      <c r="L94" s="20">
-        <f t="shared" si="2"/>
+      <c r="L94" s="9">
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
-      <c r="M94" s="20">
-        <f t="shared" si="2"/>
+      <c r="M94" s="9">
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
-      <c r="N94" s="20">
-        <f t="shared" si="2"/>
+      <c r="N94" s="9">
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
-      <c r="O94" s="20">
-        <f t="shared" si="2"/>
+      <c r="O94" s="9">
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
-      <c r="P94" s="20">
-        <f t="shared" si="2"/>
+      <c r="P94" s="9">
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
-      <c r="Q94" s="20">
-        <f t="shared" si="2"/>
+      <c r="Q94" s="9">
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
-      <c r="R94" s="20">
-        <f t="shared" si="2"/>
+      <c r="R94" s="9">
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:36" s="7" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="26" t="s">
+      <c r="A95" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B95" s="25"/>
-      <c r="C95" s="25"/>
+      <c r="B95" s="22"/>
+      <c r="C95" s="22"/>
       <c r="D95" s="15" t="e">
         <f>AVERAGE(V3:V92)</f>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="E95" s="15" t="e">
-        <f t="shared" ref="E95:R95" si="3">AVERAGE(W3:W92)</f>
-        <v>#NUM!</v>
+        <f t="shared" ref="E95:R95" si="33">AVERAGE(W3:W92)</f>
+        <v>#N/A</v>
       </c>
       <c r="F95" s="15" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
       </c>
       <c r="G95" s="15" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
       </c>
       <c r="H95" s="15" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
       </c>
       <c r="I95" s="15" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
       </c>
       <c r="J95" s="15" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
       </c>
       <c r="K95" s="15" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
       </c>
       <c r="L95" s="15" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
       </c>
       <c r="M95" s="15" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
       </c>
       <c r="N95" s="15" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
       </c>
       <c r="O95" s="15" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
       </c>
       <c r="P95" s="15" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
       </c>
       <c r="Q95" s="15" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
       </c>
       <c r="R95" s="15" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="96" spans="1:36" s="7" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="27" t="s">
+      <c r="A96" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B96" s="28"/>
-      <c r="C96" s="28"/>
-      <c r="D96" s="21" t="e">
+      <c r="B96" s="25"/>
+      <c r="C96" s="25"/>
+      <c r="D96" s="5" t="e">
         <f>_xlfn.RANK.EQ(D95,$D95:$R95,1)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="E96" s="21" t="e">
-        <f t="shared" ref="E96:R96" si="4">_xlfn.RANK.EQ(E95,$D95:$R95,1)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="F96" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="G96" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="H96" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="I96" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="J96" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="K96" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L96" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="M96" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="N96" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O96" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P96" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q96" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R96" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
+      </c>
+      <c r="E96" s="5" t="e">
+        <f t="shared" ref="E96:R96" si="34">_xlfn.RANK.EQ(E95,$D95:$R95,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F96" s="5" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="G96" s="5" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="H96" s="5" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="I96" s="5" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="J96" s="5" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="K96" s="5" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="L96" s="5" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="M96" s="5" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="N96" s="5" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="O96" s="5" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P96" s="5" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q96" s="5" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R96" s="5" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
@@ -7680,154 +7406,94 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="D3:R3">
-    <cfRule type="expression" dxfId="32" priority="30">
-      <formula>ROUND(D3,2-INT(LOG10(ABS(D3))))= ROUND(MIN($D3:$R3),2-INT(LOG10(ABS(MIN($D3:$R3)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="33" priority="30" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:R6">
-    <cfRule type="expression" dxfId="31" priority="29">
-      <formula>ROUND(D6,2-INT(LOG10(ABS(D6))))= ROUND(MIN($D6:$R6),2-INT(LOG10(ABS(MIN($D6:$R6)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="32" priority="29" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:R9">
-    <cfRule type="expression" dxfId="30" priority="28">
-      <formula>ROUND(D9,2-INT(LOG10(ABS(D9))))= ROUND(MIN($D9:$R9),2-INT(LOG10(ABS(MIN($D9:$R9)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="31" priority="28" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12:R12">
-    <cfRule type="expression" dxfId="29" priority="27">
-      <formula>ROUND(D12,2-INT(LOG10(ABS(D12))))= ROUND(MIN($D12:$R12),2-INT(LOG10(ABS(MIN($D12:$R12)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="30" priority="27" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:R15">
-    <cfRule type="expression" dxfId="28" priority="26">
-      <formula>ROUND(D15,2-INT(LOG10(ABS(D15))))= ROUND(MIN($D15:$R15),2-INT(LOG10(ABS(MIN($D15:$R15)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="29" priority="26" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:R18">
-    <cfRule type="expression" dxfId="27" priority="25">
-      <formula>ROUND(D18,2-INT(LOG10(ABS(D18))))= ROUND(MIN($D18:$R18),2-INT(LOG10(ABS(MIN($D18:$R18)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="28" priority="25" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D21:R21">
-    <cfRule type="expression" dxfId="26" priority="24">
-      <formula>ROUND(D21,2-INT(LOG10(ABS(D21))))= ROUND(MIN($D21:$R21),2-INT(LOG10(ABS(MIN($D21:$R21)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="27" priority="24" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D24:R24">
-    <cfRule type="expression" dxfId="25" priority="23">
-      <formula>ROUND(D24,2-INT(LOG10(ABS(D24))))= ROUND(MIN($D24:$R24),2-INT(LOG10(ABS(MIN($D24:$R24)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="26" priority="23" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27:R27">
-    <cfRule type="expression" dxfId="24" priority="22">
-      <formula>ROUND(D27,2-INT(LOG10(ABS(D27))))= ROUND(MIN($D27:$R27),2-INT(LOG10(ABS(MIN($D27:$R27)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="25" priority="22" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:R30">
-    <cfRule type="expression" dxfId="23" priority="21">
-      <formula>ROUND(D30,2-INT(LOG10(ABS(D30))))= ROUND(MIN($D30:$R30),2-INT(LOG10(ABS(MIN($D30:$R30)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="24" priority="21" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D33:R33">
-    <cfRule type="expression" dxfId="22" priority="20">
-      <formula>ROUND(D33,2-INT(LOG10(ABS(D33))))= ROUND(MIN($D33:$R33),2-INT(LOG10(ABS(MIN($D33:$R33)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="23" priority="20" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D36:R36">
-    <cfRule type="expression" dxfId="21" priority="19">
-      <formula>ROUND(D36,2-INT(LOG10(ABS(D36))))= ROUND(MIN($D36:$R36),2-INT(LOG10(ABS(MIN($D36:$R36)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="22" priority="19" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D39:R39">
-    <cfRule type="expression" dxfId="20" priority="18">
-      <formula>ROUND(D39,2-INT(LOG10(ABS(D39))))= ROUND(MIN($D39:$R39),2-INT(LOG10(ABS(MIN($D39:$R39)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="21" priority="18" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D42:R42">
-    <cfRule type="expression" dxfId="19" priority="17">
-      <formula>ROUND(D42,2-INT(LOG10(ABS(D42))))= ROUND(MIN($D42:$R42),2-INT(LOG10(ABS(MIN($D42:$R42)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="20" priority="17" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45:R45">
-    <cfRule type="expression" dxfId="18" priority="16">
-      <formula>ROUND(D45,2-INT(LOG10(ABS(D45))))= ROUND(MIN($D45:$R45),2-INT(LOG10(ABS(MIN($D45:$R45)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="19" priority="16" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D48:R48">
-    <cfRule type="expression" dxfId="17" priority="15">
-      <formula>ROUND(D48,2-INT(LOG10(ABS(D48))))= ROUND(MIN($D48:$R48),2-INT(LOG10(ABS(MIN($D48:$R48)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="18" priority="15" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51:R51">
-    <cfRule type="expression" dxfId="16" priority="14">
-      <formula>ROUND(D51,2-INT(LOG10(ABS(D51))))= ROUND(MIN($D51:$R51),2-INT(LOG10(ABS(MIN($D51:$R51)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="17" priority="14" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54:R54">
-    <cfRule type="expression" dxfId="15" priority="13">
-      <formula>ROUND(D54,2-INT(LOG10(ABS(D54))))= ROUND(MIN($D54:$R54),2-INT(LOG10(ABS(MIN($D54:$R54)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="16" priority="13" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D57:R57">
-    <cfRule type="expression" dxfId="14" priority="12">
-      <formula>ROUND(D57,2-INT(LOG10(ABS(D57))))= ROUND(MIN($D57:$R57),2-INT(LOG10(ABS(MIN($D57:$R57)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="15" priority="12" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D60:R60">
-    <cfRule type="expression" dxfId="13" priority="11">
-      <formula>ROUND(D60,2-INT(LOG10(ABS(D60))))= ROUND(MIN($D60:$R60),2-INT(LOG10(ABS(MIN($D60:$R60)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="14" priority="11" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:R63">
-    <cfRule type="expression" dxfId="12" priority="10">
-      <formula>ROUND(D63,2-INT(LOG10(ABS(D63))))= ROUND(MIN($D63:$R63),2-INT(LOG10(ABS(MIN($D63:$R63)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="13" priority="10" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D66:R66">
-    <cfRule type="expression" dxfId="11" priority="9">
-      <formula>ROUND(D66,2-INT(LOG10(ABS(D66))))= ROUND(MIN($D66:$R66),2-INT(LOG10(ABS(MIN($D66:$R66)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="12" priority="9" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69:R69">
-    <cfRule type="expression" dxfId="10" priority="8">
-      <formula>ROUND(D69,2-INT(LOG10(ABS(D69))))= ROUND(MIN($D69:$R69),2-INT(LOG10(ABS(MIN($D69:$R69)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="11" priority="8" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D72:R72">
-    <cfRule type="expression" dxfId="9" priority="7">
-      <formula>ROUND(D72,2-INT(LOG10(ABS(D72))))= ROUND(MIN($D72:$R72),2-INT(LOG10(ABS(MIN($D72:$R72)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="10" priority="7" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D75:R75">
-    <cfRule type="expression" dxfId="8" priority="6">
-      <formula>ROUND(D75,2-INT(LOG10(ABS(D75))))= ROUND(MIN($D75:$R75),2-INT(LOG10(ABS(MIN($D75:$R75)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="9" priority="6" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D78:R78">
-    <cfRule type="expression" dxfId="7" priority="5">
-      <formula>ROUND(D78,2-INT(LOG10(ABS(D78))))= ROUND(MIN($D78:$R78),2-INT(LOG10(ABS(MIN($D78:$R78)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="8" priority="5" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D81:R81">
-    <cfRule type="expression" dxfId="6" priority="4">
-      <formula>ROUND(D81,2-INT(LOG10(ABS(D81))))= ROUND(MIN($D81:$R81),2-INT(LOG10(ABS(MIN($D81:$R81)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="7" priority="4" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D84:R84">
-    <cfRule type="expression" dxfId="5" priority="3">
-      <formula>ROUND(D84,2-INT(LOG10(ABS(D84))))= ROUND(MIN($D84:$R84),2-INT(LOG10(ABS(MIN($D84:$R84)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="6" priority="3" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:R87">
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>ROUND(D87,2-INT(LOG10(ABS(D87))))= ROUND(MIN($D87:$R87),2-INT(LOG10(ABS(MIN($D87:$R87)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="5" priority="2" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D90:R90">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>ROUND(D90,2-INT(LOG10(ABS(D90))))= ROUND(MIN($D90:$R90),2-INT(LOG10(ABS(MIN($D90:$R90)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="4" priority="1" bottom="1" rank="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -7848,23 +7514,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -8489,7 +8155,7 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B3:N32">
-    <cfRule type="cellIs" dxfId="36" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8509,23 +8175,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -9149,7 +8815,7 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:O32">
-    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9169,23 +8835,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -9809,7 +9475,7 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:O32">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9829,23 +9495,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -10469,7 +10135,7 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:O32">
-    <cfRule type="cellIs" dxfId="33" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10489,23 +10155,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">

--- a/src/results_template/CEC2014/30Dim.xlsx
+++ b/src/results_template/CEC2014/30Dim.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\Research\Project Test\Base-Optimization-Framework\src\results_template\CEC2014\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\Research\Project Test\src\results_template\CEC2014\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{C18848A0-72C2-480E-805A-F5087020EAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC162405-7C66-45C6-A91A-D862321BC773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,20 +22,8 @@
     <sheet name="Friedman" sheetId="7" r:id="rId7"/>
     <sheet name="Explanation" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -44,12 +32,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="121">
   <si>
     <t>Comparison of optimization results for the CEC benchmark functions 2014 (30 Dim)</t>
   </si>
   <si>
     <t>Functions</t>
+  </si>
+  <si>
+    <t>Algorithm 1</t>
+  </si>
+  <si>
+    <t>Algorithm 2</t>
+  </si>
+  <si>
+    <t>Algorithm 3</t>
+  </si>
+  <si>
+    <t>Algorithm 4</t>
+  </si>
+  <si>
+    <t>Algorithm 5</t>
+  </si>
+  <si>
+    <t>Algorithm 6</t>
+  </si>
+  <si>
+    <t>Algorithm 7</t>
+  </si>
+  <si>
+    <t>Algorithm 8</t>
+  </si>
+  <si>
+    <t>Algorithm 9</t>
+  </si>
+  <si>
+    <t>Algorithm 10</t>
+  </si>
+  <si>
+    <t>Algorithm 11</t>
+  </si>
+  <si>
+    <t>Algorithm 12</t>
+  </si>
+  <si>
+    <t>Algorithm 13</t>
+  </si>
+  <si>
+    <t>Algorithm 14</t>
+  </si>
+  <si>
+    <t>Algorithm 15</t>
   </si>
   <si>
     <t>Unimodal
@@ -168,177 +201,129 @@
     <t>F30</t>
   </si>
   <si>
-    <t>Algorithm 1</t>
-  </si>
-  <si>
-    <t>Algorithm 2</t>
-  </si>
-  <si>
-    <t>Algorithm 3</t>
-  </si>
-  <si>
-    <t>Algorithm 4</t>
-  </si>
-  <si>
-    <t>Algorithm 5</t>
-  </si>
-  <si>
-    <t>Algorithm 6</t>
-  </si>
-  <si>
-    <t>Algorithm 7</t>
-  </si>
-  <si>
-    <t>Algorithm 8</t>
-  </si>
-  <si>
-    <t>Algorithm 9</t>
-  </si>
-  <si>
-    <t>Algorithm 10</t>
-  </si>
-  <si>
-    <t>Algorithm 11</t>
-  </si>
-  <si>
-    <t>Algorithm 12</t>
-  </si>
-  <si>
-    <t>Algorithm 13</t>
-  </si>
-  <si>
-    <t>Algorithm 14</t>
-  </si>
-  <si>
-    <t>Algorithm 15</t>
-  </si>
-  <si>
-    <t>Number of Best Functions</t>
+    <t>P-value of the one-sided Welch t-test for the CEC benchmark functions 2014 (30 Dim)</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>alg_base vs alg2</t>
+  </si>
+  <si>
+    <t>alg_base vs alg3</t>
+  </si>
+  <si>
+    <t>alg_base vs alg4</t>
+  </si>
+  <si>
+    <t>alg_base vs alg5</t>
+  </si>
+  <si>
+    <t>alg_base vs alg6</t>
+  </si>
+  <si>
+    <t>alg_base vs alg7</t>
+  </si>
+  <si>
+    <t>alg_base vs alg8</t>
+  </si>
+  <si>
+    <t>alg_base vs alg9</t>
+  </si>
+  <si>
+    <t>alg_base vs alg10</t>
+  </si>
+  <si>
+    <t>alg_base vs alg11</t>
+  </si>
+  <si>
+    <t>alg_base vs alg12</t>
+  </si>
+  <si>
+    <t>alg_base vs alg13</t>
+  </si>
+  <si>
+    <t>alg_base vs alg14</t>
+  </si>
+  <si>
+    <t>alg_base vs alg15</t>
+  </si>
+  <si>
+    <t>Decision (h) of the one-sided Welch t-test for the CEC benchmark functions 2014 (30 Dim)</t>
+  </si>
+  <si>
+    <t>P-value of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2014 (30 Dim)</t>
+  </si>
+  <si>
+    <t>Decision (h) of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2014 (30 Dim)</t>
+  </si>
+  <si>
+    <t>Rank-sum statistic (W) for the Wilcoxon rank-sum test for the CEC benchmark functions 2014 (30 Dim)</t>
+  </si>
+  <si>
+    <t>Function ranking and overall Friedman analysis for the CEC benchmark functions 2014 (30 Dim)</t>
+  </si>
+  <si>
+    <t>Algorithm 1 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 2 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 3 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 4 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 5 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 6 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 7 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 8 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 9 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 10 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 11 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 12 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 13 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 14 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 15 Rank</t>
+  </si>
+  <si>
+    <t>Best Algorithm</t>
+  </si>
+  <si>
+    <t>Kruskal-Wallis p</t>
+  </si>
+  <si>
+    <t>Significant?</t>
+  </si>
+  <si>
+    <t>Average Rank</t>
   </si>
   <si>
     <t>Overall Rank</t>
   </si>
   <si>
-    <t>P-value of the one-sided Welch t-test for the CEC benchmark functions 2014 (30 Dim)</t>
-  </si>
-  <si>
-    <t>Function</t>
-  </si>
-  <si>
-    <t>alg_base vs alg2</t>
-  </si>
-  <si>
-    <t>alg_base vs alg3</t>
-  </si>
-  <si>
-    <t>alg_base vs alg4</t>
-  </si>
-  <si>
-    <t>alg_base vs alg5</t>
-  </si>
-  <si>
-    <t>alg_base vs alg6</t>
-  </si>
-  <si>
-    <t>alg_base vs alg7</t>
-  </si>
-  <si>
-    <t>alg_base vs alg8</t>
-  </si>
-  <si>
-    <t>alg_base vs alg9</t>
-  </si>
-  <si>
-    <t>alg_base vs alg10</t>
-  </si>
-  <si>
-    <t>alg_base vs alg11</t>
-  </si>
-  <si>
-    <t>alg_base vs alg12</t>
-  </si>
-  <si>
-    <t>alg_base vs alg13</t>
-  </si>
-  <si>
-    <t>alg_base vs alg14</t>
-  </si>
-  <si>
-    <t>alg_base vs alg15</t>
-  </si>
-  <si>
-    <t>Decision (h) of the one-sided Welch t-test for the CEC benchmark functions 2014 (30 Dim)</t>
-  </si>
-  <si>
-    <t>P-value of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2014 (30 Dim)</t>
-  </si>
-  <si>
-    <t>Decision (h) of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2014 (30 Dim)</t>
-  </si>
-  <si>
-    <t>Rank-sum statistic (W) for the Wilcoxon rank-sum test for the CEC benchmark functions 2014 (30 Dim)</t>
-  </si>
-  <si>
-    <t>Function ranking and overall Friedman analysis for the CEC benchmark functions 2014 (30 Dim)</t>
-  </si>
-  <si>
-    <t>Algorithm 1 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 2 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 3 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 4 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 5 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 6 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 7 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 8 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 9 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 10 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 11 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 12 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 13 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 14 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 15 Rank</t>
-  </si>
-  <si>
-    <t>Best Algorithm</t>
-  </si>
-  <si>
-    <t>Kruskal-Wallis p</t>
-  </si>
-  <si>
-    <t>Significant?</t>
-  </si>
-  <si>
-    <t>Average Rank</t>
-  </si>
-  <si>
     <t>Overall Friedman Test</t>
   </si>
   <si>
@@ -409,6 +394,12 @@
   </si>
   <si>
     <t>Optional figures showing the distribution of final objective values across independent runs for each function and algorithm.</t>
+  </si>
+  <si>
+    <t>Total number of best answers</t>
+  </si>
+  <si>
+    <t>Total number of equal-best answers</t>
   </si>
 </sst>
 </file>
@@ -534,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -576,7 +567,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -592,38 +582,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -890,9 +887,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -996,37 +993,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R96"/>
+  <dimension ref="A1:R95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="5" customWidth="1"/>
     <col min="2" max="2" width="4" customWidth="1"/>
-    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="12" width="11.28515625" customWidth="1"/>
     <col min="13" max="18" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
     </row>
     <row r="2" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -1035,60 +1032,60 @@
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="Q2" s="10" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="R2" s="10" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
+      <c r="A3" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -1107,12 +1104,10 @@
       <c r="R3" s="2"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="26"/>
-      <c r="B4" s="7" t="s">
-        <v>3</v>
-      </c>
+      <c r="A4" s="28"/>
+      <c r="B4" s="26"/>
       <c r="C4" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -1131,12 +1126,10 @@
       <c r="R4" s="6"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="26"/>
-      <c r="B5" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="A5" s="28"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -1155,12 +1148,12 @@
       <c r="R5" s="4"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="26"/>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
+      <c r="A6" s="28"/>
+      <c r="B6" s="25" t="s">
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -1179,12 +1172,10 @@
       <c r="R6" s="2"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
-      <c r="B7" s="7" t="s">
-        <v>7</v>
-      </c>
+      <c r="A7" s="28"/>
+      <c r="B7" s="26"/>
       <c r="C7" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -1203,12 +1194,10 @@
       <c r="R7" s="6"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="26"/>
-      <c r="B8" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="A8" s="28"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -1227,12 +1216,12 @@
       <c r="R8" s="4"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="26"/>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
+      <c r="A9" s="28"/>
+      <c r="B9" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -1251,12 +1240,10 @@
       <c r="R9" s="2"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
-      <c r="B10" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -1275,12 +1262,10 @@
       <c r="R10" s="6"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="27"/>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="A11" s="31"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -1299,14 +1284,14 @@
       <c r="R11" s="4"/>
     </row>
     <row r="12" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>10</v>
+      <c r="A12" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>25</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -1325,12 +1310,10 @@
       <c r="R12" s="2"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
-      <c r="B13" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="A13" s="28"/>
+      <c r="B13" s="26"/>
       <c r="C13" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
@@ -1349,12 +1332,10 @@
       <c r="R13" s="6"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="26"/>
-      <c r="B14" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="A14" s="28"/>
+      <c r="B14" s="27"/>
       <c r="C14" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -1373,12 +1354,12 @@
       <c r="R14" s="4"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="26"/>
-      <c r="B15" s="1" t="s">
-        <v>11</v>
+      <c r="A15" s="28"/>
+      <c r="B15" s="25" t="s">
+        <v>26</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -1397,12 +1378,10 @@
       <c r="R15" s="2"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="26"/>
-      <c r="B16" s="7" t="s">
-        <v>11</v>
-      </c>
+      <c r="A16" s="28"/>
+      <c r="B16" s="26"/>
       <c r="C16" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -1421,12 +1400,10 @@
       <c r="R16" s="6"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A17" s="26"/>
-      <c r="B17" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="A17" s="28"/>
+      <c r="B17" s="27"/>
       <c r="C17" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -1445,12 +1422,12 @@
       <c r="R17" s="4"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" s="26"/>
-      <c r="B18" s="1" t="s">
-        <v>12</v>
+      <c r="A18" s="28"/>
+      <c r="B18" s="25" t="s">
+        <v>27</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -1469,12 +1446,10 @@
       <c r="R18" s="2"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" s="26"/>
-      <c r="B19" s="7" t="s">
-        <v>12</v>
-      </c>
+      <c r="A19" s="28"/>
+      <c r="B19" s="26"/>
       <c r="C19" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
@@ -1493,12 +1468,10 @@
       <c r="R19" s="6"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" s="26"/>
-      <c r="B20" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="A20" s="28"/>
+      <c r="B20" s="27"/>
       <c r="C20" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -1517,12 +1490,12 @@
       <c r="R20" s="4"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" s="26"/>
-      <c r="B21" s="1" t="s">
-        <v>13</v>
+      <c r="A21" s="28"/>
+      <c r="B21" s="25" t="s">
+        <v>28</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -1541,12 +1514,10 @@
       <c r="R21" s="2"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22" s="26"/>
-      <c r="B22" s="7" t="s">
-        <v>13</v>
-      </c>
+      <c r="A22" s="28"/>
+      <c r="B22" s="26"/>
       <c r="C22" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -1565,12 +1536,10 @@
       <c r="R22" s="6"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" s="26"/>
-      <c r="B23" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="A23" s="28"/>
+      <c r="B23" s="27"/>
       <c r="C23" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -1589,12 +1558,12 @@
       <c r="R23" s="4"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24" s="26"/>
-      <c r="B24" s="1" t="s">
-        <v>14</v>
+      <c r="A24" s="28"/>
+      <c r="B24" s="25" t="s">
+        <v>29</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -1613,12 +1582,10 @@
       <c r="R24" s="2"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25" s="26"/>
-      <c r="B25" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="A25" s="28"/>
+      <c r="B25" s="26"/>
       <c r="C25" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -1637,12 +1604,10 @@
       <c r="R25" s="6"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A26" s="26"/>
-      <c r="B26" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="A26" s="28"/>
+      <c r="B26" s="27"/>
       <c r="C26" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -1661,12 +1626,12 @@
       <c r="R26" s="4"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" s="26"/>
-      <c r="B27" s="1" t="s">
-        <v>15</v>
+      <c r="A27" s="28"/>
+      <c r="B27" s="25" t="s">
+        <v>30</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -1685,12 +1650,10 @@
       <c r="R27" s="2"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28" s="26"/>
-      <c r="B28" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A28" s="28"/>
+      <c r="B28" s="26"/>
       <c r="C28" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
@@ -1709,12 +1672,10 @@
       <c r="R28" s="6"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29" s="26"/>
-      <c r="B29" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="A29" s="28"/>
+      <c r="B29" s="27"/>
       <c r="C29" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -1733,12 +1694,12 @@
       <c r="R29" s="4"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" s="26"/>
-      <c r="B30" s="1" t="s">
-        <v>16</v>
+      <c r="A30" s="28"/>
+      <c r="B30" s="25" t="s">
+        <v>31</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -1757,12 +1718,10 @@
       <c r="R30" s="2"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" s="26"/>
-      <c r="B31" s="7" t="s">
-        <v>16</v>
-      </c>
+      <c r="A31" s="28"/>
+      <c r="B31" s="26"/>
       <c r="C31" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
@@ -1781,12 +1740,10 @@
       <c r="R31" s="6"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" s="26"/>
-      <c r="B32" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A32" s="28"/>
+      <c r="B32" s="27"/>
       <c r="C32" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -1805,12 +1762,12 @@
       <c r="R32" s="4"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" s="26"/>
-      <c r="B33" s="1" t="s">
-        <v>17</v>
+      <c r="A33" s="28"/>
+      <c r="B33" s="25" t="s">
+        <v>32</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -1829,12 +1786,10 @@
       <c r="R33" s="2"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34" s="26"/>
-      <c r="B34" s="7" t="s">
-        <v>17</v>
-      </c>
+      <c r="A34" s="28"/>
+      <c r="B34" s="26"/>
       <c r="C34" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
@@ -1853,12 +1808,10 @@
       <c r="R34" s="6"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A35" s="26"/>
-      <c r="B35" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="A35" s="28"/>
+      <c r="B35" s="27"/>
       <c r="C35" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -1877,12 +1830,12 @@
       <c r="R35" s="4"/>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A36" s="26"/>
-      <c r="B36" s="1" t="s">
-        <v>18</v>
+      <c r="A36" s="28"/>
+      <c r="B36" s="25" t="s">
+        <v>33</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -1901,12 +1854,10 @@
       <c r="R36" s="2"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A37" s="26"/>
-      <c r="B37" s="7" t="s">
-        <v>18</v>
-      </c>
+      <c r="A37" s="28"/>
+      <c r="B37" s="26"/>
       <c r="C37" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
@@ -1925,12 +1876,10 @@
       <c r="R37" s="6"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A38" s="26"/>
-      <c r="B38" s="3" t="s">
-        <v>18</v>
-      </c>
+      <c r="A38" s="28"/>
+      <c r="B38" s="27"/>
       <c r="C38" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -1949,12 +1898,12 @@
       <c r="R38" s="4"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A39" s="26"/>
-      <c r="B39" s="1" t="s">
+      <c r="A39" s="28"/>
+      <c r="B39" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -1973,12 +1922,10 @@
       <c r="R39" s="2"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40" s="26"/>
-      <c r="B40" s="7" t="s">
-        <v>19</v>
-      </c>
+      <c r="A40" s="28"/>
+      <c r="B40" s="26"/>
       <c r="C40" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
@@ -1997,12 +1944,10 @@
       <c r="R40" s="6"/>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A41" s="26"/>
-      <c r="B41" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="A41" s="28"/>
+      <c r="B41" s="27"/>
       <c r="C41" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -2021,12 +1966,12 @@
       <c r="R41" s="4"/>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A42" s="26"/>
-      <c r="B42" s="1" t="s">
-        <v>20</v>
+      <c r="A42" s="28"/>
+      <c r="B42" s="25" t="s">
+        <v>35</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
@@ -2045,12 +1990,10 @@
       <c r="R42" s="2"/>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A43" s="26"/>
-      <c r="B43" s="7" t="s">
+      <c r="A43" s="28"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>5</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
@@ -2069,12 +2012,10 @@
       <c r="R43" s="6"/>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A44" s="26"/>
-      <c r="B44" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="A44" s="28"/>
+      <c r="B44" s="27"/>
       <c r="C44" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -2093,12 +2034,12 @@
       <c r="R44" s="4"/>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A45" s="26"/>
-      <c r="B45" s="1" t="s">
-        <v>21</v>
+      <c r="A45" s="28"/>
+      <c r="B45" s="25" t="s">
+        <v>36</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
@@ -2117,12 +2058,10 @@
       <c r="R45" s="2"/>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A46" s="26"/>
-      <c r="B46" s="7" t="s">
-        <v>21</v>
-      </c>
+      <c r="A46" s="28"/>
+      <c r="B46" s="26"/>
       <c r="C46" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
@@ -2141,12 +2080,10 @@
       <c r="R46" s="6"/>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A47" s="26"/>
-      <c r="B47" s="3" t="s">
+      <c r="A47" s="28"/>
+      <c r="B47" s="27"/>
+      <c r="C47" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>6</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -2165,12 +2102,12 @@
       <c r="R47" s="4"/>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A48" s="26"/>
-      <c r="B48" s="1" t="s">
-        <v>22</v>
+      <c r="A48" s="28"/>
+      <c r="B48" s="25" t="s">
+        <v>37</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -2189,12 +2126,10 @@
       <c r="R48" s="2"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A49" s="26"/>
-      <c r="B49" s="7" t="s">
-        <v>22</v>
-      </c>
+      <c r="A49" s="28"/>
+      <c r="B49" s="26"/>
       <c r="C49" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
@@ -2213,12 +2148,10 @@
       <c r="R49" s="6"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A50" s="27"/>
-      <c r="B50" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="A50" s="31"/>
+      <c r="B50" s="27"/>
       <c r="C50" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -2237,14 +2170,14 @@
       <c r="R50" s="4"/>
     </row>
     <row r="51" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>24</v>
+      <c r="A51" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="25" t="s">
+        <v>39</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
@@ -2263,12 +2196,10 @@
       <c r="R51" s="2"/>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A52" s="26"/>
-      <c r="B52" s="7" t="s">
-        <v>24</v>
-      </c>
+      <c r="A52" s="28"/>
+      <c r="B52" s="26"/>
       <c r="C52" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
@@ -2287,12 +2218,10 @@
       <c r="R52" s="6"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A53" s="26"/>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="A53" s="28"/>
+      <c r="B53" s="27"/>
       <c r="C53" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -2311,12 +2240,12 @@
       <c r="R53" s="4"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A54" s="26"/>
-      <c r="B54" s="1" t="s">
-        <v>25</v>
+      <c r="A54" s="28"/>
+      <c r="B54" s="25" t="s">
+        <v>40</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
@@ -2335,12 +2264,10 @@
       <c r="R54" s="2"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A55" s="26"/>
-      <c r="B55" s="7" t="s">
-        <v>25</v>
-      </c>
+      <c r="A55" s="28"/>
+      <c r="B55" s="26"/>
       <c r="C55" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
@@ -2359,12 +2286,10 @@
       <c r="R55" s="6"/>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A56" s="26"/>
-      <c r="B56" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="A56" s="28"/>
+      <c r="B56" s="27"/>
       <c r="C56" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -2383,12 +2308,12 @@
       <c r="R56" s="4"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A57" s="26"/>
-      <c r="B57" s="1" t="s">
-        <v>26</v>
+      <c r="A57" s="28"/>
+      <c r="B57" s="25" t="s">
+        <v>41</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
@@ -2407,12 +2332,10 @@
       <c r="R57" s="2"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A58" s="26"/>
-      <c r="B58" s="7" t="s">
-        <v>26</v>
-      </c>
+      <c r="A58" s="28"/>
+      <c r="B58" s="26"/>
       <c r="C58" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
@@ -2431,12 +2354,10 @@
       <c r="R58" s="6"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A59" s="26"/>
-      <c r="B59" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="A59" s="28"/>
+      <c r="B59" s="27"/>
       <c r="C59" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -2455,12 +2376,12 @@
       <c r="R59" s="4"/>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A60" s="26"/>
-      <c r="B60" s="1" t="s">
-        <v>27</v>
+      <c r="A60" s="28"/>
+      <c r="B60" s="25" t="s">
+        <v>42</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
@@ -2479,12 +2400,10 @@
       <c r="R60" s="2"/>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A61" s="26"/>
-      <c r="B61" s="7" t="s">
-        <v>27</v>
-      </c>
+      <c r="A61" s="28"/>
+      <c r="B61" s="26"/>
       <c r="C61" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
@@ -2503,12 +2422,10 @@
       <c r="R61" s="6"/>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A62" s="26"/>
-      <c r="B62" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="A62" s="28"/>
+      <c r="B62" s="27"/>
       <c r="C62" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -2527,12 +2444,12 @@
       <c r="R62" s="4"/>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A63" s="26"/>
-      <c r="B63" s="1" t="s">
-        <v>28</v>
+      <c r="A63" s="28"/>
+      <c r="B63" s="25" t="s">
+        <v>43</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
@@ -2551,12 +2468,10 @@
       <c r="R63" s="2"/>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A64" s="26"/>
-      <c r="B64" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="A64" s="28"/>
+      <c r="B64" s="26"/>
       <c r="C64" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
@@ -2575,12 +2490,10 @@
       <c r="R64" s="6"/>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A65" s="26"/>
-      <c r="B65" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="A65" s="28"/>
+      <c r="B65" s="27"/>
       <c r="C65" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
@@ -2599,12 +2512,12 @@
       <c r="R65" s="4"/>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A66" s="26"/>
-      <c r="B66" s="1" t="s">
-        <v>29</v>
+      <c r="A66" s="28"/>
+      <c r="B66" s="25" t="s">
+        <v>44</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
@@ -2623,12 +2536,10 @@
       <c r="R66" s="2"/>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A67" s="26"/>
-      <c r="B67" s="7" t="s">
-        <v>29</v>
-      </c>
+      <c r="A67" s="28"/>
+      <c r="B67" s="26"/>
       <c r="C67" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
@@ -2647,12 +2558,10 @@
       <c r="R67" s="6"/>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A68" s="27"/>
-      <c r="B68" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A68" s="31"/>
+      <c r="B68" s="27"/>
       <c r="C68" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
@@ -2671,14 +2580,14 @@
       <c r="R68" s="4"/>
     </row>
     <row r="69" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>31</v>
+      <c r="A69" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="B69" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
@@ -2697,12 +2606,10 @@
       <c r="R69" s="2"/>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A70" s="26"/>
-      <c r="B70" s="7" t="s">
-        <v>31</v>
-      </c>
+      <c r="A70" s="28"/>
+      <c r="B70" s="26"/>
       <c r="C70" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
@@ -2721,12 +2628,10 @@
       <c r="R70" s="6"/>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A71" s="26"/>
-      <c r="B71" s="3" t="s">
-        <v>31</v>
-      </c>
+      <c r="A71" s="28"/>
+      <c r="B71" s="27"/>
       <c r="C71" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
@@ -2745,12 +2650,12 @@
       <c r="R71" s="4"/>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A72" s="26"/>
-      <c r="B72" s="1" t="s">
-        <v>32</v>
+      <c r="A72" s="28"/>
+      <c r="B72" s="25" t="s">
+        <v>47</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
@@ -2769,12 +2674,10 @@
       <c r="R72" s="2"/>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A73" s="26"/>
-      <c r="B73" s="7" t="s">
-        <v>32</v>
-      </c>
+      <c r="A73" s="28"/>
+      <c r="B73" s="26"/>
       <c r="C73" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
@@ -2793,12 +2696,10 @@
       <c r="R73" s="6"/>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A74" s="26"/>
-      <c r="B74" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="A74" s="28"/>
+      <c r="B74" s="27"/>
       <c r="C74" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
@@ -2817,12 +2718,12 @@
       <c r="R74" s="4"/>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A75" s="26"/>
-      <c r="B75" s="1" t="s">
-        <v>33</v>
+      <c r="A75" s="28"/>
+      <c r="B75" s="25" t="s">
+        <v>48</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
@@ -2841,12 +2742,10 @@
       <c r="R75" s="2"/>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A76" s="26"/>
-      <c r="B76" s="7" t="s">
-        <v>33</v>
-      </c>
+      <c r="A76" s="28"/>
+      <c r="B76" s="26"/>
       <c r="C76" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
@@ -2865,12 +2764,10 @@
       <c r="R76" s="6"/>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A77" s="26"/>
-      <c r="B77" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="A77" s="28"/>
+      <c r="B77" s="27"/>
       <c r="C77" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
@@ -2889,12 +2786,12 @@
       <c r="R77" s="4"/>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A78" s="26"/>
-      <c r="B78" s="1" t="s">
-        <v>34</v>
+      <c r="A78" s="28"/>
+      <c r="B78" s="25" t="s">
+        <v>49</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
@@ -2913,12 +2810,10 @@
       <c r="R78" s="2"/>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A79" s="26"/>
-      <c r="B79" s="7" t="s">
-        <v>34</v>
-      </c>
+      <c r="A79" s="28"/>
+      <c r="B79" s="26"/>
       <c r="C79" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
@@ -2937,12 +2832,10 @@
       <c r="R79" s="6"/>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A80" s="26"/>
-      <c r="B80" s="3" t="s">
-        <v>34</v>
-      </c>
+      <c r="A80" s="28"/>
+      <c r="B80" s="27"/>
       <c r="C80" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
@@ -2961,12 +2854,12 @@
       <c r="R80" s="4"/>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A81" s="26"/>
-      <c r="B81" s="1" t="s">
-        <v>35</v>
+      <c r="A81" s="28"/>
+      <c r="B81" s="25" t="s">
+        <v>50</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
@@ -2985,12 +2878,10 @@
       <c r="R81" s="2"/>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A82" s="26"/>
-      <c r="B82" s="7" t="s">
-        <v>35</v>
-      </c>
+      <c r="A82" s="28"/>
+      <c r="B82" s="26"/>
       <c r="C82" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
@@ -3009,12 +2900,10 @@
       <c r="R82" s="6"/>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A83" s="26"/>
-      <c r="B83" s="3" t="s">
-        <v>35</v>
-      </c>
+      <c r="A83" s="28"/>
+      <c r="B83" s="27"/>
       <c r="C83" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
@@ -3033,12 +2922,12 @@
       <c r="R83" s="4"/>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A84" s="26"/>
-      <c r="B84" s="1" t="s">
-        <v>36</v>
+      <c r="A84" s="28"/>
+      <c r="B84" s="25" t="s">
+        <v>51</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
@@ -3057,12 +2946,10 @@
       <c r="R84" s="2"/>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A85" s="26"/>
-      <c r="B85" s="7" t="s">
-        <v>36</v>
-      </c>
+      <c r="A85" s="28"/>
+      <c r="B85" s="26"/>
       <c r="C85" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D85" s="6"/>
       <c r="E85" s="6"/>
@@ -3081,12 +2968,10 @@
       <c r="R85" s="6"/>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A86" s="26"/>
-      <c r="B86" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="A86" s="28"/>
+      <c r="B86" s="27"/>
       <c r="C86" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
@@ -3105,12 +2990,12 @@
       <c r="R86" s="4"/>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A87" s="26"/>
-      <c r="B87" s="1" t="s">
-        <v>37</v>
+      <c r="A87" s="28"/>
+      <c r="B87" s="25" t="s">
+        <v>52</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
@@ -3129,12 +3014,10 @@
       <c r="R87" s="2"/>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A88" s="26"/>
-      <c r="B88" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="A88" s="28"/>
+      <c r="B88" s="26"/>
       <c r="C88" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
@@ -3153,12 +3036,10 @@
       <c r="R88" s="6"/>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A89" s="26"/>
-      <c r="B89" s="3" t="s">
-        <v>37</v>
-      </c>
+      <c r="A89" s="28"/>
+      <c r="B89" s="27"/>
       <c r="C89" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
@@ -3177,12 +3058,12 @@
       <c r="R89" s="4"/>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A90" s="26"/>
-      <c r="B90" s="1" t="s">
-        <v>38</v>
+      <c r="A90" s="28"/>
+      <c r="B90" s="25" t="s">
+        <v>53</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
@@ -3201,12 +3082,10 @@
       <c r="R90" s="2"/>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A91" s="26"/>
-      <c r="B91" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="A91" s="28"/>
+      <c r="B91" s="26"/>
       <c r="C91" s="7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D91" s="6"/>
       <c r="E91" s="6"/>
@@ -3225,12 +3104,10 @@
       <c r="R91" s="6"/>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A92" s="27"/>
-      <c r="B92" s="3" t="s">
-        <v>38</v>
-      </c>
+      <c r="A92" s="31"/>
+      <c r="B92" s="27"/>
       <c r="C92" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
@@ -3249,48 +3126,33 @@
       <c r="R92" s="4"/>
     </row>
     <row r="93" spans="1:18" s="5" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="B93" s="31"/>
-      <c r="C93" s="31"/>
-      <c r="D93" s="32"/>
-      <c r="E93" s="32"/>
-      <c r="F93" s="32"/>
-      <c r="G93" s="32"/>
-      <c r="H93" s="32"/>
-      <c r="I93" s="32"/>
-      <c r="J93" s="32"/>
-      <c r="K93" s="32"/>
-      <c r="L93" s="32"/>
-      <c r="M93" s="32"/>
-      <c r="N93" s="32"/>
-      <c r="O93" s="32"/>
-      <c r="P93" s="32"/>
-      <c r="Q93" s="32"/>
-      <c r="R93" s="32"/>
+      <c r="A93" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="B93" s="25"/>
+      <c r="C93" s="25"/>
     </row>
     <row r="94" spans="1:18" s="5" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="B94" s="34"/>
-      <c r="C94" s="34"/>
-      <c r="D94" s="35"/>
-      <c r="E94" s="35"/>
-      <c r="F94" s="35"/>
-      <c r="G94" s="35"/>
-      <c r="H94" s="35"/>
-      <c r="I94" s="35"/>
-      <c r="J94" s="35"/>
-      <c r="K94" s="35"/>
-      <c r="L94" s="35"/>
-      <c r="M94" s="35"/>
-      <c r="N94" s="35"/>
-      <c r="O94" s="35"/>
-      <c r="P94" s="35"/>
-      <c r="Q94" s="35"/>
-      <c r="R94" s="35"/>
+      <c r="A94" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="B94" s="35"/>
+      <c r="C94" s="35"/>
+      <c r="D94" s="24"/>
+      <c r="E94" s="24"/>
+      <c r="F94" s="24"/>
+      <c r="G94" s="24"/>
+      <c r="H94" s="24"/>
+      <c r="I94" s="24"/>
+      <c r="J94" s="24"/>
+      <c r="K94" s="24"/>
+      <c r="L94" s="24"/>
+      <c r="M94" s="24"/>
+      <c r="N94" s="24"/>
+      <c r="O94" s="24"/>
+      <c r="P94" s="24"/>
+      <c r="Q94" s="24"/>
+      <c r="R94" s="24"/>
     </row>
     <row r="95" spans="1:18" s="5" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95"/>
@@ -3311,34 +3173,45 @@
       <c r="Q95"/>
       <c r="R95"/>
     </row>
-    <row r="96" spans="1:18" s="5" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B96"/>
-      <c r="C96"/>
-      <c r="D96"/>
-      <c r="E96"/>
-      <c r="F96"/>
-      <c r="G96"/>
-      <c r="H96"/>
-      <c r="I96"/>
-      <c r="J96"/>
-      <c r="K96"/>
-      <c r="L96"/>
-      <c r="M96"/>
-      <c r="N96"/>
-      <c r="O96"/>
-      <c r="P96"/>
-      <c r="Q96"/>
-      <c r="R96"/>
-    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="37">
     <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A94:C94"/>
     <mergeCell ref="A93:C93"/>
     <mergeCell ref="A69:A92"/>
     <mergeCell ref="A51:A68"/>
     <mergeCell ref="A12:A50"/>
     <mergeCell ref="A3:A11"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="B60:B62"/>
+    <mergeCell ref="B63:B65"/>
+    <mergeCell ref="B66:B68"/>
+    <mergeCell ref="B69:B71"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B90:B92"/>
+    <mergeCell ref="A94:C94"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B87:B89"/>
   </mergeCells>
   <conditionalFormatting sqref="D3:R3">
     <cfRule type="top10" dxfId="33" priority="30" bottom="1" rank="1"/>
@@ -3445,74 +3318,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
+      <c r="A1" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="D2" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="E2" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="F2" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="G2" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="I2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="K2" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="L2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="M2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="N2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="O2" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -3531,7 +3404,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -3550,7 +3423,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -3569,7 +3442,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -3588,7 +3461,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -3607,7 +3480,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -3626,7 +3499,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -3645,7 +3518,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -3664,7 +3537,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -3683,7 +3556,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -3702,7 +3575,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -3721,7 +3594,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -3740,7 +3613,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -3759,7 +3632,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -3778,7 +3651,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -3797,7 +3670,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -3816,7 +3689,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -3835,7 +3708,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -3854,7 +3727,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -3873,7 +3746,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -3892,7 +3765,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -3911,7 +3784,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -3930,7 +3803,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -3949,7 +3822,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -3968,7 +3841,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -3987,7 +3860,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -4006,7 +3879,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -4025,7 +3898,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -4044,7 +3917,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -4063,7 +3936,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -4104,74 +3977,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
+      <c r="A1" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="D2" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="E2" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="F2" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="G2" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="I2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="K2" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="L2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="M2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="N2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="O2" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -4190,7 +4063,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -4209,7 +4082,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
@@ -4228,7 +4101,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="14"/>
@@ -4247,7 +4120,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
@@ -4266,7 +4139,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
@@ -4285,7 +4158,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
@@ -4304,7 +4177,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
@@ -4323,7 +4196,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
@@ -4342,7 +4215,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
@@ -4361,7 +4234,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -4380,7 +4253,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -4399,7 +4272,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -4418,7 +4291,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
@@ -4437,7 +4310,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -4456,7 +4329,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
@@ -4475,7 +4348,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -4494,7 +4367,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -4513,7 +4386,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -4532,7 +4405,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -4551,7 +4424,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
@@ -4570,7 +4443,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
@@ -4589,7 +4462,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -4608,7 +4481,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -4627,7 +4500,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
@@ -4646,7 +4519,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -4665,7 +4538,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -4684,7 +4557,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
@@ -4703,7 +4576,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
@@ -4722,7 +4595,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -4763,74 +4636,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
+      <c r="A1" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="D2" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="E2" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="F2" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="G2" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="I2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="K2" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="L2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="M2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="N2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="O2" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -4849,7 +4722,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -4868,7 +4741,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -4887,7 +4760,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -4906,7 +4779,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -4925,7 +4798,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -4944,7 +4817,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -4963,7 +4836,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -4982,7 +4855,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -5001,7 +4874,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -5020,7 +4893,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -5039,7 +4912,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -5058,7 +4931,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -5077,7 +4950,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -5096,7 +4969,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -5115,7 +4988,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -5134,7 +5007,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -5153,7 +5026,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -5172,7 +5045,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -5191,7 +5064,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -5210,7 +5083,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -5229,7 +5102,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -5248,7 +5121,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -5267,7 +5140,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -5286,7 +5159,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -5305,7 +5178,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -5324,7 +5197,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -5343,7 +5216,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -5362,7 +5235,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -5381,7 +5254,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -5422,74 +5295,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
+      <c r="A1" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="D2" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="E2" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="F2" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="G2" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="I2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="K2" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="L2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="M2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="N2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="O2" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -5508,7 +5381,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -5527,7 +5400,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
@@ -5546,7 +5419,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="14"/>
@@ -5565,7 +5438,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
@@ -5584,7 +5457,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
@@ -5603,7 +5476,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
@@ -5622,7 +5495,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
@@ -5641,7 +5514,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
@@ -5660,7 +5533,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
@@ -5679,7 +5552,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -5698,7 +5571,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -5717,7 +5590,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -5736,7 +5609,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
@@ -5755,7 +5628,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -5774,7 +5647,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
@@ -5793,7 +5666,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -5812,7 +5685,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -5831,7 +5704,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -5850,7 +5723,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -5869,7 +5742,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
@@ -5888,7 +5761,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
@@ -5907,7 +5780,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -5926,7 +5799,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -5945,7 +5818,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
@@ -5964,7 +5837,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -5983,7 +5856,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -6002,7 +5875,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
@@ -6021,7 +5894,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
@@ -6040,7 +5913,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -6081,74 +5954,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
+      <c r="A1" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="D2" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="E2" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="F2" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="G2" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="I2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="K2" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="L2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="M2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="N2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="O2" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -6167,7 +6040,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -6186,7 +6059,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -6205,7 +6078,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -6224,7 +6097,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -6243,7 +6116,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -6262,7 +6135,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -6281,7 +6154,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -6300,7 +6173,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -6319,7 +6192,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -6338,7 +6211,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -6357,7 +6230,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -6376,7 +6249,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -6395,7 +6268,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -6414,7 +6287,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -6433,7 +6306,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -6452,7 +6325,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -6471,7 +6344,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -6490,7 +6363,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -6509,7 +6382,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -6528,7 +6401,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -6547,7 +6420,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -6566,7 +6439,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -6585,7 +6458,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -6604,7 +6477,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -6623,7 +6496,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -6642,7 +6515,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -6661,7 +6534,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -6680,7 +6553,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -6699,7 +6572,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -6729,98 +6602,100 @@
   <dimension ref="A1:S45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="16" t="s">
+      <c r="D2" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="E2" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="F2" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="G2" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="H2" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="I2" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="J2" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="K2" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="L2" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="M2" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="N2" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="O2" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="N2" s="16" t="s">
+      <c r="P2" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="Q2" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="P2" s="16" t="s">
+      <c r="R2" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="Q2" s="16" t="s">
+      <c r="S2" s="36" t="s">
         <v>92</v>
-      </c>
-      <c r="R2" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="S2" s="16" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -6843,7 +6718,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -6866,7 +6741,7 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -6889,7 +6764,7 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
@@ -6912,7 +6787,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
@@ -6935,7 +6810,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -6958,7 +6833,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -6981,7 +6856,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -7004,7 +6879,7 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -7027,7 +6902,7 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -7050,7 +6925,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -7073,7 +6948,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
@@ -7096,7 +6971,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -7119,7 +6994,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -7142,7 +7017,7 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -7165,7 +7040,7 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -7188,7 +7063,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -7211,7 +7086,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -7234,7 +7109,7 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -7257,7 +7132,7 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -7280,7 +7155,7 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
@@ -7303,7 +7178,7 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -7326,7 +7201,7 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -7349,7 +7224,7 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -7372,7 +7247,7 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -7395,7 +7270,7 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -7418,7 +7293,7 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -7441,7 +7316,7 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -7464,7 +7339,7 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
@@ -7487,7 +7362,7 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -7530,50 +7405,50 @@
       <c r="S33" s="16"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="18"/>
-      <c r="M34" s="18"/>
-      <c r="N34" s="18"/>
-      <c r="O34" s="18"/>
-      <c r="P34" s="18"/>
-      <c r="Q34" s="18"/>
-      <c r="R34" s="18"/>
-      <c r="S34" s="18"/>
+      <c r="A34" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="19"/>
-      <c r="N35" s="19"/>
-      <c r="O35" s="19"/>
-      <c r="P35" s="19"/>
-      <c r="Q35" s="19"/>
-      <c r="R35" s="19"/>
-      <c r="S35" s="19"/>
+      <c r="A35" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="18"/>
+      <c r="Q35" s="18"/>
+      <c r="R35" s="18"/>
+      <c r="S35" s="18"/>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="16"/>
@@ -7597,31 +7472,31 @@
       <c r="S36" s="16"/>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A37" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-      <c r="K37" s="20"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="20"/>
-      <c r="N37" s="20"/>
-      <c r="O37" s="20"/>
-      <c r="P37" s="20"/>
-      <c r="Q37" s="20"/>
-      <c r="R37" s="20"/>
-      <c r="S37" s="20"/>
+      <c r="A37" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
+      <c r="M37" s="19"/>
+      <c r="N37" s="19"/>
+      <c r="O37" s="19"/>
+      <c r="P37" s="19"/>
+      <c r="Q37" s="19"/>
+      <c r="R37" s="19"/>
+      <c r="S37" s="19"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
@@ -7644,7 +7519,7 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -7667,7 +7542,7 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
@@ -7710,17 +7585,17 @@
       <c r="S41" s="16"/>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A42" s="20" t="s">
+      <c r="A42" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B42" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="B42" s="20" t="s">
+      <c r="C42" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" s="19" t="s">
         <v>100</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="D42" s="20" t="s">
-        <v>101</v>
       </c>
       <c r="E42" s="16"/>
       <c r="F42" s="16"/>
@@ -7802,6 +7677,9 @@
       <c r="S45" s="16"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:S1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7816,75 +7694,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="22" t="s">
+    </row>
+    <row r="2" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="B2" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="22" t="s">
+    </row>
+    <row r="3" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="B3" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="22" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="B4" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="B4" s="22" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="B5" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="B5" s="22" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="B6" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="B6" s="22" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+      <c r="B7" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="22" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
+      <c r="B8" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="22" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
+      <c r="B9" s="23" t="s">
         <v>118</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>
